--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
         <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q2" t="n">
         <v>2.42</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
         <v>4.5</v>
@@ -963,10 +963,10 @@
         <v>5.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -993,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1047,74 +1047,74 @@
         <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AQ3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX3" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AY3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BB3" t="n">
         <v>2.04</v>
       </c>
-      <c r="AS3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BC3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BF3" t="n">
         <v>5.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I5" t="n">
         <v>2.14</v>
@@ -1354,7 +1354,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -1921,67 +1921,67 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="I8" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="J8" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V8" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="X8" t="n">
         <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -1993,7 +1993,7 @@
         <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2029,16 +2029,16 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT8" t="n">
         <v>7.4</v>
@@ -2050,41 +2050,41 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB8" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD8" t="n">
         <v>48</v>
       </c>
-      <c r="BC8" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>50</v>
-      </c>
       <c r="BE8" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BF8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BG8" t="n">
         <v>27</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.83</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 02:03:33</t>
+          <t>2026-04-26 04:33:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 04:33:22</t>
+          <t>2026-04-26 07:03:13</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 04:33:22</t>
+          <t>2026-04-26 07:03:13</t>
         </is>
       </c>
     </row>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 04:33:22</t>
+          <t>2026-04-26 07:03:13</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 04:33:22</t>
+          <t>2026-04-26 07:03:13</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 04:33:22</t>
+          <t>2026-04-26 07:03:13</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2.66</v>
+        <v>4.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 04:33:22</t>
+          <t>2026-04-26 07:03:13</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G8" t="n">
         <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J8" t="n">
         <v>2.68</v>
@@ -1954,7 +1954,7 @@
         <v>1.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R8" t="n">
         <v>1.22</v>
@@ -1969,7 +1969,7 @@
         <v>1.72</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
         <v>1.39</v>
@@ -1978,10 +1978,10 @@
         <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -1993,7 +1993,7 @@
         <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2038,7 +2038,7 @@
         <v>11.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
         <v>7.4</v>
@@ -2050,7 +2050,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
         <v>15.5</v>
@@ -2062,29 +2062,29 @@
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 04:33:22</t>
+          <t>2026-04-26 07:03:13</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H9" t="n">
-        <v>2.26</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
         <v>1.49</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 04:33:22</t>
+          <t>2026-04-26 07:03:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="G2" t="n">
         <v>2.48</v>
@@ -766,13 +766,13 @@
         <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -790,7 +790,7 @@
         <v>1.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -993,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="G9" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.9</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
         <v>1.49</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 07:03:13</t>
+          <t>2026-04-26 09:30:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.18</v>
+        <v>2.06</v>
       </c>
       <c r="G2" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR2" t="n">
         <v>6.4</v>
       </c>
-      <c r="J2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 09:30:54</t>
+          <t>2026-04-26 11:53:20</t>
         </is>
       </c>
     </row>
@@ -951,34 +951,34 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.68</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
         <v>1.55</v>
@@ -987,22 +987,22 @@
         <v>2.46</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T3" t="n">
         <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AQ3" t="n">
         <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AT3" t="n">
         <v>3.45</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AV3" t="n">
         <v>5</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AX3" t="n">
         <v>4.3</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 09:30:54</t>
+          <t>2026-04-26 11:53:20</t>
         </is>
       </c>
     </row>
@@ -1157,10 +1157,10 @@
         <v>2.54</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 09:30:54</t>
+          <t>2026-04-26 11:53:20</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 09:30:54</t>
+          <t>2026-04-26 11:53:20</t>
         </is>
       </c>
     </row>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 09:30:54</t>
+          <t>2026-04-26 11:53:20</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 09:30:54</t>
+          <t>2026-04-26 11:53:20</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>2.68</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
         <v>1.44</v>
@@ -2038,7 +2038,7 @@
         <v>11.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT8" t="n">
         <v>7.4</v>
@@ -2050,7 +2050,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX8" t="n">
         <v>15.5</v>
@@ -2062,29 +2062,29 @@
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 09:30:54</t>
+          <t>2026-04-26 11:53:20</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.63</v>
       </c>
       <c r="G9" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="H9" t="n">
         <v>3.95</v>
@@ -2127,7 +2127,7 @@
         <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
         <v>1.49</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 09:30:54</t>
+          <t>2026-04-26 11:53:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G2" t="n">
         <v>2.3</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K2" t="n">
         <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
         <v>1.13</v>
@@ -805,7 +805,7 @@
         <v>1.68</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
         <v>1.77</v>
@@ -838,7 +838,7 @@
         <v>12.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
         <v>27</v>
@@ -865,16 +865,16 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
         <v>5.8</v>
@@ -883,44 +883,44 @@
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD2" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 11:53:20</t>
+          <t>2026-04-26 14:11:47</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="G3" t="n">
         <v>2.2</v>
@@ -960,7 +960,7 @@
         <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
         <v>3.15</v>
@@ -969,7 +969,7 @@
         <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
@@ -981,7 +981,7 @@
         <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q3" t="n">
         <v>2.46</v>
@@ -996,13 +996,13 @@
         <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
         <v>1.24</v>
       </c>
       <c r="W3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1011,7 +1011,7 @@
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1038,7 +1038,7 @@
         <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
         <v>32</v>
@@ -1056,65 +1056,65 @@
         <v>29</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
         <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AU3" t="n">
         <v>3.65</v>
       </c>
       <c r="AV3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY3" t="n">
         <v>4.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA3" t="n">
         <v>1.86</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="BE3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG3" t="n">
         <v>1.87</v>
       </c>
-      <c r="BF3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.86</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 11:53:20</t>
+          <t>2026-04-26 14:11:47</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I4" t="n">
         <v>2.54</v>
@@ -1163,16 +1163,16 @@
         <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
         <v>2.06</v>
@@ -1181,141 +1181,141 @@
         <v>1.73</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 11:53:20</t>
+          <t>2026-04-26 14:11:47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.3</v>
+        <v>1.58</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>1.96</v>
       </c>
       <c r="H5" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="I5" t="n">
-        <v>2.14</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W5" t="n">
         <v>2.04</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 11:53:20</t>
+          <t>2026-04-26 14:11:47</t>
         </is>
       </c>
     </row>
@@ -1524,31 +1524,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.06</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>2.32</v>
+        <v>5.8</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7</v>
+        <v>1.92</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7</v>
+        <v>2.14</v>
       </c>
       <c r="J6" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.31</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 11:53:20</t>
+          <t>2026-04-26 14:11:47</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,31 +1718,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.42</v>
+        <v>2.06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.56</v>
+        <v>2.3</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I7" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>1.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.56</v>
+        <v>3.6</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 11:53:20</t>
+          <t>2026-04-26 14:11:47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Feirense</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.15</v>
+        <v>1.42</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>1.56</v>
       </c>
       <c r="H8" t="n">
-        <v>2.52</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>2.86</v>
+        <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>2.68</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 11:53:20</t>
+          <t>2026-04-26 14:11:47</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,179 +2106,567 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Feirense</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.63</v>
+        <v>3.15</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.95</v>
+        <v>2.52</v>
       </c>
       <c r="I9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>6.4</v>
       </c>
-      <c r="J9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K9" t="n">
-        <v>950</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 11:53:20</t>
+          <t>2026-04-26 14:11:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Al-Khaleej Saihat</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Al Najma Club</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-04-26 14:11:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Al-Hilal</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>25</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-04-26 14:11:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH11"/>
+  <dimension ref="A1:BH14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,7 +814,7 @@
         <v>8.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
         <v>34</v>
@@ -838,7 +838,7 @@
         <v>12.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
         <v>27</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.97</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
         <v>4.3</v>
@@ -1002,7 +1002,7 @@
         <v>1.24</v>
       </c>
       <c r="W3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I4" t="n">
         <v>2.54</v>
@@ -1187,13 +1187,13 @@
         <v>2.84</v>
       </c>
       <c r="T4" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="U4" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W4" t="n">
         <v>1.41</v>
@@ -1262,7 +1262,7 @@
         <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>22</v>
+        <v>3.85</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1286,19 +1286,19 @@
         <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>24</v>
+        <v>3.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>3.85</v>
       </c>
       <c r="BD4" t="n">
-        <v>29</v>
+        <v>3.95</v>
       </c>
       <c r="BE4" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="BF4" t="n">
         <v>19</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -1339,88 +1339,88 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="H5" t="n">
-        <v>2.04</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X5" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
         <v>11</v>
       </c>
-      <c r="J5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1441,68 +1441,68 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>5.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>5.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>40</v>
+        <v>6.6</v>
       </c>
       <c r="AT5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY5" t="n">
         <v>8.6</v>
       </c>
-      <c r="AU5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>5.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>38</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>13.5</v>
+        <v>5.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>12</v>
+        <v>5.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>20</v>
+        <v>5.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>40</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H6" t="n">
         <v>1.92</v>
@@ -1551,16 +1551,16 @@
         <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
         <v>1.77</v>
@@ -1569,134 +1569,134 @@
         <v>2.04</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
         <v>2.3</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="K7" t="n">
         <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="P7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -1924,31 +1924,31 @@
         <v>1.42</v>
       </c>
       <c r="G8" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="I8" t="n">
         <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
         <v>6.2</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
         <v>2.32</v>
@@ -1957,134 +1957,134 @@
         <v>1.56</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>3.15</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H9" t="n">
         <v>2.52</v>
@@ -2127,7 +2127,7 @@
         <v>2.86</v>
       </c>
       <c r="J9" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K9" t="n">
         <v>3.35</v>
@@ -2193,13 +2193,13 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG9" t="n">
         <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2226,13 +2226,13 @@
         <v>7.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR9" t="n">
         <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT9" t="n">
         <v>7.4</v>
@@ -2244,7 +2244,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
         <v>15.5</v>
@@ -2256,36 +2256,36 @@
         <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG9" t="n">
         <v>4.7</v>
       </c>
-      <c r="BF9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,184 +2295,184 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.44</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="H10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.44</v>
-      </c>
       <c r="Q10" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-26 14:11:47</t>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,761 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Al-Khaleej Saihat</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Al Najma Club</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X11" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-04-26 16:26:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Al-Hilal</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Dhamk</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>1.15</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" t="n">
         <v>1.21</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" t="n">
         <v>17.5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>25</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="X12" t="n">
+        <v>65</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>250</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>330</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>340</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX12" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="K11" t="n">
+      <c r="AY12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-04-26 16:26:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Scunthorpe</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Southend</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X13" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC13" t="n">
         <v>11</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2026-04-26 14:11:47</t>
+      <c r="AD13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-26 16:26:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X14" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-26 16:26:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 16:26:46</t>
+          <t>2026-04-26 18:40:29</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G3" t="n">
         <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
         <v>5.2</v>
@@ -966,7 +966,7 @@
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.48</v>
@@ -1002,7 +1002,7 @@
         <v>1.24</v>
       </c>
       <c r="W3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AC3" t="n">
         <v>970</v>
@@ -1065,10 +1065,10 @@
         <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.97</v>
+        <v>4.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AT3" t="n">
         <v>3.5</v>
@@ -1080,7 +1080,7 @@
         <v>5.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AX3" t="n">
         <v>4.4</v>
@@ -1092,29 +1092,29 @@
         <v>5.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.79</v>
+        <v>4.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.79</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="BF3" t="n">
         <v>5.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 16:26:46</t>
+          <t>2026-04-26 18:40:29</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W4" t="n">
         <v>1.41</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 16:26:46</t>
+          <t>2026-04-26 18:40:29</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>4.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 16:26:46</t>
+          <t>2026-04-26 18:40:29</t>
         </is>
       </c>
     </row>
@@ -1587,25 +1587,25 @@
         <v>1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
         <v>30</v>
       </c>
       <c r="AB6" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
         <v>28</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 16:26:46</t>
+          <t>2026-04-26 18:40:29</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 16:26:46</t>
+          <t>2026-04-26 18:40:29</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>1.42</v>
       </c>
       <c r="G8" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="H8" t="n">
         <v>6.8</v>
@@ -1942,7 +1942,7 @@
         <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
         <v>4.8</v>
@@ -1972,7 +1972,7 @@
         <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="X8" t="n">
         <v>26</v>
@@ -2014,7 +2014,7 @@
         <v>15</v>
       </c>
       <c r="AK8" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AL8" t="n">
         <v>38</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 16:26:46</t>
+          <t>2026-04-26 18:40:29</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>3.15</v>
       </c>
       <c r="G9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H9" t="n">
         <v>2.52</v>
       </c>
       <c r="I9" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="K9" t="n">
         <v>3.35</v>
@@ -2181,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
         <v>8.6</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.2</v>
+        <v>3.75</v>
       </c>
       <c r="AQ9" t="n">
         <v>6.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT9" t="n">
         <v>7.4</v>
       </c>
       <c r="AU9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE9" t="n">
         <v>5.4</v>
       </c>
-      <c r="AV9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BF9" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 16:26:46</t>
+          <t>2026-04-26 18:40:29</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         <v>1.59</v>
       </c>
       <c r="G10" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="H10" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
         <v>6.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>85</v>
+        <v>7.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2339,31 +2339,31 @@
         <v>1.16</v>
       </c>
       <c r="P10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q10" t="n">
         <v>1.49</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="T10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
         <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="X10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y10" t="n">
         <v>36</v>
@@ -2375,10 +2375,10 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
         <v>30</v>
@@ -2387,10 +2387,10 @@
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
         <v>26</v>
@@ -2420,7 +2420,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AR10" t="n">
         <v>2.58</v>
@@ -2432,7 +2432,7 @@
         <v>2.24</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AV10" t="n">
         <v>2.38</v>
@@ -2444,10 +2444,10 @@
         <v>2.24</v>
       </c>
       <c r="AY10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BA10" t="n">
         <v>2.58</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-26 16:26:46</t>
+          <t>2026-04-26 18:40:29</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
         <v>1.74</v>
@@ -2554,7 +2554,7 @@
         <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="X11" t="n">
         <v>29</v>
@@ -2596,10 +2596,10 @@
         <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -2611,19 +2611,19 @@
         <v>110</v>
       </c>
       <c r="AP11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AR11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AU11" t="n">
         <v>9.199999999999999</v>
@@ -2632,10 +2632,10 @@
         <v>4.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AY11" t="n">
         <v>8</v>
@@ -2644,7 +2644,7 @@
         <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB11" t="n">
         <v>10.5</v>
@@ -2653,20 +2653,20 @@
         <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF11" t="n">
         <v>4.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-26 16:26:46</t>
+          <t>2026-04-26 18:40:29</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>11</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
@@ -2736,10 +2736,10 @@
         <v>2.02</v>
       </c>
       <c r="S12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="T12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U12" t="n">
         <v>1.81</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-26 16:26:46</t>
+          <t>2026-04-26 18:40:29</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
         <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
         <v>1.51</v>
@@ -2948,22 +2948,22 @@
         <v>23</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AA13" t="n">
         <v>28</v>
       </c>
       <c r="AB13" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
         <v>11</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
@@ -2972,10 +2972,10 @@
         <v>29</v>
       </c>
       <c r="AG13" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
@@ -2999,7 +2999,7 @@
         <v>13.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AQ13" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
         <v>12</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AT13" t="n">
         <v>13.5</v>
@@ -3020,10 +3020,10 @@
         <v>8.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AY13" t="n">
         <v>11.5</v>
@@ -3032,29 +3032,29 @@
         <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>19.5</v>
+        <v>5.5</v>
       </c>
       <c r="BG13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-26 16:26:46</t>
+          <t>2026-04-26 18:40:29</t>
         </is>
       </c>
     </row>
@@ -3088,13 +3088,13 @@
         <v>2.42</v>
       </c>
       <c r="G14" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H14" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I14" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="J14" t="n">
         <v>4.1</v>
@@ -3115,13 +3115,13 @@
         <v>1.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q14" t="n">
         <v>1.42</v>
       </c>
       <c r="R14" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -3133,16 +3133,16 @@
         <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X14" t="n">
         <v>34</v>
       </c>
       <c r="Y14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z14" t="n">
         <v>27</v>
@@ -3178,7 +3178,7 @@
         <v>38</v>
       </c>
       <c r="AK14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="n">
         <v>23</v>
@@ -3205,7 +3205,7 @@
         <v>44</v>
       </c>
       <c r="AT14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AU14" t="n">
         <v>10</v>
@@ -3223,7 +3223,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
         <v>24</v>
@@ -3232,7 +3232,7 @@
         <v>34</v>
       </c>
       <c r="BC14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD14" t="n">
         <v>21</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-26 16:26:46</t>
+          <t>2026-04-26 18:40:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W4" t="n">
         <v>1.41</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G5" t="n">
         <v>1.81</v>
@@ -1375,7 +1375,7 @@
         <v>1.68</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
         <v>2.74</v>
@@ -1447,16 +1447,16 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>5.5</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AR5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT5" t="n">
         <v>8.800000000000001</v>
@@ -1465,10 +1465,10 @@
         <v>8.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX5" t="n">
         <v>9.800000000000001</v>
@@ -1480,10 +1480,10 @@
         <v>5.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC5" t="n">
         <v>5.1</v>
@@ -1498,11 +1498,11 @@
         <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>5.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I6" t="n">
         <v>2.14</v>
@@ -1641,7 +1641,7 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>6.4</v>
@@ -1650,31 +1650,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="AT6" t="n">
         <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AX6" t="n">
         <v>2.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BB6" t="n">
         <v>3.1</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -1769,10 +1769,10 @@
         <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V7" t="n">
         <v>1.22</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -1960,13 +1960,13 @@
         <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="T8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V8" t="n">
         <v>1.11</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="O9" t="n">
         <v>1.48</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>1.59</v>
       </c>
       <c r="G10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H10" t="n">
         <v>4.1</v>
@@ -2324,10 +2324,10 @@
         <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
@@ -2336,31 +2336,31 @@
         <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="Q10" t="n">
         <v>1.49</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
         <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="X10" t="n">
         <v>34</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G11" t="n">
         <v>1.55</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -2700,19 +2700,19 @@
         <v>1.15</v>
       </c>
       <c r="G12" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="H12" t="n">
         <v>17.5</v>
       </c>
       <c r="I12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.16</v>
@@ -2736,10 +2736,10 @@
         <v>2.02</v>
       </c>
       <c r="S12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="T12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
         <v>1.81</v>
@@ -2748,7 +2748,7 @@
         <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="X12" t="n">
         <v>65</v>
@@ -2757,7 +2757,7 @@
         <v>80</v>
       </c>
       <c r="Z12" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
@@ -2802,19 +2802,19 @@
         <v>2.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AP12" t="n">
         <v>8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR12" t="n">
         <v>9</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT12" t="n">
         <v>12.5</v>
@@ -2838,7 +2838,7 @@
         <v>7.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB12" t="n">
         <v>8.199999999999999</v>
@@ -2847,7 +2847,7 @@
         <v>11.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE12" t="n">
         <v>8.800000000000001</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>3.7</v>
       </c>
       <c r="H13" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I13" t="n">
         <v>2.32</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G14" t="n">
         <v>2.42</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.44</v>
-      </c>
       <c r="H14" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I14" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J14" t="n">
         <v>4.1</v>
@@ -3103,13 +3103,13 @@
         <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
         <v>1.13</v>
@@ -3124,7 +3124,7 @@
         <v>1.94</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T14" t="n">
         <v>1.4</v>
@@ -3133,34 +3133,34 @@
         <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X14" t="n">
         <v>34</v>
       </c>
       <c r="Y14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z14" t="n">
         <v>27</v>
       </c>
       <c r="AA14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC14" t="n">
         <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF14" t="n">
         <v>23</v>
@@ -3175,7 +3175,7 @@
         <v>26</v>
       </c>
       <c r="AJ14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK14" t="n">
         <v>20</v>
@@ -3184,13 +3184,13 @@
         <v>23</v>
       </c>
       <c r="AM14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AP14" t="n">
         <v>30</v>
@@ -3202,10 +3202,10 @@
         <v>26</v>
       </c>
       <c r="AS14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AU14" t="n">
         <v>10</v>
@@ -3217,7 +3217,7 @@
         <v>22</v>
       </c>
       <c r="AX14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY14" t="n">
         <v>11.5</v>
@@ -3229,7 +3229,7 @@
         <v>24</v>
       </c>
       <c r="BB14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC14" t="n">
         <v>19</v>
@@ -3238,17 +3238,17 @@
         <v>21</v>
       </c>
       <c r="BE14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-26 18:40:29</t>
+          <t>2026-04-26 20:52:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH14"/>
+  <dimension ref="A1:BH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>FC Ashdod</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.96</v>
+        <v>2.3</v>
       </c>
       <c r="G4" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="I4" t="n">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>1.61</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>1.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.66</v>
+        <v>2.96</v>
       </c>
       <c r="G5" t="n">
-        <v>1.81</v>
+        <v>3.45</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>2.24</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>2.54</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="W5" t="n">
-        <v>2.22</v>
+        <v>1.41</v>
       </c>
       <c r="X5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,184 +1519,184 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.3</v>
+        <v>1.66</v>
       </c>
       <c r="G6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X6" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
         <v>5.6</v>
       </c>
-      <c r="H6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X6" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AQ6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW6" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.84</v>
-      </c>
       <c r="AX6" t="n">
-        <v>2.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.78</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.78</v>
+        <v>5.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.96</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>1.91</v>
       </c>
       <c r="I7" t="n">
-        <v>5.5</v>
+        <v>2.14</v>
       </c>
       <c r="J7" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X7" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BB7" t="n">
         <v>3.1</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S7" t="n">
-        <v>8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="X7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>240</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>550</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>350</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BC7" t="n">
-        <v>7.8</v>
+        <v>3.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.6</v>
+        <v>3.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>32</v>
+        <v>3.05</v>
       </c>
       <c r="BG7" t="n">
-        <v>9</v>
+        <v>3.05</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>1.56</v>
+        <v>2.3</v>
       </c>
       <c r="H8" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>2.68</v>
       </c>
       <c r="K8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X8" t="n">
         <v>6.2</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="Y8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>550</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>350</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT8" t="n">
         <v>4.8</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X8" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AU8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY8" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="AZ8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE8" t="n">
         <v>9</v>
       </c>
-      <c r="AV8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5</v>
-      </c>
       <c r="BF8" t="n">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="BG8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Feirense</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.15</v>
+        <v>1.42</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6</v>
+        <v>1.56</v>
       </c>
       <c r="H9" t="n">
-        <v>2.52</v>
+        <v>6.8</v>
       </c>
       <c r="I9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W9" t="n">
         <v>2.88</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.39</v>
-      </c>
       <c r="X9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="AD9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>15</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="AW9" t="n">
         <v>5</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG9" t="n">
         <v>5.1</v>
       </c>
-      <c r="BD9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>5</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,112 +2300,112 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Feirense</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.59</v>
+        <v>3.15</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71</v>
+        <v>3.6</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>2.52</v>
       </c>
       <c r="I10" t="n">
-        <v>6.8</v>
+        <v>2.84</v>
       </c>
       <c r="J10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.35</v>
       </c>
-      <c r="K10" t="n">
-        <v>5.8</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="O10" t="n">
-        <v>1.15</v>
+        <v>1.48</v>
       </c>
       <c r="P10" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.49</v>
+        <v>2.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>2.06</v>
+        <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4</v>
+        <v>1.39</v>
       </c>
       <c r="X10" t="n">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2417,69 +2417,69 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.42</v>
+        <v>6.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.58</v>
+        <v>4.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.58</v>
+        <v>5.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.24</v>
+        <v>7.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.22</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.38</v>
+        <v>9.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.58</v>
+        <v>5.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>2.24</v>
+        <v>4.9</v>
       </c>
       <c r="AY10" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.36</v>
+        <v>4.9</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.58</v>
+        <v>5.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.32</v>
+        <v>5.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.42</v>
+        <v>5.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.58</v>
+        <v>5.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.58</v>
+        <v>5.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,184 +2489,184 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="G11" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="P11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X11" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>2.42</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="AR11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AV11" t="n">
         <v>2.38</v>
       </c>
-      <c r="T11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="X11" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AW11" t="n">
-        <v>5</v>
+        <v>2.58</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.65</v>
+        <v>2.24</v>
       </c>
       <c r="AY11" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>2.36</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.9</v>
+        <v>2.58</v>
       </c>
       <c r="BB11" t="n">
-        <v>10.5</v>
+        <v>2.32</v>
       </c>
       <c r="BC11" t="n">
-        <v>11</v>
+        <v>2.3</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>2.42</v>
       </c>
       <c r="BE11" t="n">
-        <v>5</v>
+        <v>2.58</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>5</v>
+        <v>2.58</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="G12" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="H12" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="I12" t="n">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X12" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC12" t="n">
         <v>11</v>
       </c>
-      <c r="K12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="X12" t="n">
-        <v>65</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>240</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>330</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>210</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>330</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BD12" t="n">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.42</v>
+        <v>4.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.15</v>
+        <v>1.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.7</v>
+        <v>1.18</v>
       </c>
       <c r="H13" t="n">
-        <v>2.06</v>
+        <v>17.5</v>
       </c>
       <c r="I13" t="n">
-        <v>2.32</v>
+        <v>22</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>11</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="L13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M13" t="n">
         <v>1.01</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.04</v>
       </c>
-      <c r="N13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.75</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.37</v>
+        <v>6.6</v>
       </c>
       <c r="X13" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="Y13" t="n">
-        <v>970</v>
+        <v>80</v>
       </c>
       <c r="Z13" t="n">
-        <v>970</v>
+        <v>240</v>
       </c>
       <c r="AA13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AC13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>330</v>
+      </c>
+      <c r="AF13" t="n">
         <v>11</v>
       </c>
-      <c r="AD13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>29</v>
-      </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AI13" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="AJ13" t="n">
-        <v>60</v>
+        <v>10.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AL13" t="n">
         <v>40</v>
       </c>
       <c r="AM13" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN13" t="n">
-        <v>26</v>
+        <v>2.8</v>
       </c>
       <c r="AO13" t="n">
-        <v>13.5</v>
+        <v>330</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.4</v>
+        <v>19.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY13" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.5</v>
+        <v>2.42</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-26 20:52:33</t>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,153 +3071,153 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="G14" t="n">
-        <v>2.42</v>
+        <v>3.7</v>
       </c>
       <c r="H14" t="n">
-        <v>2.94</v>
+        <v>2.06</v>
       </c>
       <c r="I14" t="n">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.94</v>
+        <v>1.52</v>
       </c>
       <c r="S14" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="U14" t="n">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.71</v>
+        <v>1.37</v>
       </c>
       <c r="X14" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="Y14" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AB14" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AF14" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AG14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR14" t="n">
         <v>12</v>
       </c>
-      <c r="AH14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>26</v>
-      </c>
       <c r="AS14" t="n">
-        <v>46</v>
+        <v>5.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>22</v>
+        <v>5.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>21</v>
+        <v>5.6</v>
       </c>
       <c r="AY14" t="n">
         <v>11.5</v>
@@ -3226,29 +3226,223 @@
         <v>12</v>
       </c>
       <c r="BA14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-26 23:03:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X15" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y15" t="n">
         <v>24</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="Z15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB15" t="n">
         <v>32</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BC15" t="n">
         <v>19</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BD15" t="n">
         <v>21</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BE15" t="n">
         <v>32</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BF15" t="n">
         <v>8.6</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BG15" t="n">
         <v>11.5</v>
       </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>2026-04-26 20:52:33</t>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-04-26 23:03:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H2" t="n">
         <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>3.4</v>
@@ -781,7 +781,7 @@
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O2" t="n">
         <v>1.56</v>
@@ -808,7 +808,7 @@
         <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X2" t="n">
         <v>8.6</v>
@@ -847,10 +847,10 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK2" t="n">
         <v>32</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>34</v>
       </c>
       <c r="AL2" t="n">
         <v>70</v>
@@ -868,13 +868,13 @@
         <v>4.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
         <v>5.8</v>
@@ -883,10 +883,10 @@
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>9.800000000000001</v>
@@ -895,32 +895,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB2" t="n">
         <v>6.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG2" t="n">
         <v>8.4</v>
       </c>
-      <c r="BF2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
         <v>4.4</v>
@@ -963,7 +963,7 @@
         <v>5.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
         <v>3.65</v>
@@ -999,7 +999,7 @@
         <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
         <v>1.87</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="I4" t="n">
         <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1172,7 +1172,7 @@
         <v>1.61</v>
       </c>
       <c r="O4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
         <v>1.61</v>
@@ -1193,7 +1193,7 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
         <v>1.43</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W5" t="n">
         <v>1.41</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -1539,10 +1539,10 @@
         <v>1.81</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
@@ -1563,19 +1563,19 @@
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
         <v>2.74</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U6" t="n">
         <v>2.12</v>
@@ -1584,10 +1584,10 @@
         <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -1611,7 +1611,7 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
@@ -1641,16 +1641,16 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT6" t="n">
         <v>8.800000000000001</v>
@@ -1659,10 +1659,10 @@
         <v>8.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX6" t="n">
         <v>9.800000000000001</v>
@@ -1671,32 +1671,32 @@
         <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
         <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>4.3</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="H7" t="n">
         <v>1.91</v>
@@ -1748,31 +1748,31 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
         <v>1.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="T7" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="V7" t="n">
         <v>1.87</v>
@@ -1805,17 +1805,17 @@
         <v>28</v>
       </c>
       <c r="AF7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI7" t="n">
         <v>44</v>
       </c>
-      <c r="AG7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>55</v>
-      </c>
       <c r="AJ7" t="n">
         <v>1000</v>
       </c>
@@ -1832,65 +1832,65 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.96</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.42</v>
+        <v>4</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.54</v>
+        <v>4.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.84</v>
+        <v>6</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.78</v>
+        <v>5.7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.78</v>
+        <v>5.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.96</v>
+        <v>4.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.05</v>
+        <v>5.7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
         <v>2.62</v>
       </c>
       <c r="U8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V8" t="n">
         <v>1.22</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
         <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="X9" t="n">
         <v>26</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>3.35</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
@@ -2423,10 +2423,10 @@
         <v>6.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT10" t="n">
         <v>7.4</v>
@@ -2438,41 +2438,41 @@
         <v>9.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY10" t="n">
         <v>4.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC10" t="n">
         <v>5.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG10" t="n">
         <v>5.5</v>
       </c>
-      <c r="BF10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -2527,13 +2527,13 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
         <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>1.44</v>
+        <v>2.52</v>
       </c>
       <c r="Q11" t="n">
         <v>1.49</v>
@@ -2554,7 +2554,7 @@
         <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="X11" t="n">
         <v>34</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="G12" t="n">
         <v>1.55</v>
@@ -2706,19 +2706,19 @@
         <v>6.6</v>
       </c>
       <c r="I12" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.25</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
         <v>5.1</v>
@@ -2730,25 +2730,25 @@
         <v>2.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T12" t="n">
         <v>1.74</v>
       </c>
       <c r="U12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W12" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="X12" t="n">
         <v>29</v>
@@ -2760,13 +2760,13 @@
         <v>75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB12" t="n">
         <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD12" t="n">
         <v>32</v>
@@ -2793,7 +2793,7 @@
         <v>970</v>
       </c>
       <c r="AL12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -2805,31 +2805,31 @@
         <v>110</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AU12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AY12" t="n">
         <v>8</v>
@@ -2838,7 +2838,7 @@
         <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB12" t="n">
         <v>10.5</v>
@@ -2850,17 +2850,17 @@
         <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="G13" t="n">
         <v>1.18</v>
@@ -2900,10 +2900,10 @@
         <v>17.5</v>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K13" t="n">
         <v>11.5</v>
@@ -2924,34 +2924,34 @@
         <v>3.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R13" t="n">
         <v>2.02</v>
       </c>
       <c r="S13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="T13" t="n">
         <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
         <v>6.6</v>
       </c>
       <c r="X13" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="Y13" t="n">
         <v>80</v>
       </c>
       <c r="Z13" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
@@ -2966,7 +2966,7 @@
         <v>70</v>
       </c>
       <c r="AE13" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AF13" t="n">
         <v>11</v>
@@ -2978,7 +2978,7 @@
         <v>42</v>
       </c>
       <c r="AI13" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ13" t="n">
         <v>10.5</v>
@@ -2996,7 +2996,7 @@
         <v>2.8</v>
       </c>
       <c r="AO13" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AP13" t="n">
         <v>8</v>
@@ -3005,10 +3005,10 @@
         <v>8.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT13" t="n">
         <v>12.5</v>
@@ -3017,10 +3017,10 @@
         <v>19.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX13" t="n">
         <v>8.800000000000001</v>
@@ -3029,7 +3029,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA13" t="n">
         <v>9</v>
@@ -3044,17 +3044,17 @@
         <v>7.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF13" t="n">
         <v>2.42</v>
       </c>
       <c r="BG13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>
@@ -3396,10 +3396,10 @@
         <v>26</v>
       </c>
       <c r="AS15" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AT15" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AU15" t="n">
         <v>10</v>
@@ -3435,14 +3435,14 @@
         <v>32</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG15" t="n">
         <v>11.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-26 23:03:02</t>
+          <t>2026-04-27 01:14:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -766,13 +766,13 @@
         <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.49</v>
@@ -802,7 +802,7 @@
         <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V2" t="n">
         <v>1.25</v>
@@ -826,7 +826,7 @@
         <v>7</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
         <v>21</v>
@@ -865,16 +865,16 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT2" t="n">
         <v>5.8</v>
@@ -883,10 +883,10 @@
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX2" t="n">
         <v>9.800000000000001</v>
@@ -895,32 +895,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -951,31 +951,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.65</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O3" t="n">
         <v>1.5</v>
@@ -999,10 +999,10 @@
         <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W3" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1017,10 +1017,10 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>22</v>
@@ -1059,62 +1059,62 @@
         <v>130</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AR3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY3" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="G4" t="n">
         <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J4" t="n">
         <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.61</v>
+        <v>2.82</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.96</v>
       </c>
       <c r="G5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H5" t="n">
         <v>2.24</v>
@@ -1351,7 +1351,7 @@
         <v>2.54</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>4.1</v>
@@ -1369,28 +1369,28 @@
         <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R5" t="n">
         <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X5" t="n">
         <v>22</v>
@@ -1402,7 +1402,7 @@
         <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB5" t="n">
         <v>17.5</v>
@@ -1459,7 +1459,7 @@
         <v>3.85</v>
       </c>
       <c r="AT5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
@@ -1468,7 +1468,7 @@
         <v>8.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX5" t="n">
         <v>17</v>
@@ -1489,20 +1489,20 @@
         <v>3.85</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
         <v>4</v>
       </c>
       <c r="BF5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG5" t="n">
         <v>11.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G6" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.27</v>
@@ -1563,13 +1563,13 @@
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
         <v>1.69</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
         <v>2.74</v>
@@ -1578,13 +1578,13 @@
         <v>1.72</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
         <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X6" t="n">
         <v>24</v>
@@ -1689,14 +1689,14 @@
         <v>7.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>4.3</v>
       </c>
       <c r="G7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>1.91</v>
@@ -1739,19 +1739,19 @@
         <v>2.14</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.36</v>
@@ -1775,7 +1775,7 @@
         <v>1.94</v>
       </c>
       <c r="V7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W7" t="n">
         <v>1.25</v>
@@ -1808,7 +1808,7 @@
         <v>42</v>
       </c>
       <c r="AG7" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
@@ -1832,65 +1832,65 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AQ7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU7" t="n">
         <v>4.1</v>
       </c>
-      <c r="AR7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="AV7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>6</v>
       </c>
-      <c r="AT7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV7" t="n">
+      <c r="BA7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD7" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ7" t="n">
+      <c r="BE7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG7" t="n">
         <v>5.8</v>
       </c>
-      <c r="BA7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H8" t="n">
         <v>4.6</v>
@@ -1933,7 +1933,7 @@
         <v>5.5</v>
       </c>
       <c r="J8" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K8" t="n">
         <v>3.1</v>
@@ -1945,7 +1945,7 @@
         <v>1.19</v>
       </c>
       <c r="N8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
         <v>1.81</v>
@@ -1963,16 +1963,16 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V8" t="n">
         <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X8" t="n">
         <v>6.2</v>
@@ -2032,7 +2032,7 @@
         <v>5.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR8" t="n">
         <v>7.4</v>
@@ -2041,7 +2041,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
@@ -2053,7 +2053,7 @@
         <v>8.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY8" t="n">
         <v>11.5</v>
@@ -2077,14 +2077,14 @@
         <v>9</v>
       </c>
       <c r="BF8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG8" t="n">
         <v>9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="G9" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I9" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.27</v>
@@ -2142,7 +2142,7 @@
         <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
         <v>2.32</v>
@@ -2151,31 +2151,31 @@
         <v>1.56</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="T9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V9" t="n">
         <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="X9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
         <v>34</v>
       </c>
       <c r="Z9" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2184,22 +2184,22 @@
         <v>11.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE9" t="n">
         <v>130</v>
       </c>
       <c r="AF9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG9" t="n">
         <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>110</v>
@@ -2211,13 +2211,13 @@
         <v>970</v>
       </c>
       <c r="AL9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
         <v>150</v>
@@ -2238,10 +2238,10 @@
         <v>7.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AW9" t="n">
         <v>5</v>
@@ -2259,7 +2259,7 @@
         <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
         <v>11.5</v>
@@ -2271,14 +2271,14 @@
         <v>5</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>3.15</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H10" t="n">
         <v>2.52</v>
@@ -2321,13 +2321,13 @@
         <v>2.84</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="K10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
@@ -2336,13 +2336,13 @@
         <v>2.92</v>
       </c>
       <c r="O10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P10" t="n">
         <v>1.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
@@ -2360,7 +2360,7 @@
         <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
         <v>11.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -2503,64 +2503,64 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1.71</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O11" t="n">
         <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>2.06</v>
+        <v>1.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2569,37 +2569,37 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -2703,16 +2703,16 @@
         <v>1.55</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L12" t="n">
         <v>1.25</v>
@@ -2721,25 +2721,25 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U12" t="n">
         <v>2.08</v>
@@ -2748,7 +2748,7 @@
         <v>1.14</v>
       </c>
       <c r="W12" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="X12" t="n">
         <v>29</v>
@@ -2769,7 +2769,7 @@
         <v>13.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE12" t="n">
         <v>110</v>
@@ -2787,7 +2787,7 @@
         <v>90</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK12" t="n">
         <v>970</v>
@@ -2805,62 +2805,62 @@
         <v>110</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="AV12" t="n">
         <v>4.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY12" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>4.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="BC12" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="BD12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF12" t="n">
         <v>4.6</v>
       </c>
-      <c r="BE12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>11.5</v>
@@ -2927,13 +2927,13 @@
         <v>1.31</v>
       </c>
       <c r="R13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S13" t="n">
         <v>1.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U13" t="n">
         <v>1.83</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H14" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="I14" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
@@ -3127,16 +3127,16 @@
         <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="U14" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="W14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
         <v>23</v>
@@ -3148,7 +3148,7 @@
         <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB14" t="n">
         <v>970</v>
@@ -3175,7 +3175,7 @@
         <v>30</v>
       </c>
       <c r="AJ14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
         <v>40</v>
@@ -3187,13 +3187,13 @@
         <v>75</v>
       </c>
       <c r="AN14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AO14" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AQ14" t="n">
         <v>10</v>
@@ -3202,10 +3202,10 @@
         <v>12</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU14" t="n">
         <v>7.4</v>
@@ -3214,10 +3214,10 @@
         <v>8.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AY14" t="n">
         <v>11.5</v>
@@ -3226,29 +3226,29 @@
         <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC14" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BD14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF14" t="n">
         <v>5.9</v>
       </c>
-      <c r="BD14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BG14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
         <v>34</v>
       </c>
       <c r="Y15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z15" t="n">
         <v>27</v>
@@ -3372,13 +3372,13 @@
         <v>36</v>
       </c>
       <c r="AK15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL15" t="n">
         <v>23</v>
       </c>
       <c r="AM15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AN15" t="n">
         <v>9.199999999999999</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 01:14:02</t>
+          <t>2026-04-27 03:24:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH15"/>
+  <dimension ref="A1:BH16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,16 +781,16 @@
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P2" t="n">
         <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R2" t="n">
         <v>1.17</v>
@@ -910,7 +910,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF2" t="n">
         <v>7.2</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
         <v>5.3</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
         <v>2.66</v>
       </c>
       <c r="I4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J4" t="n">
         <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,7 +1169,7 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
         <v>1.37</v>
@@ -1187,16 +1187,16 @@
         <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U4" t="n">
         <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,69 +1253,69 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.55</v>
+        <v>1.68</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.88</v>
+        <v>1.36</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.4</v>
+        <v>2.32</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.65</v>
+        <v>1.36</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.3</v>
+        <v>2.28</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.88</v>
+        <v>1.21</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.88</v>
+        <v>1.36</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.4</v>
+        <v>2.08</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.2</v>
+        <v>2.28</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.4</v>
+        <v>2.32</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.05</v>
+        <v>1.32</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.05</v>
+        <v>1.32</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Al-Shabab (KSA)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.96</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4</v>
+        <v>1.94</v>
       </c>
       <c r="H5" t="n">
-        <v>2.24</v>
+        <v>3.95</v>
       </c>
       <c r="I5" t="n">
-        <v>2.54</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="S5" t="n">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="V5" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.43</v>
+        <v>2.06</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AA5" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>60</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AF5" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="AH5" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI5" t="n">
         <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
-        <v>42</v>
+        <v>17.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN5" t="n">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="AP5" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>12</v>
+        <v>5.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BA5" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="BB5" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>19.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.68</v>
+        <v>2.96</v>
       </c>
       <c r="G6" t="n">
-        <v>1.78</v>
+        <v>3.4</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>2.24</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>2.54</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="T6" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="W6" t="n">
-        <v>2.28</v>
+        <v>1.43</v>
       </c>
       <c r="X6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR6" t="n">
         <v>12</v>
       </c>
-      <c r="AG6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AS6" t="n">
-        <v>7.4</v>
+        <v>3.85</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,108 +1713,108 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3</v>
+        <v>1.64</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="H7" t="n">
-        <v>1.91</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="n">
-        <v>2.14</v>
+        <v>5.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>3.75</v>
+        <v>2.66</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="U7" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.88</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>2.34</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
@@ -1829,68 +1829,68 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.3</v>
+        <v>18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AS7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BG7" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>4.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.32</v>
+        <v>4.9</v>
       </c>
       <c r="H8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD8" t="n">
         <v>4.6</v>
       </c>
-      <c r="I8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>240</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>550</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>350</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BE8" t="n">
-        <v>9</v>
+        <v>1.84</v>
       </c>
       <c r="BF8" t="n">
-        <v>30</v>
+        <v>3.15</v>
       </c>
       <c r="BG8" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.45</v>
+        <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.54</v>
+        <v>2.32</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="K9" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27</v>
+        <v>1.74</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.22</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.11</v>
-      </c>
       <c r="W9" t="n">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>6.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AF9" t="n">
         <v>11.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AI9" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="AK9" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AL9" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="AM9" t="n">
-        <v>130</v>
+        <v>550</v>
       </c>
       <c r="AN9" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="AO9" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="AU9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5</v>
-      </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.8</v>
+        <v>30</v>
       </c>
       <c r="BG9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Feirense</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.15</v>
+        <v>1.45</v>
       </c>
       <c r="G10" t="n">
-        <v>3.65</v>
+        <v>1.53</v>
       </c>
       <c r="H10" t="n">
-        <v>2.52</v>
+        <v>7.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.84</v>
+        <v>9.6</v>
       </c>
       <c r="J10" t="n">
-        <v>2.66</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.11</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="W10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="X10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF10" t="n">
         <v>4.8</v>
       </c>
-      <c r="T10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>5</v>
       </c>
-      <c r="AY10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,76 +2494,76 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Feirense</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>1.26</v>
+        <v>2.92</v>
       </c>
       <c r="O11" t="n">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="P11" t="n">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.2</v>
+        <v>2.44</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2572,22 +2572,22 @@
         <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG11" t="n">
         <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
@@ -2611,69 +2611,69 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="G12" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="H12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I12" t="n">
         <v>6.8</v>
       </c>
-      <c r="I12" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="J12" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.25</v>
@@ -2721,146 +2721,146 @@
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
         <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="U12" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="X12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z12" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE12" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AI12" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AK12" t="n">
         <v>970</v>
       </c>
       <c r="AL12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM12" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR12" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AS12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW12" t="n">
         <v>4.7</v>
       </c>
-      <c r="AR12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU12" t="n">
+      <c r="AX12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC12" t="n">
         <v>3.9</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BD12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG12" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="G13" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="H13" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="I13" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="K13" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="P13" t="n">
-        <v>3.55</v>
+        <v>2.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="R13" t="n">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="X13" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="Y13" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="Z13" t="n">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB13" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
         <v>25</v>
       </c>
-      <c r="AD13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>310</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>42</v>
-      </c>
       <c r="AI13" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AJ13" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>310</v>
+        <v>110</v>
       </c>
       <c r="AP13" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="AU13" t="n">
-        <v>19.5</v>
+        <v>4.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="AX13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY13" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="BE13" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.42</v>
+        <v>4.7</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.35</v>
+        <v>1.16</v>
       </c>
       <c r="G14" t="n">
-        <v>3.8</v>
+        <v>1.18</v>
       </c>
       <c r="H14" t="n">
-        <v>2.02</v>
+        <v>17.5</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>3.75</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="T14" t="n">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="V14" t="n">
-        <v>1.84</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>6.6</v>
       </c>
       <c r="X14" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>80</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>230</v>
       </c>
       <c r="AA14" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AC14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>310</v>
+      </c>
+      <c r="AF14" t="n">
         <v>11</v>
       </c>
-      <c r="AD14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>29</v>
-      </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AI14" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="AJ14" t="n">
-        <v>65</v>
+        <v>10.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AL14" t="n">
         <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>30</v>
+        <v>2.8</v>
       </c>
       <c r="AO14" t="n">
-        <v>970</v>
+        <v>310</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>19.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY14" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.9</v>
+        <v>2.42</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 03:24:52</t>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,153 +3265,153 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.42</v>
+        <v>3.35</v>
       </c>
       <c r="G15" t="n">
-        <v>2.44</v>
+        <v>3.8</v>
       </c>
       <c r="H15" t="n">
-        <v>2.88</v>
+        <v>2.06</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="R15" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="U15" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="W15" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="X15" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="Y15" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA15" t="n">
         <v>27</v>
       </c>
-      <c r="AA15" t="n">
-        <v>48</v>
-      </c>
       <c r="AB15" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT15" t="n">
         <v>14</v>
       </c>
-      <c r="AE15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AU15" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AX15" t="n">
-        <v>21</v>
+        <v>5.9</v>
       </c>
       <c r="AY15" t="n">
         <v>11.5</v>
@@ -3420,29 +3420,223 @@
         <v>12</v>
       </c>
       <c r="BA15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-04-27 05:35:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X16" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y16" t="n">
         <v>24</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="Z16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB16" t="n">
         <v>32</v>
       </c>
-      <c r="BC15" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE15" t="n">
+      <c r="BC16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE16" t="n">
         <v>32</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BF16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BG16" t="n">
         <v>11.5</v>
       </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>2026-04-27 03:24:52</t>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-27 05:35:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH16"/>
+  <dimension ref="A1:BH20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,103 +757,103 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.06</v>
+        <v>1.74</v>
       </c>
       <c r="G2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.28</v>
       </c>
-      <c r="H2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W2" t="n">
         <v>2.16</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.78</v>
-      </c>
       <c r="X2" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG2" t="n">
         <v>970</v>
       </c>
       <c r="AH2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK2" t="n">
         <v>27</v>
       </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>32</v>
-      </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX2" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA2" t="n">
         <v>6.4</v>
       </c>
-      <c r="AW2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
         <v>1.47</v>
@@ -978,7 +978,7 @@
         <v>2.72</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P3" t="n">
         <v>1.57</v>
@@ -1002,7 +1002,7 @@
         <v>1.24</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1017,16 +1017,16 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
         <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1035,7 +1035,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
         <v>110</v>
@@ -1059,62 +1059,62 @@
         <v>130</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.65</v>
+        <v>5.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.86</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BC3" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I4" t="n">
         <v>2.6</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.5</v>
-      </c>
       <c r="J4" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
         <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
         <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="AQ4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV4" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AW4" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.36</v>
+        <v>2.18</v>
       </c>
       <c r="BA4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BF4" t="n">
         <v>2.08</v>
       </c>
-      <c r="BB4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.32</v>
-      </c>
       <c r="BG4" t="n">
-        <v>1.32</v>
+        <v>2.06</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="G5" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="H5" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="I5" t="n">
         <v>4.5</v>
@@ -1357,25 +1357,25 @@
         <v>4.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
         <v>2.32</v>
@@ -1384,13 +1384,13 @@
         <v>1.56</v>
       </c>
       <c r="U5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X5" t="n">
         <v>27</v>
@@ -1402,28 +1402,28 @@
         <v>36</v>
       </c>
       <c r="AA5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB5" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>70</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI5" t="n">
         <v>42</v>
@@ -1432,84 +1432,84 @@
         <v>25</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AL5" t="n">
         <v>27</v>
       </c>
       <c r="AM5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AO5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="AT5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB5" t="n">
         <v>6</v>
       </c>
-      <c r="AU5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BC5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Al-Zulfi SC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>Al Taee</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.96</v>
+        <v>1.98</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="H6" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>2.54</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
         <v>11.5</v>
       </c>
-      <c r="BA6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BG6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.64</v>
+        <v>2.56</v>
       </c>
       <c r="G7" t="n">
-        <v>1.74</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X7" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS7" t="n">
         <v>5.1</v>
       </c>
-      <c r="I7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X7" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AT7" t="n">
         <v>11</v>
       </c>
-      <c r="AC7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF7" t="n">
         <v>12</v>
       </c>
-      <c r="AG7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG7" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,114 +1907,114 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.3</v>
+        <v>1.64</v>
       </c>
       <c r="G8" t="n">
-        <v>4.9</v>
+        <v>1.73</v>
       </c>
       <c r="H8" t="n">
-        <v>1.91</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>2.14</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>2.64</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="U8" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.88</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
         <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2023,75 +2023,75 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.3</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
         <v>6</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.85</v>
+        <v>7.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.91</v>
+        <v>14.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.84</v>
+        <v>7.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.15</v>
+        <v>6.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="G9" t="n">
-        <v>2.32</v>
+        <v>1.75</v>
       </c>
       <c r="H9" t="n">
         <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.19</v>
       </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.81</v>
-      </c>
       <c r="P9" t="n">
-        <v>1.32</v>
+        <v>2.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.55</v>
+        <v>1.56</v>
       </c>
       <c r="R9" t="n">
-        <v>1.12</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>2.34</v>
       </c>
       <c r="T9" t="n">
-        <v>2.66</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.48</v>
+        <v>2.32</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="X9" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.6</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AI9" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AL9" t="n">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>50</v>
+        <v>7.6</v>
       </c>
       <c r="AO9" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.6</v>
+        <v>4.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.6</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>30</v>
+        <v>5.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Feirense</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L10" t="n">
         <v>1.45</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="M10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV10" t="n">
         <v>9.6</v>
       </c>
-      <c r="J10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="AW10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE10" t="n">
         <v>6</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="X10" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5</v>
-      </c>
       <c r="BF10" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Feirense</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.15</v>
+        <v>1.41</v>
       </c>
       <c r="G11" t="n">
-        <v>3.65</v>
+        <v>1.49</v>
       </c>
       <c r="H11" t="n">
-        <v>2.52</v>
+        <v>7.2</v>
       </c>
       <c r="I11" t="n">
-        <v>2.84</v>
+        <v>9.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2.74</v>
+        <v>4.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.11</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="W11" t="n">
+        <v>3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR11" t="n">
         <v>4.8</v>
       </c>
-      <c r="T11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="AS11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT11" t="n">
         <v>7.6</v>
       </c>
-      <c r="AD11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AU11" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.6</v>
+        <v>4.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG11" t="n">
         <v>5</v>
       </c>
-      <c r="AY11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.59</v>
+        <v>2.08</v>
       </c>
       <c r="G12" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
         <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="K12" t="n">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>1.99</v>
       </c>
       <c r="O12" t="n">
-        <v>1.19</v>
+        <v>1.82</v>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>1.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.56</v>
+        <v>3.55</v>
       </c>
       <c r="R12" t="n">
-        <v>1.61</v>
+        <v>1.12</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.66</v>
+        <v>2.68</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="X12" t="n">
-        <v>30</v>
+        <v>6.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>5.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF12" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ12" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AL12" t="n">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AN12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>350</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR12" t="n">
         <v>7.6</v>
       </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AS12" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.7</v>
+        <v>9.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.55</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="BB12" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Najma Club</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.48</v>
+        <v>4.3</v>
       </c>
       <c r="G13" t="n">
-        <v>1.55</v>
+        <v>4.9</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6</v>
+        <v>1.91</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>2.12</v>
       </c>
       <c r="J13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X13" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BD13" t="n">
         <v>4.6</v>
       </c>
-      <c r="K13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X13" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>220</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5</v>
-      </c>
       <c r="BE13" t="n">
-        <v>5.5</v>
+        <v>1.85</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.7</v>
+        <v>2.84</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:50:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Al Bukayriyah</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Jeddah Club</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.16</v>
+        <v>1.79</v>
       </c>
       <c r="G14" t="n">
-        <v>1.18</v>
+        <v>1.93</v>
       </c>
       <c r="H14" t="n">
-        <v>17.5</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG14" t="n">
         <v>1.01</v>
       </c>
-      <c r="N14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="X14" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>230</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>310</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>310</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Al Najma Club</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.35</v>
+        <v>1.48</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8</v>
+        <v>1.55</v>
       </c>
       <c r="H15" t="n">
-        <v>2.06</v>
+        <v>6.6</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X15" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV15" t="n">
         <v>4.8</v>
       </c>
-      <c r="O15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X15" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP15" t="n">
+      <c r="AW15" t="n">
         <v>5.6</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>15</v>
-      </c>
       <c r="AX15" t="n">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY15" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>4.7</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 05:35:57</t>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,184 +3459,960 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>1.16</v>
       </c>
       <c r="G16" t="n">
-        <v>2.44</v>
+        <v>1.18</v>
       </c>
       <c r="H16" t="n">
-        <v>2.88</v>
+        <v>17.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="P16" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="R16" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="S16" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>1.83</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.69</v>
+        <v>6.6</v>
       </c>
       <c r="X16" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="Y16" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="Z16" t="n">
-        <v>27</v>
+        <v>230</v>
       </c>
       <c r="AA16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AC16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>310</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>36</v>
-      </c>
       <c r="AK16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>310</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU16" t="n">
         <v>19.5</v>
       </c>
-      <c r="AL16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AN16" t="n">
+      <c r="AV16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AO16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>22</v>
-      </c>
       <c r="AX16" t="n">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY16" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-27 07:47:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Scunthorpe</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Southend</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X17" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY17" t="n">
         <v>12</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="AZ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-27 07:47:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Portuguese Liga 3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fafe</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sao Joao Ver</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X18" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-27 07:47:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X19" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y19" t="n">
         <v>24</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="Z19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB19" t="n">
         <v>32</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BC19" t="n">
         <v>18.5</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BD19" t="n">
         <v>22</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BE19" t="n">
         <v>32</v>
       </c>
-      <c r="BF16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG16" t="n">
+      <c r="BF19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG19" t="n">
         <v>11.5</v>
       </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>2026-04-27 05:35:57</t>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-27 07:47:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Brazilian Campeonato Women</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EC Bahia (W)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Gremio FBPA (W)</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-27 07:47:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,103 +757,103 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="I2" t="n">
-        <v>7.4</v>
+        <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.78</v>
+        <v>1.26</v>
       </c>
       <c r="O2" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.48</v>
+        <v>1.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1.02</v>
       </c>
       <c r="T2" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
         <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2.16</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.98</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.72</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>1.49</v>
+        <v>1.09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>1.09</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1020,13 +1020,13 @@
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
         <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1035,10 +1035,10 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
         <v>32</v>
@@ -1047,7 +1047,7 @@
         <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1056,65 +1056,65 @@
         <v>29</v>
       </c>
       <c r="AO3" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.7</v>
+        <v>1.21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.4</v>
+        <v>1.21</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.2</v>
+        <v>1.17</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.4</v>
+        <v>1.21</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.8</v>
+        <v>1.21</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.2</v>
+        <v>1.21</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.4</v>
+        <v>1.15</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.6</v>
+        <v>1.21</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.6</v>
+        <v>1.21</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.35</v>
+        <v>1.21</v>
       </c>
       <c r="BB3" t="n">
-        <v>4</v>
+        <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.1</v>
+        <v>1.17</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.8</v>
+        <v>1.21</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.4</v>
+        <v>1.21</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>1.16</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.4</v>
+        <v>1.21</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
         <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>1.65</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="O4" t="n">
-        <v>1.37</v>
+        <v>1.06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1.06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>1.06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
         <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.7</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S5" t="n">
-        <v>2.32</v>
+        <v>1.41</v>
       </c>
       <c r="T5" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="X5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -1533,58 +1533,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.98</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>2.38</v>
+        <v>970</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>970</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>1.94</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>1.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>1.81</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1614,7 +1614,7 @@
         <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
         <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.82</v>
+        <v>110</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>2.36</v>
       </c>
       <c r="O7" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="P7" t="n">
         <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T7" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
         <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -1921,61 +1921,61 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="G8" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.7</v>
+        <v>1.52</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>2.64</v>
+        <v>1.18</v>
       </c>
       <c r="T8" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W8" t="n">
         <v>2.2</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.36</v>
-      </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
         <v>1000</v>
@@ -1987,22 +1987,22 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2014,7 +2014,7 @@
         <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2023,68 +2023,68 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -2115,64 +2115,64 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="P9" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="R9" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="T9" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="W9" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="X9" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2181,104 +2181,104 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -2309,67 +2309,67 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>2.82</v>
+        <v>1.92</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
         <v>2.92</v>
       </c>
       <c r="O10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P10" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2378,22 +2378,22 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
         <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="H11" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="I11" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7</v>
+        <v>2.88</v>
       </c>
       <c r="K11" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>1.24</v>
       </c>
       <c r="O11" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="R11" t="n">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>1.03</v>
       </c>
       <c r="T11" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="X11" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>970</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>1.06</v>
       </c>
       <c r="I12" t="n">
-        <v>5.6</v>
+        <v>970</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>3.05</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.99</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>1.12</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>1.49</v>
       </c>
       <c r="T12" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="X12" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -2891,58 +2891,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.3</v>
+        <v>1.37</v>
       </c>
       <c r="G13" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="I13" t="n">
-        <v>2.12</v>
+        <v>3.75</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>1.24</v>
       </c>
       <c r="O13" t="n">
-        <v>1.36</v>
+        <v>1.07</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.06</v>
+        <v>1.27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="S13" t="n">
-        <v>3.75</v>
+        <v>1.07</v>
       </c>
       <c r="T13" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>970</v>
@@ -2978,7 +2978,7 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.4</v>
+        <v>1.24</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.3</v>
+        <v>1.24</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.1</v>
+        <v>1.24</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.4</v>
+        <v>1.19</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.5</v>
+        <v>1.24</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.2</v>
+        <v>1.24</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.9</v>
+        <v>1.24</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.4</v>
+        <v>1.18</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="AY13" t="n">
-        <v>6</v>
+        <v>1.17</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6</v>
+        <v>1.18</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.9</v>
+        <v>1.17</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.92</v>
+        <v>1.17</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.82</v>
+        <v>1.17</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>1.17</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.85</v>
+        <v>1.17</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.84</v>
+        <v>1.24</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.9</v>
+        <v>1.24</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.79</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
-        <v>1.93</v>
+        <v>2.48</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>2.04</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="P14" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>3.05</v>
+        <v>1.81</v>
       </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
         <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6</v>
+        <v>1.09</v>
       </c>
       <c r="K15" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="P15" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="R15" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.08</v>
+        <v>1.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="X15" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H16" t="n">
         <v>17.5</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="K16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>8.4</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="P16" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="R16" t="n">
-        <v>2.04</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="T16" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
         <v>6.6</v>
       </c>
       <c r="X16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI16" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AK16" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM16" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.8</v>
+        <v>970</v>
       </c>
       <c r="AO16" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.6</v>
+        <v>1.14</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.6</v>
+        <v>1.13</v>
       </c>
       <c r="AT16" t="n">
-        <v>12.5</v>
+        <v>1.06</v>
       </c>
       <c r="AU16" t="n">
-        <v>19.5</v>
+        <v>1.14</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.4</v>
+        <v>1.14</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="AY16" t="n">
-        <v>11.5</v>
+        <v>1.13</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7.8</v>
+        <v>1.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="BC16" t="n">
-        <v>11.5</v>
+        <v>1.13</v>
       </c>
       <c r="BD16" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.42</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -3667,170 +3667,170 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.4</v>
+        <v>1.32</v>
       </c>
       <c r="G17" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H17" t="n">
         <v>2.06</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="P17" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.61</v>
+        <v>1.03</v>
       </c>
       <c r="R17" t="n">
-        <v>1.53</v>
+        <v>1.06</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>1.13</v>
       </c>
       <c r="T17" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="W17" t="n">
         <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -3864,167 +3864,167 @@
         <v>1.95</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="H18" t="n">
-        <v>3.55</v>
+        <v>1.53</v>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>1.82</v>
       </c>
       <c r="O18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.32</v>
       </c>
-      <c r="P18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.28</v>
-      </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T18" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
         <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I19" t="n">
         <v>2.92</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.94</v>
       </c>
       <c r="J19" t="n">
         <v>4.1</v>
@@ -4088,7 +4088,7 @@
         <v>3.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R19" t="n">
         <v>1.95</v>
@@ -4097,16 +4097,16 @@
         <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="X19" t="n">
         <v>34</v>
@@ -4148,7 +4148,7 @@
         <v>36</v>
       </c>
       <c r="AK19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL19" t="n">
         <v>23</v>
@@ -4163,16 +4163,16 @@
         <v>12.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT19" t="n">
         <v>20</v>
@@ -4184,7 +4184,7 @@
         <v>13.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
         <v>21</v>
@@ -4211,14 +4211,14 @@
         <v>32</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG19" t="n">
         <v>11.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>
@@ -4249,58 +4249,58 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>2.32</v>
+        <v>970</v>
       </c>
       <c r="H20" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>4.4</v>
+        <v>970</v>
       </c>
       <c r="J20" t="n">
-        <v>2.92</v>
+        <v>1.03</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="O20" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="T20" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4357,52 +4357,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-27 07:47:48</t>
+          <t>2026-04-27 10:04:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>1.78</v>
       </c>
       <c r="H2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S2" t="n">
         <v>5.1</v>
       </c>
-      <c r="I2" t="n">
-        <v>110</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.02</v>
-      </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>2.28</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>2.74</v>
       </c>
       <c r="O3" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.09</v>
+        <v>2.46</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1017,16 +1017,16 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
         <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1035,10 +1035,10 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
         <v>32</v>
@@ -1047,7 +1047,7 @@
         <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1056,65 +1056,65 @@
         <v>29</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.21</v>
+        <v>4.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.21</v>
+        <v>5.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.17</v>
+        <v>7.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.21</v>
+        <v>8.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.21</v>
+        <v>5.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.21</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.15</v>
+        <v>6.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.21</v>
+        <v>8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.21</v>
+        <v>5.1</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.21</v>
+        <v>5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.21</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.21</v>
+        <v>8.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.17</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.17</v>
+        <v>6.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.21</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.21</v>
+        <v>7</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.16</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.21</v>
+        <v>8.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>2.88</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="I4" t="n">
         <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.06</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.06</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>1.06</v>
+        <v>3.75</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
         <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="G5" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="H5" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="I5" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>2.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="S5" t="n">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -1533,58 +1533,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="G6" t="n">
-        <v>970</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>970</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.94</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.73</v>
-      </c>
       <c r="Q6" t="n">
-        <v>1.05</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>1.81</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1614,7 +1614,7 @@
         <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="G7" t="n">
         <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I7" t="n">
-        <v>110</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
         <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="S7" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
         <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="G8" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>14.5</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.52</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S8" t="n">
-        <v>1.18</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,34 +1987,34 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2023,68 +2023,68 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X9" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>1.14</v>
       </c>
-      <c r="W9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -2309,61 +2309,61 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.06</v>
+        <v>2.48</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>2.66</v>
       </c>
       <c r="J10" t="n">
-        <v>1.92</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
         <v>2.92</v>
       </c>
       <c r="O10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M11" t="n">
         <v>1.04</v>
       </c>
-      <c r="G11" t="n">
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.55</v>
       </c>
-      <c r="H11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S11" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W11" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>970</v>
+        <v>2.34</v>
       </c>
       <c r="H12" t="n">
-        <v>1.06</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>970</v>
+        <v>5.8</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>2.54</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>3.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="R12" t="n">
         <v>1.12</v>
       </c>
       <c r="S12" t="n">
-        <v>1.49</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -2891,61 +2891,61 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.37</v>
+        <v>4.3</v>
       </c>
       <c r="G13" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="H13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.86</v>
       </c>
-      <c r="I13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K13" t="n">
-        <v>950</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="U13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.24</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="n">
         <v>970</v>
@@ -2978,7 +2978,7 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.24</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.24</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.24</v>
+        <v>5.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.19</v>
+        <v>6.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.24</v>
+        <v>5.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.24</v>
+        <v>4.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.24</v>
+        <v>8.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.18</v>
+        <v>6.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.14</v>
+        <v>6.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.17</v>
+        <v>6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.18</v>
+        <v>6</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.17</v>
+        <v>7.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.17</v>
+        <v>5.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.17</v>
+        <v>7.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.17</v>
+        <v>6.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.17</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.24</v>
+        <v>7.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.24</v>
+        <v>13</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -3085,34 +3085,34 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="G14" t="n">
-        <v>2.48</v>
+        <v>1.92</v>
       </c>
       <c r="H14" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.04</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
         <v>1.73</v>
@@ -3121,134 +3121,134 @@
         <v>1.81</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>1.81</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="H15" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.09</v>
+        <v>4.6</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="P15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U15" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.02</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="G16" t="n">
         <v>1.17</v>
       </c>
       <c r="H16" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3</v>
+        <v>10.5</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="O16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.04</v>
       </c>
-      <c r="P16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W16" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ16" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL16" t="n">
         <v>38</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN16" t="n">
-        <v>970</v>
+        <v>2.82</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.14</v>
+        <v>7.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.14</v>
+        <v>8</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.14</v>
+        <v>8.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.13</v>
+        <v>8.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.06</v>
+        <v>12.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.14</v>
+        <v>21</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.14</v>
+        <v>7.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.14</v>
+        <v>8.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.13</v>
+        <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.14</v>
+        <v>8.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.13</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.14</v>
+        <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.13</v>
+        <v>2.46</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.14</v>
+        <v>8.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
@@ -3667,177 +3667,177 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.32</v>
+        <v>3.4</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H17" t="n">
         <v>2.06</v>
       </c>
       <c r="I17" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="R17" t="n">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>1.13</v>
+        <v>2.52</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="W17" t="n">
         <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Portuguese Liga 3</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,55 +3852,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sao Joao Ver</t>
+          <t>Olympique Akbou</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.82</v>
+        <v>1.24</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="S18" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -3909,7 +3909,7 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
         <v>1.01</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Portuguese Liga 3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,373 +4046,567 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Sao Joao Ver</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="G19" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="I19" t="n">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X19" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS19" t="n">
         <v>4.1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="AT19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE19" t="n">
         <v>4.2</v>
       </c>
-      <c r="L19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N19" t="n">
-        <v>8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="X19" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>32</v>
-      </c>
       <c r="BF19" t="n">
-        <v>8.800000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="BG19" t="n">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-27 10:04:50</t>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X20" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:16:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Brazilian Campeonato Women</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>EC Bahia (W)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Gremio FBPA (W)</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G20" t="n">
-        <v>970</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I20" t="n">
-        <v>970</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K20" t="n">
-        <v>950</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>2026-04-27 10:04:50</t>
+      <c r="F21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X21" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:16:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,55 +757,55 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H2" t="n">
         <v>6.4</v>
       </c>
       <c r="I2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O2" t="n">
         <v>1.55</v>
       </c>
       <c r="P2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R2" t="n">
         <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U2" t="n">
         <v>1.68</v>
       </c>
       <c r="V2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
         <v>2.28</v>
@@ -814,13 +814,13 @@
         <v>9</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
         <v>60</v>
       </c>
       <c r="AA2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AB2" t="n">
         <v>5.7</v>
@@ -829,16 +829,16 @@
         <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE2" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>36</v>
@@ -865,16 +865,16 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
         <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
         <v>5.3</v>
@@ -886,19 +886,19 @@
         <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB2" t="n">
         <v>12.5</v>
@@ -907,20 +907,20 @@
         <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF2" t="n">
         <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>2.18</v>
@@ -966,7 +966,7 @@
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
         <v>1.47</v>
@@ -996,7 +996,7 @@
         <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
         <v>1.25</v>
@@ -1008,7 +1008,7 @@
         <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
         <v>38</v>
@@ -1038,7 +1038,7 @@
         <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
         <v>32</v>
@@ -1056,7 +1056,7 @@
         <v>29</v>
       </c>
       <c r="AO3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP3" t="n">
         <v>4.7</v>
@@ -1068,7 +1068,7 @@
         <v>7.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT3" t="n">
         <v>5.9</v>
@@ -1080,13 +1080,13 @@
         <v>6.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
         <v>5.1</v>
       </c>
       <c r="AY3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ3" t="n">
         <v>6.6</v>
@@ -1101,7 +1101,7 @@
         <v>6.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE3" t="n">
         <v>7</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G4" t="n">
         <v>3.2</v>
@@ -1160,7 +1160,7 @@
         <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>1.44</v>
@@ -1172,19 +1172,19 @@
         <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
         <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
         <v>1.8</v>
@@ -1196,10 +1196,10 @@
         <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1262,53 +1262,53 @@
         <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT4" t="n">
         <v>8</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="AY4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE4" t="n">
         <v>5.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>1.82</v>
       </c>
       <c r="G5" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H5" t="n">
         <v>3.8</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
         <v>4.2</v>
@@ -1366,31 +1366,31 @@
         <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
         <v>2.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="R5" t="n">
         <v>1.71</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T5" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X5" t="n">
         <v>34</v>
@@ -1417,7 +1417,7 @@
         <v>46</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
@@ -1447,62 +1447,62 @@
         <v>27</v>
       </c>
       <c r="AP5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG5" t="n">
         <v>7</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="G6" t="n">
         <v>2.2</v>
@@ -1542,7 +1542,7 @@
         <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
         <v>3.35</v>
@@ -1566,19 +1566,19 @@
         <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
         <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
         <v>1.27</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G7" t="n">
         <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I7" t="n">
         <v>2.8</v>
@@ -1760,19 +1760,19 @@
         <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
         <v>2.54</v>
       </c>
       <c r="T7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V7" t="n">
         <v>1.56</v>
@@ -1844,7 +1844,7 @@
         <v>14.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>11</v>
@@ -1868,19 +1868,19 @@
         <v>11</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
         <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF7" t="n">
         <v>12.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -1930,19 +1930,19 @@
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
         <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
         <v>5.1</v>
@@ -1954,7 +1954,7 @@
         <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R8" t="n">
         <v>1.52</v>
@@ -1966,10 +1966,10 @@
         <v>1.67</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
         <v>2.36</v>
@@ -2071,7 +2071,7 @@
         <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE8" t="n">
         <v>6.2</v>
@@ -2080,11 +2080,11 @@
         <v>6.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I9" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.25</v>
@@ -2157,22 +2157,22 @@
         <v>2.42</v>
       </c>
       <c r="T9" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="U9" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
         <v>1.21</v>
       </c>
       <c r="W9" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="Y9" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2187,7 +2187,7 @@
         <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2211,7 +2211,7 @@
         <v>970</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.26</v>
+        <v>2.02</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.26</v>
+        <v>2.94</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.52</v>
+        <v>3.05</v>
       </c>
       <c r="AY9" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.26</v>
+        <v>1.99</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.24</v>
+        <v>3.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.19</v>
+        <v>2.02</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.26</v>
+        <v>3.05</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.15</v>
+        <v>2.04</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="BF9" t="n">
         <v>5.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.23</v>
+        <v>2.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>2.48</v>
       </c>
       <c r="I10" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J10" t="n">
         <v>3.1</v>
@@ -2336,13 +2336,13 @@
         <v>2.92</v>
       </c>
       <c r="O10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P10" t="n">
         <v>1.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
@@ -2426,16 +2426,16 @@
         <v>11</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
         <v>5.1</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="AW10" t="n">
         <v>8</v>
@@ -2447,22 +2447,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>7</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.74</v>
+        <v>8.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.18</v>
+        <v>7.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.22</v>
+        <v>2.88</v>
       </c>
       <c r="BF10" t="n">
         <v>8.800000000000001</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>1.41</v>
       </c>
       <c r="G11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="J11" t="n">
         <v>4.9</v>
@@ -2545,19 +2545,19 @@
         <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U11" t="n">
         <v>1.98</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y11" t="n">
         <v>32</v>
@@ -2587,7 +2587,7 @@
         <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
         <v>120</v>
@@ -2599,13 +2599,13 @@
         <v>970</v>
       </c>
       <c r="AL11" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM11" t="n">
         <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO11" t="n">
         <v>160</v>
@@ -2614,13 +2614,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="AT11" t="n">
         <v>7.8</v>
@@ -2629,13 +2629,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW11" t="n">
         <v>7.2</v>
       </c>
-      <c r="AW11" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AX11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY11" t="n">
         <v>8</v>
@@ -2644,7 +2644,7 @@
         <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB11" t="n">
         <v>9.6</v>
@@ -2653,20 +2653,20 @@
         <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.56</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -2700,31 +2700,31 @@
         <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J12" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
         <v>1.19</v>
       </c>
       <c r="N12" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="O12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="P12" t="n">
         <v>1.32</v>
@@ -2739,7 +2739,7 @@
         <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="U12" t="n">
         <v>1.5</v>
@@ -2748,10 +2748,10 @@
         <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="X12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y12" t="n">
         <v>12.5</v>
@@ -2775,7 +2775,7 @@
         <v>160</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG12" t="n">
         <v>17</v>
@@ -2811,56 +2811,56 @@
         <v>8.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AU12" t="n">
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY12" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB12" t="n">
         <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="J13" t="n">
         <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
         <v>1.43</v>
@@ -2933,16 +2933,16 @@
         <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U13" t="n">
         <v>1.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="W13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
         <v>14</v>
@@ -3005,56 +3005,56 @@
         <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AV13" t="n">
         <v>8.6</v>
       </c>
       <c r="AW13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX13" t="n">
         <v>6.2</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AY13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB13" t="n">
         <v>6.8</v>
       </c>
-      <c r="AY13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BC13" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG13" t="n">
         <v>13</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="G14" t="n">
         <v>1.92</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
         <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
         <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H15" t="n">
         <v>6</v>
@@ -3291,16 +3291,16 @@
         <v>7.2</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.25</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
         <v>5.2</v>
@@ -3315,13 +3315,13 @@
         <v>1.56</v>
       </c>
       <c r="R15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T15" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U15" t="n">
         <v>2.16</v>
@@ -3330,19 +3330,19 @@
         <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y15" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z15" t="n">
         <v>60</v>
       </c>
       <c r="AA15" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB15" t="n">
         <v>12</v>
@@ -3351,19 +3351,19 @@
         <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AE15" t="n">
         <v>80</v>
       </c>
       <c r="AF15" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG15" t="n">
         <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
         <v>70</v>
@@ -3375,7 +3375,7 @@
         <v>970</v>
       </c>
       <c r="AL15" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AM15" t="n">
         <v>100</v>
@@ -3399,16 +3399,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AV15" t="n">
         <v>6.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX15" t="n">
         <v>9.4</v>
@@ -3438,11 +3438,11 @@
         <v>5.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H17" t="n">
         <v>2.06</v>
@@ -3679,10 +3679,10 @@
         <v>2.18</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.27</v>
@@ -3697,7 +3697,7 @@
         <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q17" t="n">
         <v>1.61</v>
@@ -3718,7 +3718,7 @@
         <v>1.85</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
         <v>23</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -3873,10 +3873,10 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,22 +3885,22 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
         <v>1.01</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R18" t="n">
         <v>1.12</v>
       </c>
       <c r="S18" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -3969,52 +3969,52 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
         <v>1.01</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G19" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
         <v>3.05</v>
@@ -4085,7 +4085,7 @@
         <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
         <v>2.1</v>
@@ -4097,7 +4097,7 @@
         <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U19" t="n">
         <v>1.94</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.4</v>
       </c>
       <c r="G20" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H20" t="n">
         <v>2.86</v>
@@ -4261,7 +4261,7 @@
         <v>2.88</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K20" t="n">
         <v>4.3</v>
@@ -4285,13 +4285,13 @@
         <v>1.41</v>
       </c>
       <c r="R20" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U20" t="n">
         <v>3.4</v>
@@ -4300,10 +4300,10 @@
         <v>1.53</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y20" t="n">
         <v>25</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>
@@ -4455,13 +4455,13 @@
         <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K21" t="n">
         <v>4.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-27 12:16:49</t>
+          <t>2026-04-27 14:29:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -787,7 +787,7 @@
         <v>1.55</v>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q2" t="n">
         <v>2.56</v>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>36</v>
@@ -868,13 +868,13 @@
         <v>8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
         <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT2" t="n">
         <v>5.3</v>
@@ -901,7 +901,7 @@
         <v>5.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
@@ -913,14 +913,14 @@
         <v>5.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
         <v>4.4</v>
@@ -981,7 +981,7 @@
         <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
         <v>2.46</v>
@@ -1002,16 +1002,16 @@
         <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1023,7 +1023,7 @@
         <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>85</v>
@@ -1041,10 +1041,10 @@
         <v>110</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL3" t="n">
         <v>55</v>
@@ -1053,22 +1053,22 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO3" t="n">
         <v>130</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>5.9</v>
@@ -1077,44 +1077,44 @@
         <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB3" t="n">
         <v>7</v>
       </c>
-      <c r="AX3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB3" t="n">
+      <c r="BC3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF3" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>2.52</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J4" t="n">
         <v>3.2</v>
@@ -1175,7 +1175,7 @@
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
         <v>2.08</v>
@@ -1187,7 +1187,7 @@
         <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
         <v>4.8</v>
@@ -1363,37 +1363,37 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R5" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
         <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
         <v>24</v>
@@ -1408,7 +1408,7 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>220</v>
       </c>
       <c r="AD5" t="n">
         <v>20</v>
@@ -1417,7 +1417,7 @@
         <v>46</v>
       </c>
       <c r="AF5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
@@ -1435,22 +1435,22 @@
         <v>970</v>
       </c>
       <c r="AL5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN5" t="n">
         <v>7.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP5" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR5" t="n">
         <v>7.4</v>
@@ -1459,10 +1459,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AV5" t="n">
         <v>6.4</v>
@@ -1471,13 +1471,13 @@
         <v>7.8</v>
       </c>
       <c r="AX5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.4</v>
       </c>
       <c r="BA5" t="n">
         <v>7.6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -1563,22 +1563,22 @@
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
         <v>1.93</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
         <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
         <v>1.27</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>2.52</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
         <v>3.65</v>
@@ -1772,10 +1772,10 @@
         <v>1.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W7" t="n">
         <v>1.53</v>
@@ -1832,7 +1832,7 @@
         <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AP7" t="n">
         <v>16</v>
@@ -1844,7 +1844,7 @@
         <v>14.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT7" t="n">
         <v>11</v>
@@ -1871,7 +1871,7 @@
         <v>6.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC7" t="n">
         <v>19</v>
@@ -1880,7 +1880,7 @@
         <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF7" t="n">
         <v>12.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>1.61</v>
       </c>
       <c r="G8" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="J8" t="n">
         <v>4.3</v>
@@ -1939,7 +1939,7 @@
         <v>4.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -1951,7 +1951,7 @@
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
         <v>1.59</v>
@@ -1963,22 +1963,22 @@
         <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="U8" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="X8" t="n">
         <v>28</v>
       </c>
       <c r="Y8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,43 +1987,43 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AK8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2035,10 +2035,10 @@
         <v>20</v>
       </c>
       <c r="AR8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT8" t="n">
         <v>9.800000000000001</v>
@@ -2050,10 +2050,10 @@
         <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
         <v>8.4</v>
@@ -2062,29 +2062,29 @@
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC8" t="n">
         <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.8</v>
+        <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF8" t="n">
         <v>6.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="G9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J9" t="n">
         <v>4.1</v>
@@ -2142,16 +2142,16 @@
         <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="R9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
         <v>2.42</v>
@@ -2160,19 +2160,19 @@
         <v>1.7</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="V9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X9" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2187,7 +2187,7 @@
         <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2211,7 +2211,7 @@
         <v>970</v>
       </c>
       <c r="AL9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.04</v>
+        <v>6.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.94</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="AY9" t="n">
-        <v>2.86</v>
+        <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.42</v>
+        <v>7.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G10" t="n">
         <v>3.4</v>
@@ -2324,40 +2324,40 @@
         <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O10" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="P10" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
         <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="U10" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W10" t="n">
         <v>1.41</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR10" t="n">
         <v>5.6</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>11</v>
-      </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AU10" t="n">
         <v>4.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="AX10" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>8.6</v>
+        <v>2.66</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.4</v>
+        <v>2.72</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.199999999999999</v>
+        <v>2.62</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -2536,13 +2536,13 @@
         <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R11" t="n">
         <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
         <v>1.89</v>
@@ -2557,7 +2557,7 @@
         <v>3.15</v>
       </c>
       <c r="X11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y11" t="n">
         <v>32</v>
@@ -2587,7 +2587,7 @@
         <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
         <v>120</v>
@@ -2599,7 +2599,7 @@
         <v>970</v>
       </c>
       <c r="AL11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM11" t="n">
         <v>140</v>
@@ -2614,13 +2614,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AT11" t="n">
         <v>7.8</v>
@@ -2629,10 +2629,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX11" t="n">
         <v>7.2</v>
@@ -2644,7 +2644,7 @@
         <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BB11" t="n">
         <v>9.6</v>
@@ -2653,20 +2653,20 @@
         <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF11" t="n">
         <v>5</v>
       </c>
       <c r="BG11" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
         <v>2.28</v>
@@ -2721,7 +2721,7 @@
         <v>1.19</v>
       </c>
       <c r="N12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>1.82</v>
@@ -2742,7 +2742,7 @@
         <v>2.66</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
         <v>1.22</v>
@@ -2763,10 +2763,10 @@
         <v>200</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
         <v>26</v>
@@ -2778,7 +2778,7 @@
         <v>13.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH12" t="n">
         <v>40</v>
@@ -2787,7 +2787,7 @@
         <v>220</v>
       </c>
       <c r="AJ12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
         <v>46</v>
@@ -2811,56 +2811,56 @@
         <v>8.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.7</v>
+        <v>27</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="AU12" t="n">
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY12" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB12" t="n">
         <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
         <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
@@ -2948,34 +2948,34 @@
         <v>14</v>
       </c>
       <c r="Y13" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="Z13" t="n">
         <v>970</v>
       </c>
       <c r="AA13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AB13" t="n">
         <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
         <v>970</v>
       </c>
       <c r="AE13" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AF13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
         <v>44</v>
@@ -3005,56 +3005,56 @@
         <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
         <v>13</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
         <v>4.1</v>
@@ -3115,7 +3115,7 @@
         <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
         <v>1.81</v>
@@ -3127,10 +3127,10 @@
         <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V14" t="n">
         <v>1.19</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -3282,49 +3282,49 @@
         <v>1.52</v>
       </c>
       <c r="G15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
       </c>
       <c r="P15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.44</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.42</v>
-      </c>
       <c r="T15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U15" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
         <v>1.16</v>
@@ -3333,10 +3333,10 @@
         <v>2.68</v>
       </c>
       <c r="X15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Z15" t="n">
         <v>60</v>
@@ -3351,7 +3351,7 @@
         <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
         <v>80</v>
@@ -3363,7 +3363,7 @@
         <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
         <v>70</v>
@@ -3375,7 +3375,7 @@
         <v>970</v>
       </c>
       <c r="AL15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM15" t="n">
         <v>100</v>
@@ -3399,10 +3399,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AV15" t="n">
         <v>6.8</v>
@@ -3423,7 +3423,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" t="n">
         <v>12.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>1.15</v>
       </c>
       <c r="G16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="H16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="K16" t="n">
         <v>11.5</v>
@@ -3500,19 +3500,19 @@
         <v>8.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P16" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="R16" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="S16" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="T16" t="n">
         <v>1.99</v>
@@ -3524,7 +3524,7 @@
         <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="X16" t="n">
         <v>60</v>
@@ -3539,22 +3539,22 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AD16" t="n">
         <v>85</v>
       </c>
       <c r="AE16" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
         <v>44</v>
@@ -3566,55 +3566,55 @@
         <v>10</v>
       </c>
       <c r="AK16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="AO16" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV16" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AW16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX16" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AY16" t="n">
         <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB16" t="n">
         <v>8.199999999999999</v>
@@ -3623,20 +3623,20 @@
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -3676,10 +3676,10 @@
         <v>2.06</v>
       </c>
       <c r="I17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K17" t="n">
         <v>4.4</v>
@@ -3694,16 +3694,16 @@
         <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P17" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S17" t="n">
         <v>2.52</v>
@@ -3712,10 +3712,10 @@
         <v>1.58</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="W17" t="n">
         <v>1.36</v>
@@ -3742,10 +3742,10 @@
         <v>970</v>
       </c>
       <c r="AE17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG17" t="n">
         <v>18</v>
@@ -3787,50 +3787,50 @@
         <v>19</v>
       </c>
       <c r="AT17" t="n">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="AU17" t="n">
         <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>5.9</v>
       </c>
       <c r="BA17" t="n">
         <v>21</v>
       </c>
       <c r="BB17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC17" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BD17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF17" t="n">
         <v>7</v>
       </c>
-      <c r="BD17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>21</v>
-      </c>
       <c r="BG17" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -3861,170 +3861,170 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>1.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.47</v>
+        <v>2.22</v>
       </c>
       <c r="R18" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.47</v>
+        <v>2.44</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>2.22</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H19" t="n">
         <v>3.05</v>
@@ -4067,19 +4067,19 @@
         <v>3.55</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
         <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.38</v>
@@ -4097,7 +4097,7 @@
         <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U19" t="n">
         <v>1.94</v>
@@ -4106,10 +4106,10 @@
         <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X19" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Y19" t="n">
         <v>13.5</v>
@@ -4169,7 +4169,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
         <v>4.1</v>
@@ -4184,7 +4184,7 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -4193,16 +4193,16 @@
         <v>8.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.7</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB19" t="n">
         <v>4</v>
       </c>
-      <c r="BB19" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BC19" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BD19" t="n">
         <v>4</v>
@@ -4211,14 +4211,14 @@
         <v>4.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G20" t="n">
         <v>2.44</v>
@@ -4264,7 +4264,7 @@
         <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.23</v>
@@ -4273,25 +4273,25 @@
         <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q20" t="n">
         <v>1.41</v>
       </c>
       <c r="R20" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U20" t="n">
         <v>3.4</v>
@@ -4315,10 +4315,10 @@
         <v>48</v>
       </c>
       <c r="AB20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
         <v>14</v>
@@ -4327,10 +4327,10 @@
         <v>25</v>
       </c>
       <c r="AF20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
         <v>12.5</v>
@@ -4342,7 +4342,7 @@
         <v>36</v>
       </c>
       <c r="AK20" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="n">
         <v>23</v>
@@ -4372,10 +4372,10 @@
         <v>20</v>
       </c>
       <c r="AU20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
         <v>23</v>
@@ -4384,7 +4384,7 @@
         <v>21</v>
       </c>
       <c r="AY20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
         <v>12</v>
@@ -4396,7 +4396,7 @@
         <v>32</v>
       </c>
       <c r="BC20" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD20" t="n">
         <v>21</v>
@@ -4405,14 +4405,14 @@
         <v>32</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG20" t="n">
         <v>11</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
         <v>4.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
@@ -4476,7 +4476,7 @@
         <v>1.93</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
         <v>1.36</v>
@@ -4554,19 +4554,19 @@
         <v>4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AV21" t="n">
         <v>4</v>
@@ -4575,25 +4575,25 @@
         <v>4.7</v>
       </c>
       <c r="AX21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AZ21" t="n">
         <v>4.1</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC21" t="n">
         <v>4.3</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE21" t="n">
         <v>4.9</v>
@@ -4602,11 +4602,11 @@
         <v>4</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-27 14:29:17</t>
+          <t>2026-04-27 16:38:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G2" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H2" t="n">
         <v>6.4</v>
       </c>
       <c r="I2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.44</v>
@@ -790,7 +790,7 @@
         <v>1.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R2" t="n">
         <v>1.19</v>
@@ -805,10 +805,10 @@
         <v>1.68</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X2" t="n">
         <v>9</v>
@@ -820,19 +820,19 @@
         <v>60</v>
       </c>
       <c r="AA2" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AB2" t="n">
         <v>5.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
         <v>30</v>
       </c>
       <c r="AE2" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
@@ -868,19 +868,19 @@
         <v>8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT2" t="n">
         <v>5.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
         <v>21</v>
@@ -889,16 +889,16 @@
         <v>13.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="BB2" t="n">
         <v>16</v>
@@ -907,20 +907,20 @@
         <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H3" t="n">
         <v>4.4</v>
@@ -969,22 +969,22 @@
         <v>3.35</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
@@ -1002,7 +1002,7 @@
         <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1026,7 +1026,7 @@
         <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1059,16 +1059,16 @@
         <v>130</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AR3" t="n">
         <v>7.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
         <v>5.9</v>
@@ -1077,7 +1077,7 @@
         <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW3" t="n">
         <v>7.4</v>
@@ -1092,13 +1092,13 @@
         <v>6.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB3" t="n">
         <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD3" t="n">
         <v>8</v>
@@ -1107,14 +1107,14 @@
         <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="J4" t="n">
         <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1175,7 +1175,7 @@
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
         <v>2.08</v>
@@ -1196,25 +1196,25 @@
         <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="X4" t="n">
         <v>15</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1250,31 +1250,31 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP4" t="n">
         <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
         <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AU4" t="n">
         <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
         <v>14.5</v>
@@ -1286,29 +1286,29 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
         <v>3.95</v>
@@ -1372,7 +1372,7 @@
         <v>2.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="R5" t="n">
         <v>1.67</v>
@@ -1390,25 +1390,25 @@
         <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
         <v>36</v>
       </c>
       <c r="AA5" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>220</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
         <v>20</v>
@@ -1453,7 +1453,7 @@
         <v>6.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS5" t="n">
         <v>8.199999999999999</v>
@@ -1462,25 +1462,25 @@
         <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AV5" t="n">
         <v>6.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>6.4</v>
       </c>
-      <c r="AY5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BA5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
         <v>6.6</v>
@@ -1492,17 +1492,17 @@
         <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF5" t="n">
         <v>5.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
         <v>1.34</v>
@@ -1563,16 +1563,16 @@
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
         <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
         <v>1.78</v>
@@ -1587,7 +1587,7 @@
         <v>1.84</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -1635,28 +1635,28 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AR6" t="n">
         <v>3.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT6" t="n">
         <v>3.05</v>
       </c>
       <c r="AU6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AV6" t="n">
         <v>3.5</v>
@@ -1680,7 +1680,7 @@
         <v>3.75</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BD6" t="n">
         <v>3.9</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G7" t="n">
         <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I7" t="n">
         <v>2.78</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.26</v>
@@ -1772,7 +1772,7 @@
         <v>1.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V7" t="n">
         <v>1.57</v>
@@ -1829,7 +1829,7 @@
         <v>65</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
         <v>17</v>
@@ -1844,7 +1844,7 @@
         <v>14.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>11</v>
@@ -1868,7 +1868,7 @@
         <v>11</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB7" t="n">
         <v>6.8</v>
@@ -1877,10 +1877,10 @@
         <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
         <v>12.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -1921,28 +1921,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="G8" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
         <v>1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
         <v>5.1</v>
@@ -1957,31 +1957,31 @@
         <v>1.59</v>
       </c>
       <c r="R8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
         <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V8" t="n">
         <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="X8" t="n">
         <v>28</v>
       </c>
       <c r="Y8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -1999,13 +1999,13 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AG8" t="n">
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
@@ -2023,7 +2023,7 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2035,10 +2035,10 @@
         <v>20</v>
       </c>
       <c r="AR8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS8" t="n">
         <v>8</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AT8" t="n">
         <v>9.800000000000001</v>
@@ -2047,25 +2047,25 @@
         <v>9.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC8" t="n">
         <v>13</v>
@@ -2074,17 +2074,17 @@
         <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -2115,64 +2115,64 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="G9" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I9" t="n">
         <v>6.2</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="U9" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V9" t="n">
         <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="X9" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Y9" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2181,22 +2181,22 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
         <v>970</v>
@@ -2208,77 +2208,77 @@
         <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.04</v>
+        <v>16.5</v>
       </c>
       <c r="AQ9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF9" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BG9" t="n">
-        <v>2.42</v>
+        <v>29</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -2312,64 +2312,64 @@
         <v>3.15</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H10" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I10" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J10" t="n">
         <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X10" t="n">
         <v>12</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2396,7 +2396,7 @@
         <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="AU10" t="n">
         <v>4.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.72</v>
+        <v>3.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.41</v>
       </c>
       <c r="G11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H11" t="n">
         <v>7.6</v>
@@ -2533,7 +2533,7 @@
         <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
         <v>1.62</v>
@@ -2554,7 +2554,7 @@
         <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X11" t="n">
         <v>24</v>
@@ -2614,13 +2614,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="AT11" t="n">
         <v>7.8</v>
@@ -2629,13 +2629,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW11" t="n">
         <v>5.3</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AY11" t="n">
         <v>8</v>
@@ -2653,7 +2653,7 @@
         <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE11" t="n">
         <v>5.3</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
         <v>5.6</v>
@@ -2739,7 +2739,7 @@
         <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="U12" t="n">
         <v>1.48</v>
@@ -2775,7 +2775,7 @@
         <v>160</v>
       </c>
       <c r="AF12" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
         <v>16.5</v>
@@ -2808,13 +2808,13 @@
         <v>5.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
         <v>27</v>
       </c>
       <c r="AS12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT12" t="n">
         <v>4.8</v>
@@ -2823,10 +2823,10 @@
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX12" t="n">
         <v>9.800000000000001</v>
@@ -2835,32 +2835,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="BA12" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB12" t="n">
         <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.4</v>
+        <v>27</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF12" t="n">
         <v>34</v>
       </c>
       <c r="BG12" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -2897,16 +2897,16 @@
         <v>5.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="I13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J13" t="n">
         <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.39</v>
@@ -2930,7 +2930,7 @@
         <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T13" t="n">
         <v>1.84</v>
@@ -2939,7 +2939,7 @@
         <v>1.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W13" t="n">
         <v>1.22</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -3091,13 +3091,13 @@
         <v>1.92</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
         <v>4.1</v>
@@ -3115,10 +3115,10 @@
         <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
         <v>1.34</v>
@@ -3133,7 +3133,7 @@
         <v>1.99</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
         <v>2.08</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -3279,58 +3279,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="G15" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="H15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="X15" t="n">
         <v>26</v>
@@ -3339,7 +3339,7 @@
         <v>29</v>
       </c>
       <c r="Z15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA15" t="n">
         <v>180</v>
@@ -3351,10 +3351,10 @@
         <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AE15" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AF15" t="n">
         <v>11.5</v>
@@ -3366,7 +3366,7 @@
         <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="n">
         <v>970</v>
@@ -3384,31 +3384,31 @@
         <v>6.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AR15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS15" t="n">
         <v>8</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AT15" t="n">
         <v>9.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX15" t="n">
         <v>9.4</v>
@@ -3417,32 +3417,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BC15" t="n">
         <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF15" t="n">
         <v>5.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>1.15</v>
       </c>
       <c r="G16" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="H16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="K16" t="n">
         <v>11.5</v>
@@ -3503,13 +3503,13 @@
         <v>1.11</v>
       </c>
       <c r="P16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q16" t="n">
         <v>1.32</v>
       </c>
       <c r="R16" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>1.81</v>
@@ -3524,7 +3524,7 @@
         <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="X16" t="n">
         <v>60</v>
@@ -3539,7 +3539,7 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AC16" t="n">
         <v>26</v>
@@ -3575,22 +3575,22 @@
         <v>200</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AO16" t="n">
         <v>320</v>
       </c>
       <c r="AP16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
         <v>20</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX16" t="n">
         <v>8.4</v>
@@ -3611,10 +3611,10 @@
         <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB16" t="n">
         <v>8.199999999999999</v>
@@ -3623,20 +3623,20 @@
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BG16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -3667,70 +3667,70 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I17" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.27</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T17" t="n">
         <v>1.6</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.58</v>
-      </c>
       <c r="U17" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="W17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
         <v>970</v>
       </c>
       <c r="Z17" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AA17" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AB17" t="n">
         <v>970</v>
@@ -3739,28 +3739,28 @@
         <v>970</v>
       </c>
       <c r="AD17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG17" t="n">
         <v>970</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>18</v>
       </c>
       <c r="AH17" t="n">
         <v>970</v>
       </c>
       <c r="AI17" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AJ17" t="n">
         <v>70</v>
       </c>
       <c r="AK17" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL17" t="n">
         <v>42</v>
@@ -3772,65 +3772,65 @@
         <v>29</v>
       </c>
       <c r="AO17" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AP17" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS17" t="n">
         <v>19</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
         <v>5.6</v>
       </c>
       <c r="AW17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX17" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX17" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AY17" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AZ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG17" t="n">
         <v>5.9</v>
       </c>
-      <c r="BA17" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -3861,67 +3861,67 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="H18" t="n">
         <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="J18" t="n">
         <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M18" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="P18" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W18" t="n">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="X18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y18" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
@@ -3930,10 +3930,10 @@
         <v>6</v>
       </c>
       <c r="AC18" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
@@ -3945,86 +3945,86 @@
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="n">
         <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.84</v>
+        <v>4.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AV18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB18" t="n">
         <v>4.8</v>
       </c>
-      <c r="AW18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ18" t="n">
+      <c r="BC18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF18" t="n">
         <v>4.8</v>
       </c>
-      <c r="BA18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4</v>
-      </c>
       <c r="BG18" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
         <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>1.46</v>
@@ -4085,7 +4085,7 @@
         <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q19" t="n">
         <v>2.1</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>2.42</v>
       </c>
       <c r="G20" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I20" t="n">
         <v>2.86</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.88</v>
       </c>
       <c r="J20" t="n">
         <v>4.1</v>
@@ -4276,31 +4276,31 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R20" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T20" t="n">
         <v>1.4</v>
       </c>
       <c r="U20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="V20" t="n">
         <v>1.53</v>
       </c>
       <c r="W20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X20" t="n">
         <v>36</v>
@@ -4309,13 +4309,13 @@
         <v>25</v>
       </c>
       <c r="Z20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA20" t="n">
         <v>48</v>
       </c>
       <c r="AB20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC20" t="n">
         <v>11</v>
@@ -4324,10 +4324,10 @@
         <v>14</v>
       </c>
       <c r="AE20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
@@ -4336,22 +4336,22 @@
         <v>12.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ20" t="n">
         <v>36</v>
       </c>
       <c r="AK20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="n">
         <v>23</v>
       </c>
       <c r="AM20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AN20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO20" t="n">
         <v>12</v>
@@ -4366,16 +4366,16 @@
         <v>27</v>
       </c>
       <c r="AS20" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU20" t="n">
         <v>10.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW20" t="n">
         <v>23</v>
@@ -4405,14 +4405,14 @@
         <v>32</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG20" t="n">
         <v>11</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>
@@ -4449,40 +4449,40 @@
         <v>2.3</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I21" t="n">
         <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="K21" t="n">
         <v>4.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P21" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>2.96</v>
+        <v>2.44</v>
       </c>
       <c r="T21" t="n">
         <v>1.71</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-27 16:38:34</t>
+          <t>2026-04-27 18:47:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,46 +757,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="G2" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P2" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T2" t="n">
         <v>2.36</v>
@@ -805,122 +805,122 @@
         <v>1.68</v>
       </c>
       <c r="V2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="X2" t="n">
         <v>9</v>
       </c>
       <c r="Y2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AB2" t="n">
         <v>5.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>30</v>
       </c>
       <c r="AE2" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
         <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="n">
         <v>380</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AP2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX2" t="n">
         <v>8</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7.8</v>
       </c>
       <c r="AY2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -954,16 +954,16 @@
         <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="n">
         <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.35</v>
@@ -975,16 +975,16 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
         <v>1.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
@@ -1002,7 +1002,7 @@
         <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1059,7 +1059,7 @@
         <v>130</v>
       </c>
       <c r="AP3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ3" t="n">
         <v>5.9</v>
@@ -1080,7 +1080,7 @@
         <v>6.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="AX3" t="n">
         <v>5.4</v>
@@ -1101,20 +1101,20 @@
         <v>7.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BF3" t="n">
         <v>7</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I4" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="J4" t="n">
         <v>3.2</v>
@@ -1169,43 +1169,43 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R4" t="n">
         <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W4" t="n">
         <v>1.43</v>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y4" t="n">
         <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
@@ -1262,7 +1262,7 @@
         <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT4" t="n">
         <v>9.6</v>
@@ -1274,7 +1274,7 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
         <v>14.5</v>
@@ -1286,29 +1286,29 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC4" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6.4</v>
       </c>
       <c r="BD4" t="n">
         <v>36</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
         <v>3.95</v>
@@ -1384,13 +1384,13 @@
         <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V5" t="n">
         <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
@@ -1402,13 +1402,13 @@
         <v>36</v>
       </c>
       <c r="AA5" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>140</v>
       </c>
       <c r="AD5" t="n">
         <v>20</v>
@@ -1426,7 +1426,7 @@
         <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ5" t="n">
         <v>22</v>
@@ -1474,7 +1474,7 @@
         <v>6.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>6.4</v>
@@ -1483,26 +1483,26 @@
         <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
         <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G6" t="n">
         <v>2.18</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
         <v>3.4</v>
@@ -1557,13 +1557,13 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
         <v>1.92</v>
@@ -1578,10 +1578,10 @@
         <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
         <v>1.84</v>
@@ -1641,46 +1641,46 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.8</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
         <v>4.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.05</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
         <v>4</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.35</v>
+        <v>9.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.6</v>
+        <v>13.5</v>
       </c>
       <c r="BA6" t="n">
         <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.75</v>
+        <v>18</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.7</v>
+        <v>16</v>
       </c>
       <c r="BD6" t="n">
         <v>3.9</v>
@@ -1689,14 +1689,14 @@
         <v>4.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG6" t="n">
         <v>4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
         <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
@@ -1745,13 +1745,13 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.21</v>
@@ -1769,13 +1769,13 @@
         <v>2.54</v>
       </c>
       <c r="T7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
         <v>1.53</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G8" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I8" t="n">
         <v>6.2</v>
@@ -1951,34 +1951,34 @@
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
         <v>1.59</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
         <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
         <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="X8" t="n">
         <v>28</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z8" t="n">
         <v>55</v>
@@ -1993,13 +1993,13 @@
         <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG8" t="n">
         <v>10</v>
@@ -2035,10 +2035,10 @@
         <v>20</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
         <v>9.800000000000001</v>
@@ -2047,10 +2047,10 @@
         <v>9.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX8" t="n">
         <v>9.800000000000001</v>
@@ -2062,7 +2062,7 @@
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8" t="n">
         <v>13</v>
@@ -2074,17 +2074,17 @@
         <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8" t="n">
         <v>6.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="H9" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
         <v>1.25</v>
@@ -2139,40 +2139,40 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.6</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.61</v>
-      </c>
       <c r="S9" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="T9" t="n">
         <v>1.67</v>
       </c>
       <c r="U9" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V9" t="n">
         <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="X9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2184,19 +2184,19 @@
         <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>970</v>
@@ -2208,10 +2208,10 @@
         <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2223,13 +2223,13 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
         <v>17.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS9" t="n">
         <v>42</v>
@@ -2238,7 +2238,7 @@
         <v>10.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV9" t="n">
         <v>15.5</v>
@@ -2247,13 +2247,13 @@
         <v>30</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
         <v>29</v>
@@ -2262,7 +2262,7 @@
         <v>13</v>
       </c>
       <c r="BC9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD9" t="n">
         <v>19</v>
@@ -2271,14 +2271,14 @@
         <v>32</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG9" t="n">
         <v>29</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
         <v>1.71</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="R10" t="n">
         <v>1.26</v>
@@ -2363,13 +2363,13 @@
         <v>1.42</v>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2396,7 +2396,7 @@
         <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="AQ10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AT10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.5</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.55</v>
+        <v>6.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.9</v>
+        <v>2.52</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.85</v>
+        <v>2.48</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.9</v>
+        <v>2.52</v>
       </c>
       <c r="BE10" t="n">
-        <v>4</v>
+        <v>2.18</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G11" t="n">
         <v>1.45</v>
@@ -2518,10 +2518,10 @@
         <v>4.9</v>
       </c>
       <c r="K11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
         <v>1.04</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
         <v>5.6</v>
@@ -2712,7 +2712,7 @@
         <v>2.7</v>
       </c>
       <c r="K12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.75</v>
@@ -2730,7 +2730,7 @@
         <v>1.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
         <v>1.12</v>
@@ -2739,82 +2739,82 @@
         <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="U12" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="X12" t="n">
         <v>7</v>
       </c>
       <c r="Y12" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA12" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AE12" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AG12" t="n">
         <v>16.5</v>
       </c>
       <c r="AH12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>40</v>
       </c>
-      <c r="AI12" t="n">
-        <v>220</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>34</v>
-      </c>
       <c r="AK12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL12" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AM12" t="n">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="AN12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO12" t="n">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="AP12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS12" t="n">
         <v>5.2</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>6.2</v>
       </c>
       <c r="AT12" t="n">
         <v>4.8</v>
@@ -2823,13 +2823,13 @@
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.2</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY12" t="n">
         <v>11.5</v>
@@ -2838,29 +2838,29 @@
         <v>30</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>27</v>
+        <v>4.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -2891,67 +2891,67 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="G13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="I13" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
         <v>1.36</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U13" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="W13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
         <v>25</v>
@@ -2960,16 +2960,16 @@
         <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF13" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>7</v>
       </c>
       <c r="AR13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS13" t="n">
         <v>5.4</v>
       </c>
-      <c r="AS13" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AT13" t="n">
-        <v>5.8</v>
+        <v>15.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AV13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX13" t="n">
         <v>6</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AY13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB13" t="n">
         <v>6.8</v>
       </c>
-      <c r="AY13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BC13" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>5.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
         <v>4.1</v>
@@ -3115,7 +3115,7 @@
         <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
         <v>1.92</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G15" t="n">
         <v>1.55</v>
@@ -3291,7 +3291,7 @@
         <v>7.8</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K15" t="n">
         <v>5.4</v>
@@ -3309,7 +3309,7 @@
         <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q15" t="n">
         <v>1.56</v>
@@ -3318,13 +3318,13 @@
         <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T15" t="n">
         <v>1.74</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
         <v>1.15</v>
@@ -3345,7 +3345,7 @@
         <v>180</v>
       </c>
       <c r="AB15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC15" t="n">
         <v>12</v>
@@ -3357,10 +3357,10 @@
         <v>100</v>
       </c>
       <c r="AF15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
         <v>21</v>
@@ -3372,7 +3372,7 @@
         <v>970</v>
       </c>
       <c r="AK15" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AL15" t="n">
         <v>30</v>
@@ -3381,34 +3381,34 @@
         <v>100</v>
       </c>
       <c r="AN15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO15" t="n">
         <v>85</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT15" t="n">
         <v>9.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX15" t="n">
         <v>9.4</v>
@@ -3417,32 +3417,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC15" t="n">
         <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF15" t="n">
         <v>5.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
         <v>10.5</v>
       </c>
       <c r="K16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
         <v>1.16</v>
@@ -3542,7 +3542,7 @@
         <v>14.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AD16" t="n">
         <v>85</v>
@@ -3557,7 +3557,7 @@
         <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AI16" t="n">
         <v>210</v>
@@ -3581,28 +3581,28 @@
         <v>320</v>
       </c>
       <c r="AP16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR16" t="n">
         <v>9</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AS16" t="n">
         <v>9.4</v>
       </c>
-      <c r="AR16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AT16" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AU16" t="n">
         <v>20</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>8.4</v>
@@ -3611,10 +3611,10 @@
         <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB16" t="n">
         <v>8.199999999999999</v>
@@ -3623,20 +3623,20 @@
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BF16" t="n">
         <v>2.54</v>
       </c>
       <c r="BG16" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -3670,16 +3670,16 @@
         <v>3.35</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H17" t="n">
         <v>2.08</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
@@ -3691,10 +3691,10 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
         <v>2.26</v>
@@ -3703,22 +3703,22 @@
         <v>1.65</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U17" t="n">
         <v>2.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X17" t="n">
         <v>22</v>
@@ -3772,16 +3772,16 @@
         <v>29</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR17" t="n">
         <v>5.9</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>5.7</v>
       </c>
       <c r="AS17" t="n">
         <v>19</v>
@@ -3793,25 +3793,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AZ17" t="n">
         <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC17" t="n">
         <v>6.8</v>
@@ -3820,17 +3820,17 @@
         <v>7</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -3864,13 +3864,13 @@
         <v>1.62</v>
       </c>
       <c r="G18" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H18" t="n">
         <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J18" t="n">
         <v>3.35</v>
@@ -3891,7 +3891,7 @@
         <v>1.54</v>
       </c>
       <c r="P18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q18" t="n">
         <v>2.46</v>
@@ -3900,7 +3900,7 @@
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="T18" t="n">
         <v>2.46</v>
@@ -3909,10 +3909,10 @@
         <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W18" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X18" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AQ18" t="n">
         <v>14.5</v>
@@ -3984,7 +3984,7 @@
         <v>4.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AV18" t="n">
         <v>5.5</v>
@@ -3996,7 +3996,7 @@
         <v>6.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ18" t="n">
         <v>5.4</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>3.05</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J19" t="n">
         <v>3.5</v>
@@ -4079,19 +4079,19 @@
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O19" t="n">
         <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
         <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
         <v>3.9</v>
@@ -4103,7 +4103,7 @@
         <v>1.94</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
         <v>1.67</v>
@@ -4112,13 +4112,13 @@
         <v>15.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
         <v>27</v>
       </c>
       <c r="AA19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB19" t="n">
         <v>11</v>
@@ -4142,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ19" t="n">
         <v>40</v>
@@ -4169,10 +4169,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT19" t="n">
         <v>6.6</v>
@@ -4184,7 +4184,7 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -4196,29 +4196,29 @@
         <v>15</v>
       </c>
       <c r="BA19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB19" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB19" t="n">
-        <v>4</v>
-      </c>
       <c r="BC19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF19" t="n">
         <v>4.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>2.46</v>
       </c>
       <c r="H20" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I20" t="n">
         <v>2.86</v>
@@ -4264,43 +4264,43 @@
         <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L20" t="n">
         <v>1.23</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="V20" t="n">
         <v>1.53</v>
       </c>
       <c r="W20" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X20" t="n">
         <v>36</v>
@@ -4315,7 +4315,7 @@
         <v>48</v>
       </c>
       <c r="AB20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC20" t="n">
         <v>11</v>
@@ -4327,7 +4327,7 @@
         <v>24</v>
       </c>
       <c r="AF20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
@@ -4339,7 +4339,7 @@
         <v>25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK20" t="n">
         <v>20</v>
@@ -4348,16 +4348,16 @@
         <v>23</v>
       </c>
       <c r="AM20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AN20" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO20" t="n">
         <v>12</v>
       </c>
       <c r="AP20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ20" t="n">
         <v>23</v>
@@ -4375,7 +4375,7 @@
         <v>10.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
         <v>23</v>
@@ -4393,7 +4393,7 @@
         <v>24</v>
       </c>
       <c r="BB20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC20" t="n">
         <v>19.5</v>
@@ -4402,17 +4402,17 @@
         <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG20" t="n">
         <v>11</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H21" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="I21" t="n">
         <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="K21" t="n">
         <v>4.1</v>
@@ -4467,7 +4467,7 @@
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>1.26</v>
@@ -4476,16 +4476,16 @@
         <v>1.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
         <v>2.44</v>
       </c>
       <c r="T21" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="U21" t="n">
         <v>2.1</v>
@@ -4494,7 +4494,7 @@
         <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X21" t="n">
         <v>18</v>
@@ -4521,7 +4521,7 @@
         <v>55</v>
       </c>
       <c r="AF21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG21" t="n">
         <v>12.5</v>
@@ -4533,7 +4533,7 @@
         <v>60</v>
       </c>
       <c r="AJ21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK21" t="n">
         <v>26</v>
@@ -4545,68 +4545,68 @@
         <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO21" t="n">
         <v>50</v>
       </c>
       <c r="AP21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX21" t="n">
         <v>4</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR21" t="n">
+      <c r="AY21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC21" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ21" t="n">
+      <c r="BD21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF21" t="n">
         <v>4.1</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BG21" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-27 18:47:03</t>
+          <t>2026-04-27 20:54:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="G2" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="H2" t="n">
         <v>6.2</v>
@@ -769,10 +769,10 @@
         <v>7.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.46</v>
@@ -787,19 +787,19 @@
         <v>1.57</v>
       </c>
       <c r="P2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
         <v>1.68</v>
@@ -808,10 +808,10 @@
         <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y2" t="n">
         <v>15.5</v>
@@ -820,7 +820,7 @@
         <v>55</v>
       </c>
       <c r="AA2" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
         <v>5.7</v>
@@ -832,13 +832,13 @@
         <v>30</v>
       </c>
       <c r="AE2" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
         <v>8.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>34</v>
@@ -847,7 +847,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AK2" t="n">
         <v>25</v>
@@ -859,68 +859,68 @@
         <v>380</v>
       </c>
       <c r="AN2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO2" t="n">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="AS2" t="n">
         <v>13</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU2" t="n">
         <v>7.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BB2" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BE2" t="n">
         <v>13</v>
       </c>
       <c r="BF2" t="n">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="BG2" t="n">
         <v>13</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
         <v>5</v>
@@ -990,10 +990,10 @@
         <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
         <v>1.75</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
         <v>8</v>
@@ -1059,16 +1059,16 @@
         <v>130</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>5.9</v>
@@ -1080,41 +1080,41 @@
         <v>6.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF3" t="n">
         <v>7.2</v>
       </c>
-      <c r="BD3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7</v>
-      </c>
       <c r="BG3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I4" t="n">
         <v>2.68</v>
@@ -1160,7 +1160,7 @@
         <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
         <v>1.38</v>
@@ -1196,40 +1196,40 @@
         <v>1.59</v>
       </c>
       <c r="W4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB4" t="n">
         <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
         <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1244,7 +1244,7 @@
         <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>34</v>
       </c>
       <c r="AP4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AT4" t="n">
         <v>9.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE4" t="n">
         <v>10</v>
       </c>
-      <c r="AW4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BF4" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>1.84</v>
       </c>
       <c r="G5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>4.5</v>
@@ -1357,7 +1357,7 @@
         <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
@@ -1387,10 +1387,10 @@
         <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
@@ -1408,19 +1408,19 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AD5" t="n">
         <v>20</v>
       </c>
       <c r="AE5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
         <v>18</v>
@@ -1429,7 +1429,7 @@
         <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="n">
         <v>970</v>
@@ -1441,68 +1441,68 @@
         <v>60</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="AO5" t="n">
         <v>29</v>
       </c>
       <c r="AP5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT5" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR5" t="n">
+      <c r="AU5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC5" t="n">
         <v>7.2</v>
       </c>
-      <c r="AS5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6</v>
-      </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>3.45</v>
       </c>
       <c r="BF5" t="n">
         <v>6.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.97</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H6" t="n">
         <v>3.55</v>
@@ -1545,7 +1545,7 @@
         <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
         <v>3.95</v>
@@ -1584,7 +1584,7 @@
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X6" t="n">
         <v>18</v>
@@ -1677,7 +1677,7 @@
         <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>18</v>
+        <v>3.75</v>
       </c>
       <c r="BC6" t="n">
         <v>16</v>
@@ -1689,14 +1689,14 @@
         <v>4.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="BG6" t="n">
         <v>4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G7" t="n">
         <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
@@ -1868,7 +1868,7 @@
         <v>11</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB7" t="n">
         <v>6.8</v>
@@ -1877,7 +1877,7 @@
         <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
         <v>7.2</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
         <v>1.72</v>
       </c>
       <c r="U8" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V8" t="n">
         <v>1.19</v>
@@ -2044,7 +2044,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV8" t="n">
         <v>17.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="G9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.25</v>
@@ -2145,10 +2145,10 @@
         <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R9" t="n">
         <v>1.6</v>
@@ -2166,7 +2166,7 @@
         <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="X9" t="n">
         <v>32</v>
@@ -2208,7 +2208,7 @@
         <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
         <v>46</v>
@@ -2217,16 +2217,16 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR9" t="n">
         <v>27</v>
@@ -2235,50 +2235,50 @@
         <v>42</v>
       </c>
       <c r="AT9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
         <v>15.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB9" t="n">
         <v>13</v>
       </c>
       <c r="BC9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE9" t="n">
         <v>32</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG9" t="n">
         <v>29</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -2318,10 +2318,10 @@
         <v>2.54</v>
       </c>
       <c r="I10" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
         <v>3.35</v>
@@ -2339,13 +2339,13 @@
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
         <v>4.4</v>
@@ -2417,7 +2417,7 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AQ10" t="n">
         <v>8.199999999999999</v>
@@ -2435,7 +2435,7 @@
         <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AW10" t="n">
         <v>3.05</v>
@@ -2447,32 +2447,32 @@
         <v>5.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA10" t="n">
         <v>7.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BE10" t="n">
         <v>2.18</v>
       </c>
       <c r="BF10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG10" t="n">
         <v>3.05</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H11" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I11" t="n">
         <v>9.6</v>
       </c>
       <c r="J11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
         <v>5.7</v>
@@ -2554,7 +2554,7 @@
         <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X11" t="n">
         <v>24</v>
@@ -2614,13 +2614,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="AT11" t="n">
         <v>7.8</v>
@@ -2629,10 +2629,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="AX11" t="n">
         <v>8.4</v>
@@ -2653,20 +2653,20 @@
         <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="BF11" t="n">
         <v>5</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.3</v>
+        <v>3.45</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L12" t="n">
         <v>1.75</v>
@@ -2739,28 +2739,28 @@
         <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
         <v>1.52</v>
       </c>
       <c r="V12" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z12" t="n">
         <v>44</v>
       </c>
       <c r="AA12" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AB12" t="n">
         <v>6.4</v>
@@ -2772,64 +2772,64 @@
         <v>32</v>
       </c>
       <c r="AE12" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF12" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
         <v>16.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AI12" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AJ12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK12" t="n">
         <v>55</v>
       </c>
       <c r="AL12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM12" t="n">
-        <v>560</v>
+        <v>530</v>
       </c>
       <c r="AN12" t="n">
         <v>55</v>
       </c>
       <c r="AO12" t="n">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU12" t="n">
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY12" t="n">
         <v>11.5</v>
@@ -2838,29 +2838,29 @@
         <v>30</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF12" t="n">
         <v>36</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>5.1</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H13" t="n">
         <v>1.9</v>
@@ -2906,13 +2906,13 @@
         <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
         <v>3.4</v>
@@ -2924,16 +2924,16 @@
         <v>1.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="R13" t="n">
         <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U13" t="n">
         <v>2.04</v>
@@ -2945,28 +2945,28 @@
         <v>1.21</v>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AB13" t="n">
         <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF13" t="n">
         <v>44</v>
@@ -2978,7 +2978,7 @@
         <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ13" t="n">
         <v>1000</v>
@@ -3008,10 +3008,10 @@
         <v>9.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU13" t="n">
         <v>6.8</v>
@@ -3020,41 +3020,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.6</v>
+        <v>18.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG13" t="n">
         <v>11.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J14" t="n">
         <v>3.6</v>
@@ -3109,16 +3109,16 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
         <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R14" t="n">
         <v>1.34</v>
@@ -3127,16 +3127,16 @@
         <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X14" t="n">
         <v>17</v>
@@ -3145,7 +3145,7 @@
         <v>20</v>
       </c>
       <c r="Z14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA14" t="n">
         <v>150</v>
@@ -3169,7 +3169,7 @@
         <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
         <v>90</v>
@@ -3193,62 +3193,62 @@
         <v>100</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW14" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4</v>
-      </c>
       <c r="AX14" t="n">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.65</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB14" t="n">
         <v>3.65</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.65</v>
+        <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.35</v>
+        <v>9.6</v>
       </c>
       <c r="BG14" t="n">
         <v>4.1</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -3279,25 +3279,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="G15" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="H15" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
         <v>4.7</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
@@ -3309,7 +3309,7 @@
         <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q15" t="n">
         <v>1.56</v>
@@ -3321,28 +3321,28 @@
         <v>2.42</v>
       </c>
       <c r="T15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U15" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="X15" t="n">
         <v>26</v>
       </c>
       <c r="Y15" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Z15" t="n">
         <v>65</v>
       </c>
       <c r="AA15" t="n">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="AB15" t="n">
         <v>11.5</v>
@@ -3363,16 +3363,16 @@
         <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
         <v>970</v>
       </c>
       <c r="AK15" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AL15" t="n">
         <v>30</v>
@@ -3384,65 +3384,65 @@
         <v>6.2</v>
       </c>
       <c r="AO15" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AP15" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS15" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS15" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AT15" t="n">
-        <v>9.6</v>
+        <v>4.9</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AV15" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BC15" t="n">
         <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -3476,19 +3476,19 @@
         <v>1.15</v>
       </c>
       <c r="G16" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="H16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="I16" t="n">
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.16</v>
@@ -3503,7 +3503,7 @@
         <v>1.11</v>
       </c>
       <c r="P16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q16" t="n">
         <v>1.32</v>
@@ -3524,7 +3524,7 @@
         <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="X16" t="n">
         <v>60</v>
@@ -3578,7 +3578,7 @@
         <v>2.9</v>
       </c>
       <c r="AO16" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AP16" t="n">
         <v>8</v>
@@ -3593,25 +3593,25 @@
         <v>9.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
         <v>8.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX16" t="n">
         <v>8.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BA16" t="n">
         <v>9</v>
@@ -3620,7 +3620,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD16" t="n">
         <v>7.6</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -3673,13 +3673,13 @@
         <v>3.65</v>
       </c>
       <c r="H17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I17" t="n">
         <v>2.24</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
@@ -3697,7 +3697,7 @@
         <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
         <v>1.65</v>
@@ -3736,7 +3736,7 @@
         <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>280</v>
       </c>
       <c r="AD17" t="n">
         <v>13.5</v>
@@ -3745,7 +3745,7 @@
         <v>22</v>
       </c>
       <c r="AF17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG17" t="n">
         <v>970</v>
@@ -3769,7 +3769,7 @@
         <v>65</v>
       </c>
       <c r="AN17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO17" t="n">
         <v>12</v>
@@ -3778,22 +3778,22 @@
         <v>14.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AW17" t="n">
         <v>6.2</v>
@@ -3802,7 +3802,7 @@
         <v>6.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AZ17" t="n">
         <v>13.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
         <v>2.46</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S18" t="n">
         <v>5.1</v>
@@ -3972,7 +3972,7 @@
         <v>3.9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
         <v>5.8</v>
@@ -3987,7 +3987,7 @@
         <v>3.9</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW18" t="n">
         <v>6</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>3.05</v>
       </c>
       <c r="I19" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
         <v>3.5</v>
@@ -4103,7 +4103,7 @@
         <v>1.94</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
         <v>1.67</v>
@@ -4199,7 +4199,7 @@
         <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
         <v>4.1</v>
@@ -4211,14 +4211,14 @@
         <v>4.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG19" t="n">
         <v>4.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H20" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="I20" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="J20" t="n">
         <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.23</v>
@@ -4273,7 +4273,7 @@
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O20" t="n">
         <v>1.13</v>
@@ -4282,7 +4282,7 @@
         <v>3.35</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R20" t="n">
         <v>1.98</v>
@@ -4297,10 +4297,10 @@
         <v>3.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W20" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X20" t="n">
         <v>36</v>
@@ -4312,7 +4312,7 @@
         <v>29</v>
       </c>
       <c r="AA20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB20" t="n">
         <v>23</v>
@@ -4327,7 +4327,7 @@
         <v>24</v>
       </c>
       <c r="AF20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
@@ -4357,7 +4357,7 @@
         <v>12</v>
       </c>
       <c r="AP20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AQ20" t="n">
         <v>23</v>
@@ -4378,7 +4378,7 @@
         <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX20" t="n">
         <v>21</v>
@@ -4393,7 +4393,7 @@
         <v>24</v>
       </c>
       <c r="BB20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC20" t="n">
         <v>19.5</v>
@@ -4405,14 +4405,14 @@
         <v>34</v>
       </c>
       <c r="BF20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG20" t="n">
         <v>11</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>
@@ -4563,10 +4563,10 @@
         <v>5.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AV21" t="n">
         <v>4.1</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-27 20:54:50</t>
+          <t>2026-04-27 23:02:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,46 +757,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="G2" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="P2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T2" t="n">
         <v>2.38</v>
@@ -805,22 +805,22 @@
         <v>1.68</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
         <v>55</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB2" t="n">
         <v>5.7</v>
@@ -829,34 +829,34 @@
         <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF2" t="n">
         <v>8.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
         <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
         <v>24</v>
@@ -868,59 +868,59 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>42</v>
+        <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AU2" t="n">
         <v>7.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="BA2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
         <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="BG2" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -951,46 +951,46 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
         <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T3" t="n">
         <v>2.1</v>
@@ -999,16 +999,16 @@
         <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
         <v>34</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
         <v>8</v>
@@ -1059,16 +1059,16 @@
         <v>130</v>
       </c>
       <c r="AP3" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>5.9</v>
@@ -1077,44 +1077,44 @@
         <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB3" t="n">
         <v>7</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BC3" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD3" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I4" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="J4" t="n">
         <v>3.2</v>
@@ -1163,73 +1163,73 @@
         <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
         <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
         <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1238,7 +1238,7 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
@@ -1250,25 +1250,25 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR4" t="n">
         <v>13.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
@@ -1277,38 +1277,38 @@
         <v>25</v>
       </c>
       <c r="AX4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE4" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BC4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>10</v>
-      </c>
       <c r="BF4" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="BG4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="G5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
         <v>4.5</v>
@@ -1354,31 +1354,31 @@
         <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S5" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
         <v>1.58</v>
@@ -1387,7 +1387,7 @@
         <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
         <v>2.14</v>
@@ -1408,7 +1408,7 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="AD5" t="n">
         <v>20</v>
@@ -1420,10 +1420,10 @@
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI5" t="n">
         <v>42</v>
@@ -1441,34 +1441,34 @@
         <v>60</v>
       </c>
       <c r="AN5" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
         <v>7.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
         <v>7.8</v>
@@ -1480,29 +1480,29 @@
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD5" t="n">
         <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="BF5" t="n">
         <v>6.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -1536,10 +1536,10 @@
         <v>1.97</v>
       </c>
       <c r="G6" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I6" t="n">
         <v>4.5</v>
@@ -1548,31 +1548,31 @@
         <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
         <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
         <v>1.78</v>
@@ -1584,10 +1584,10 @@
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -1602,7 +1602,7 @@
         <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR6" t="n">
-        <v>21</v>
+        <v>3.95</v>
       </c>
       <c r="AS6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW6" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4</v>
-      </c>
       <c r="AX6" t="n">
-        <v>9.4</v>
+        <v>3.45</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.8</v>
+        <v>3.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13.5</v>
+        <v>3.75</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>3.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -1733,10 +1733,10 @@
         <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
@@ -1745,37 +1745,37 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
         <v>1.21</v>
       </c>
       <c r="P7" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
         <v>1.56</v>
       </c>
       <c r="U7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W7" t="n">
         <v>1.53</v>
@@ -1829,7 +1829,7 @@
         <v>65</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>17</v>
@@ -1856,7 +1856,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
         <v>15</v>
@@ -1871,10 +1871,10 @@
         <v>6.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD7" t="n">
         <v>6.8</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
         <v>6.2</v>
@@ -1939,40 +1939,40 @@
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="R8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="T8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U8" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V8" t="n">
         <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="X8" t="n">
         <v>28</v>
@@ -1999,7 +1999,7 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
         <v>10</v>
@@ -2011,7 +2011,7 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK8" t="n">
         <v>16</v>
@@ -2029,19 +2029,19 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="AQ8" t="n">
         <v>20</v>
       </c>
       <c r="AR8" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU8" t="n">
         <v>9.6</v>
@@ -2050,19 +2050,19 @@
         <v>17.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.6</v>
+        <v>24</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8" t="n">
         <v>13</v>
@@ -2074,17 +2074,17 @@
         <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="G9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
         <v>4.1</v>
@@ -2133,46 +2133,46 @@
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
         <v>2.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="T9" t="n">
         <v>1.67</v>
       </c>
       <c r="U9" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W9" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="X9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2187,19 +2187,19 @@
         <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2208,10 +2208,10 @@
         <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2223,13 +2223,13 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS9" t="n">
         <v>42</v>
@@ -2238,47 +2238,47 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BB9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC9" t="n">
         <v>13</v>
       </c>
-      <c r="BC9" t="n">
-        <v>12</v>
-      </c>
       <c r="BD9" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BE9" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG9" t="n">
         <v>29</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         <v>3.15</v>
       </c>
       <c r="G10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I10" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="J10" t="n">
         <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.51</v>
@@ -2336,19 +2336,19 @@
         <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="P10" t="n">
         <v>1.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
         <v>1.89</v>
@@ -2357,10 +2357,10 @@
         <v>1.98</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AQ10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AU10" t="n">
         <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.05</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
         <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE10" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2.18</v>
-      </c>
       <c r="BF10" t="n">
-        <v>7.8</v>
+        <v>2.46</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.05</v>
+        <v>28</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -2506,49 +2506,49 @@
         <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R11" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T11" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="U11" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
         <v>1.11</v>
@@ -2566,7 +2566,7 @@
         <v>90</v>
       </c>
       <c r="AA11" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AB11" t="n">
         <v>10.5</v>
@@ -2575,7 +2575,7 @@
         <v>970</v>
       </c>
       <c r="AD11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AE11" t="n">
         <v>140</v>
@@ -2590,7 +2590,7 @@
         <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ11" t="n">
         <v>970</v>
@@ -2602,25 +2602,25 @@
         <v>34</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO11" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP11" t="n">
-        <v>17.5</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AT11" t="n">
         <v>7.8</v>
@@ -2629,19 +2629,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18</v>
+        <v>7.2</v>
       </c>
       <c r="BA11" t="n">
         <v>5.3</v>
@@ -2650,23 +2650,23 @@
         <v>9.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD11" t="n">
         <v>7.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF11" t="n">
         <v>5</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G12" t="n">
         <v>2.34</v>
@@ -2706,31 +2706,31 @@
         <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J12" t="n">
         <v>2.72</v>
       </c>
       <c r="K12" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="O12" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="P12" t="n">
         <v>1.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R12" t="n">
         <v>1.12</v>
@@ -2739,7 +2739,7 @@
         <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U12" t="n">
         <v>1.52</v>
@@ -2757,7 +2757,7 @@
         <v>10.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AA12" t="n">
         <v>200</v>
@@ -2769,10 +2769,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AE12" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF12" t="n">
         <v>12</v>
@@ -2802,7 +2802,7 @@
         <v>55</v>
       </c>
       <c r="AO12" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AP12" t="n">
         <v>5.1</v>
@@ -2811,10 +2811,10 @@
         <v>8.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT12" t="n">
         <v>4.9</v>
@@ -2826,7 +2826,7 @@
         <v>20</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX12" t="n">
         <v>9.800000000000001</v>
@@ -2835,32 +2835,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>30</v>
+        <v>5.3</v>
       </c>
       <c r="BA12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF12" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>36</v>
-      </c>
       <c r="BG12" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -2891,31 +2891,31 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="G13" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I13" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="J13" t="n">
         <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.36</v>
@@ -2924,25 +2924,25 @@
         <v>1.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R13" t="n">
         <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U13" t="n">
         <v>2.04</v>
       </c>
       <c r="V13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
         <v>14.5</v>
@@ -2951,7 +2951,7 @@
         <v>8.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AA13" t="n">
         <v>22</v>
@@ -2969,7 +2969,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
@@ -3008,7 +3008,7 @@
         <v>9.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AT13" t="n">
         <v>15</v>
@@ -3020,41 +3020,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY13" t="n">
         <v>18.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG13" t="n">
         <v>11.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G14" t="n">
         <v>1.93</v>
@@ -3094,7 +3094,7 @@
         <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J14" t="n">
         <v>3.6</v>
@@ -3103,19 +3103,19 @@
         <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
         <v>1.96</v>
@@ -3124,7 +3124,7 @@
         <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="T14" t="n">
         <v>1.86</v>
@@ -3133,7 +3133,7 @@
         <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
         <v>2.06</v>
@@ -3148,7 +3148,7 @@
         <v>46</v>
       </c>
       <c r="AA14" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB14" t="n">
         <v>10.5</v>
@@ -3160,7 +3160,7 @@
         <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF14" t="n">
         <v>13.5</v>
@@ -3172,7 +3172,7 @@
         <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="n">
         <v>25</v>
@@ -3190,7 +3190,7 @@
         <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP14" t="n">
         <v>3.45</v>
@@ -3199,7 +3199,7 @@
         <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
         <v>4.2</v>
@@ -3217,7 +3217,7 @@
         <v>4.1</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY14" t="n">
         <v>7.6</v>
@@ -3229,13 +3229,13 @@
         <v>4.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BC14" t="n">
         <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
         <v>4.2</v>
@@ -3244,11 +3244,11 @@
         <v>9.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -3279,55 +3279,55 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
         <v>1.52</v>
       </c>
       <c r="H15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N15" t="n">
         <v>5.5</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S15" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
         <v>2.92</v>
@@ -3336,16 +3336,16 @@
         <v>26</v>
       </c>
       <c r="Y15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z15" t="n">
         <v>65</v>
       </c>
       <c r="AA15" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC15" t="n">
         <v>12</v>
@@ -3363,7 +3363,7 @@
         <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
         <v>80</v>
@@ -3381,46 +3381,46 @@
         <v>100</v>
       </c>
       <c r="AN15" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AO15" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.4</v>
+        <v>3.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="AU15" t="n">
         <v>10</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX15" t="n">
-        <v>9</v>
+        <v>5.2</v>
       </c>
       <c r="AY15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
@@ -3429,20 +3429,20 @@
         <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF15" t="n">
         <v>5.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -3473,61 +3473,61 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="G16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H16" t="n">
         <v>19</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="L16" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O16" t="n">
         <v>1.11</v>
       </c>
       <c r="P16" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S16" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="T16" t="n">
         <v>1.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="V16" t="n">
         <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="X16" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Y16" t="n">
         <v>95</v>
@@ -3542,7 +3542,7 @@
         <v>14.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AD16" t="n">
         <v>85</v>
@@ -3551,58 +3551,58 @@
         <v>320</v>
       </c>
       <c r="AF16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AI16" t="n">
         <v>210</v>
       </c>
       <c r="AJ16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
         <v>200</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AO16" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AP16" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AT16" t="n">
         <v>12</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX16" t="n">
         <v>8.4</v>
@@ -3611,32 +3611,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BB16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -3667,67 +3667,67 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G17" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="O17" t="n">
         <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R17" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
         <v>1.61</v>
       </c>
       <c r="U17" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="n">
         <v>970</v>
       </c>
       <c r="Z17" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AA17" t="n">
         <v>32</v>
@@ -3736,10 +3736,10 @@
         <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>280</v>
+        <v>970</v>
       </c>
       <c r="AD17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>22</v>
@@ -3754,10 +3754,10 @@
         <v>970</v>
       </c>
       <c r="AI17" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AJ17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK17" t="n">
         <v>36</v>
@@ -3772,22 +3772,22 @@
         <v>28</v>
       </c>
       <c r="AO17" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AP17" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>5.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU17" t="n">
         <v>8.199999999999999</v>
@@ -3796,41 +3796,41 @@
         <v>5.7</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AZ17" t="n">
         <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC17" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC17" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BD17" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG17" t="n">
         <v>5.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G18" t="n">
         <v>1.72</v>
@@ -3873,40 +3873,40 @@
         <v>9</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O18" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="R18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V18" t="n">
         <v>1.12</v>
@@ -3915,7 +3915,7 @@
         <v>2.4</v>
       </c>
       <c r="X18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y18" t="n">
         <v>19.5</v>
@@ -3933,13 +3933,13 @@
         <v>10</v>
       </c>
       <c r="AD18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
@@ -3957,7 +3957,7 @@
         <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS18" t="n">
         <v>5.8</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>6.2</v>
       </c>
       <c r="AT18" t="n">
         <v>4.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AX18" t="n">
         <v>6.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BA18" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BB18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC18" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC18" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE18" t="n">
         <v>5.8</v>
       </c>
-      <c r="BE18" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BF18" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -4055,61 +4055,61 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G19" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="H19" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J19" t="n">
         <v>3.55</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.5</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P19" t="n">
         <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
         <v>1.94</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="X19" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y19" t="n">
         <v>13</v>
@@ -4121,10 +4121,10 @@
         <v>75</v>
       </c>
       <c r="AB19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
         <v>970</v>
@@ -4133,31 +4133,31 @@
         <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
         <v>65</v>
       </c>
       <c r="AJ19" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
         <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO19" t="n">
         <v>60</v>
@@ -4169,10 +4169,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AT19" t="n">
         <v>6.6</v>
@@ -4184,7 +4184,7 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -4196,29 +4196,29 @@
         <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BB19" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G20" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I20" t="n">
         <v>2.8</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.82</v>
       </c>
       <c r="J20" t="n">
         <v>4.1</v>
@@ -4267,22 +4267,22 @@
         <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.98</v>
@@ -4297,19 +4297,19 @@
         <v>3.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y20" t="n">
         <v>25</v>
       </c>
       <c r="Z20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA20" t="n">
         <v>46</v>
@@ -4321,10 +4321,10 @@
         <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF20" t="n">
         <v>23</v>
@@ -4339,7 +4339,7 @@
         <v>25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK20" t="n">
         <v>20</v>
@@ -4351,10 +4351,10 @@
         <v>36</v>
       </c>
       <c r="AN20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP20" t="n">
         <v>32</v>
@@ -4369,7 +4369,7 @@
         <v>44</v>
       </c>
       <c r="AT20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU20" t="n">
         <v>10.5</v>
@@ -4408,11 +4408,11 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
         <v>1.12</v>
       </c>
       <c r="M21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
         <v>3.1</v>
@@ -4479,7 +4479,7 @@
         <v>1.79</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
         <v>2.44</v>
@@ -4497,116 +4497,116 @@
         <v>1.78</v>
       </c>
       <c r="X21" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-27 23:02:04</t>
+          <t>2026-04-28 01:09:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="G2" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="H2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
         <v>6</v>
       </c>
-      <c r="I2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.6</v>
-      </c>
       <c r="T2" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U2" t="n">
         <v>1.68</v>
       </c>
       <c r="V2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="X2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL2" t="n">
         <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE2" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE2" t="n">
+      <c r="BF2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG2" t="n">
         <v>14.5</v>
       </c>
-      <c r="BF2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -954,61 +954,61 @@
         <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
         <v>34</v>
@@ -1017,16 +1017,16 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AC3" t="n">
         <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AE3" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1035,7 +1035,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AI3" t="n">
         <v>110</v>
@@ -1044,77 +1044,77 @@
         <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AO3" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="AU3" t="n">
         <v>6.6</v>
       </c>
       <c r="AV3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AW3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX3" t="n">
+      <c r="BA3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG3" t="n">
         <v>6</v>
       </c>
-      <c r="AY3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
         <v>3.5</v>
@@ -1154,13 +1154,13 @@
         <v>2.44</v>
       </c>
       <c r="I4" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
         <v>1.47</v>
@@ -1172,34 +1172,34 @@
         <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P4" t="n">
         <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W4" t="n">
         <v>1.4</v>
       </c>
       <c r="X4" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y4" t="n">
         <v>9.6</v>
@@ -1214,13 +1214,13 @@
         <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF4" t="n">
         <v>23</v>
@@ -1238,10 +1238,10 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>130</v>
@@ -1256,16 +1256,16 @@
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
         <v>13.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
         <v>6.6</v>
@@ -1280,25 +1280,25 @@
         <v>18.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BF4" t="n">
         <v>32</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -1339,46 +1339,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
         <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R5" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T5" t="n">
         <v>1.58</v>
@@ -1387,28 +1387,28 @@
         <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="AD5" t="n">
         <v>20</v>
@@ -1420,7 +1420,7 @@
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
         <v>970</v>
@@ -1429,10 +1429,10 @@
         <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK5" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AL5" t="n">
         <v>26</v>
@@ -1444,22 +1444,22 @@
         <v>7.4</v>
       </c>
       <c r="AO5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR5" t="n">
         <v>30</v>
       </c>
-      <c r="AP5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>10</v>
-      </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
         <v>8.199999999999999</v>
@@ -1468,7 +1468,7 @@
         <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX5" t="n">
         <v>7.8</v>
@@ -1480,29 +1480,29 @@
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD5" t="n">
         <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5" t="n">
         <v>6.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1566,13 +1566,13 @@
         <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
         <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
         <v>1.78</v>
@@ -1581,10 +1581,10 @@
         <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
@@ -1599,23 +1599,23 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG6" t="n">
         <v>11</v>
       </c>
-      <c r="AC6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>13</v>
-      </c>
       <c r="AH6" t="n">
         <v>1000</v>
       </c>
@@ -1635,68 +1635,68 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.15</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.05</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G7" t="n">
         <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="I7" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
         <v>1.32</v>
@@ -1754,37 +1754,37 @@
         <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="R7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
         <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z7" t="n">
         <v>21</v>
@@ -1793,7 +1793,7 @@
         <v>40</v>
       </c>
       <c r="AB7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC7" t="n">
         <v>9.800000000000001</v>
@@ -1802,7 +1802,7 @@
         <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF7" t="n">
         <v>22</v>
@@ -1835,46 +1835,46 @@
         <v>17</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW7" t="n">
         <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="BD7" t="n">
         <v>6.8</v>
@@ -1883,14 +1883,14 @@
         <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BG7" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J8" t="n">
         <v>4.5</v>
@@ -1939,49 +1939,49 @@
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S8" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U8" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V8" t="n">
         <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X8" t="n">
         <v>28</v>
       </c>
       <c r="Y8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -1993,7 +1993,7 @@
         <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2005,7 +2005,7 @@
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
@@ -2014,7 +2014,7 @@
         <v>15.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL8" t="n">
         <v>32</v>
@@ -2023,7 +2023,7 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2032,37 +2032,37 @@
         <v>8.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AS8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW8" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>24</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB8" t="n">
         <v>13</v>
@@ -2077,14 +2077,14 @@
         <v>9</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.69</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.74</v>
-      </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.31</v>
@@ -2145,34 +2145,34 @@
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R9" t="n">
         <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U9" t="n">
         <v>2.34</v>
       </c>
       <c r="V9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2181,25 +2181,25 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG9" t="n">
         <v>10</v>
       </c>
-      <c r="AD9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2208,77 +2208,77 @@
         <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>630</v>
       </c>
       <c r="AP9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>17.5</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>19</v>
-      </c>
       <c r="AR9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AS9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
         <v>38</v>
       </c>
       <c r="BB9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC9" t="n">
         <v>14</v>
       </c>
-      <c r="BC9" t="n">
-        <v>13</v>
-      </c>
       <c r="BD9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE9" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BF9" t="n">
         <v>6.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -2309,52 +2309,52 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
         <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I10" t="n">
         <v>2.64</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L10" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U10" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
         <v>1.6</v>
@@ -2363,13 +2363,13 @@
         <v>1.41</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
         <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2387,7 +2387,7 @@
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AW10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BA10" t="n">
-        <v>2.46</v>
+        <v>8.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BE10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BG10" t="n">
         <v>7.8</v>
       </c>
-      <c r="BF10" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>28</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -2503,88 +2503,88 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K11" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P11" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="S11" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Y11" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD11" t="n">
         <v>32</v>
       </c>
-      <c r="Z11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>300</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AE11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>970</v>
-      </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>24</v>
@@ -2593,80 +2593,80 @@
         <v>110</v>
       </c>
       <c r="AJ11" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AK11" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AL11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY11" t="n">
         <v>6.2</v>
       </c>
-      <c r="AO11" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BC11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -2700,31 +2700,31 @@
         <v>2.18</v>
       </c>
       <c r="G12" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
         <v>5.4</v>
       </c>
       <c r="J12" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="K12" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="L12" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="M12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="N12" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="O12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="P12" t="n">
         <v>1.32</v>
@@ -2733,13 +2733,13 @@
         <v>3.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="U12" t="n">
         <v>1.52</v>
@@ -2748,10 +2748,10 @@
         <v>1.23</v>
       </c>
       <c r="W12" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="X12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y12" t="n">
         <v>10.5</v>
@@ -2760,7 +2760,7 @@
         <v>36</v>
       </c>
       <c r="AA12" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB12" t="n">
         <v>6.4</v>
@@ -2769,7 +2769,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AE12" t="n">
         <v>150</v>
@@ -2781,13 +2781,13 @@
         <v>16.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI12" t="n">
         <v>230</v>
       </c>
       <c r="AJ12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
         <v>55</v>
@@ -2805,62 +2805,62 @@
         <v>320</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="AW12" t="n">
         <v>5.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.3</v>
+        <v>30</v>
       </c>
       <c r="BA12" t="n">
         <v>5.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.4</v>
+        <v>36</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="BG12" t="n">
         <v>5.9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -2894,28 +2894,28 @@
         <v>4.8</v>
       </c>
       <c r="G13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="I13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
         <v>3.55</v>
       </c>
       <c r="L13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O13" t="n">
         <v>1.36</v>
@@ -2924,25 +2924,25 @@
         <v>1.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R13" t="n">
         <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U13" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X13" t="n">
         <v>14.5</v>
@@ -2960,7 +2960,7 @@
         <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
         <v>11</v>
@@ -2969,13 +2969,13 @@
         <v>21</v>
       </c>
       <c r="AF13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
         <v>40</v>
@@ -2996,22 +2996,22 @@
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP13" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR13" t="n">
         <v>9.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="AU13" t="n">
         <v>6.8</v>
@@ -3023,38 +3023,38 @@
         <v>6.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD13" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BE13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF13" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>8.4</v>
       </c>
       <c r="BG13" t="n">
         <v>11.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>1.82</v>
       </c>
       <c r="G14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
         <v>5.8</v>
@@ -3100,10 +3100,10 @@
         <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -3112,73 +3112,73 @@
         <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="R14" t="n">
         <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AA14" t="n">
         <v>140</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
         <v>85</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="n">
         <v>46</v>
@@ -3187,68 +3187,68 @@
         <v>140</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO14" t="n">
         <v>95</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT14" t="n">
         <v>6.4</v>
       </c>
       <c r="AU14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD14" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4</v>
-      </c>
       <c r="BE14" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
         <v>7.6</v>
@@ -3294,46 +3294,46 @@
         <v>4.9</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="T15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U15" t="n">
         <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
         <v>2.92</v>
       </c>
       <c r="X15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Y15" t="n">
         <v>32</v>
@@ -3342,10 +3342,10 @@
         <v>65</v>
       </c>
       <c r="AA15" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AB15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC15" t="n">
         <v>12</v>
@@ -3354,22 +3354,22 @@
         <v>32</v>
       </c>
       <c r="AE15" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG15" t="n">
         <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ15" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AK15" t="n">
         <v>970</v>
@@ -3378,71 +3378,71 @@
         <v>30</v>
       </c>
       <c r="AM15" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AO15" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS15" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS15" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AT15" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU15" t="n">
         <v>10</v>
       </c>
       <c r="AV15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BB15" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BC15" t="n">
         <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF15" t="n">
         <v>5.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G16" t="n">
         <v>1.16</v>
       </c>
-      <c r="G16" t="n">
-        <v>1.17</v>
-      </c>
       <c r="H16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I16" t="n">
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
         <v>1.2</v>
@@ -3497,34 +3497,34 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O16" t="n">
         <v>1.11</v>
       </c>
       <c r="P16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="T16" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V16" t="n">
         <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="X16" t="n">
         <v>70</v>
@@ -3539,58 +3539,58 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC16" t="n">
         <v>26</v>
       </c>
       <c r="AD16" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AE16" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="AF16" t="n">
         <v>10</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AI16" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AJ16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AK16" t="n">
         <v>13.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="n">
         <v>2.88</v>
       </c>
       <c r="AO16" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="AP16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AS16" t="n">
         <v>11</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>12.5</v>
       </c>
       <c r="AT16" t="n">
         <v>12</v>
@@ -3602,7 +3602,7 @@
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AX16" t="n">
         <v>8.4</v>
@@ -3611,32 +3611,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD16" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="BE16" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
         <v>2.56</v>
       </c>
       <c r="BG16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -3670,10 +3670,10 @@
         <v>3.4</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I17" t="n">
         <v>2.2</v>
@@ -3682,52 +3682,52 @@
         <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="T17" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="V17" t="n">
         <v>1.83</v>
       </c>
       <c r="W17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z17" t="n">
         <v>970</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>18.5</v>
       </c>
       <c r="AA17" t="n">
         <v>32</v>
@@ -3736,101 +3736,101 @@
         <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AF17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AJ17" t="n">
         <v>65</v>
       </c>
       <c r="AK17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN17" t="n">
         <v>36</v>
       </c>
-      <c r="AL17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>28</v>
-      </c>
       <c r="AO17" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AP17" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT17" t="n">
         <v>6.4</v>
       </c>
-      <c r="AS17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT17" t="n">
+      <c r="AU17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY17" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AZ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE17" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AV17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD17" t="n">
+      <c r="BF17" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG17" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -3861,40 +3861,40 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G18" t="n">
         <v>1.64</v>
       </c>
-      <c r="G18" t="n">
-        <v>1.72</v>
-      </c>
       <c r="H18" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M18" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="O18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
@@ -3903,25 +3903,25 @@
         <v>5.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V18" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="X18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
@@ -3933,25 +3933,25 @@
         <v>10</v>
       </c>
       <c r="AD18" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AK18" t="n">
         <v>27</v>
@@ -3963,68 +3963,68 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="AY18" t="n">
         <v>4.1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BA18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD18" t="n">
         <v>5.7</v>
       </c>
-      <c r="BB18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BE18" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -4085,16 +4085,16 @@
         <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R19" t="n">
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
         <v>1.9</v>
@@ -4106,7 +4106,7 @@
         <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X19" t="n">
         <v>14.5</v>
@@ -4121,7 +4121,7 @@
         <v>75</v>
       </c>
       <c r="AB19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
         <v>9.4</v>
@@ -4169,10 +4169,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS19" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>5</v>
       </c>
       <c r="AT19" t="n">
         <v>6.6</v>
@@ -4184,7 +4184,7 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -4196,29 +4196,29 @@
         <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BB19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD19" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BE19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG19" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H20" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J20" t="n">
         <v>4.1</v>
@@ -4267,55 +4267,55 @@
         <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T20" t="n">
         <v>1.4</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.39</v>
-      </c>
       <c r="U20" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="V20" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W20" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA20" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC20" t="n">
         <v>11</v>
@@ -4351,28 +4351,28 @@
         <v>36</v>
       </c>
       <c r="AN20" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP20" t="n">
         <v>32</v>
       </c>
       <c r="AQ20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV20" t="n">
         <v>13</v>
@@ -4399,20 +4399,20 @@
         <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE20" t="n">
         <v>34</v>
       </c>
       <c r="BF20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -4461,31 +4461,31 @@
         <v>4.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="T21" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
         <v>2.1</v>
@@ -4497,116 +4497,116 @@
         <v>1.78</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
         <v>1.95</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.6</v>
@@ -781,25 +781,25 @@
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
         <v>1.68</v>
@@ -811,16 +811,16 @@
         <v>2.04</v>
       </c>
       <c r="X2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
         <v>6</v>
@@ -829,7 +829,7 @@
         <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
         <v>160</v>
@@ -856,28 +856,28 @@
         <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN2" t="n">
         <v>25</v>
       </c>
       <c r="AO2" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AP2" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU2" t="n">
         <v>7.4</v>
@@ -895,10 +895,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA2" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
@@ -910,7 +910,7 @@
         <v>50</v>
       </c>
       <c r="BE2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF2" t="n">
         <v>21</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -957,85 +957,85 @@
         <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
         <v>1.59</v>
       </c>
       <c r="M3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T3" t="n">
         <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
         <v>1.9</v>
       </c>
       <c r="X3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Y3" t="n">
         <v>18</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
         <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE3" t="n">
         <v>95</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>95</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AI3" t="n">
         <v>110</v>
@@ -1044,7 +1044,7 @@
         <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL3" t="n">
         <v>65</v>
@@ -1053,68 +1053,68 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AO3" t="n">
         <v>150</v>
       </c>
       <c r="AP3" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AQ3" t="n">
         <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT3" t="n">
         <v>6</v>
       </c>
-      <c r="AT3" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AX3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>8.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB3" t="n">
         <v>9.4</v>
       </c>
-      <c r="BB3" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BC3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BF3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG3" t="n">
         <v>8.6</v>
       </c>
-      <c r="BE3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>6</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
         <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
         <v>1.29</v>
@@ -1187,7 +1187,7 @@
         <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
         <v>2.02</v>
@@ -1208,7 +1208,7 @@
         <v>15.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
         <v>12</v>
@@ -1235,7 +1235,7 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK4" t="n">
         <v>44</v>
@@ -1247,7 +1247,7 @@
         <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1262,7 +1262,7 @@
         <v>13.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K5" t="n">
         <v>4.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.28</v>
@@ -1363,25 +1363,25 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U5" t="n">
         <v>2.6</v>
@@ -1390,88 +1390,88 @@
         <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA5" t="n">
         <v>85</v>
       </c>
       <c r="AB5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD5" t="n">
         <v>970</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="AH5" t="n">
         <v>970</v>
       </c>
       <c r="AI5" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
         <v>60</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AR5" t="n">
         <v>30</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.6</v>
+        <v>44</v>
       </c>
       <c r="AT5" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.5</v>
+        <v>8.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.6</v>
+        <v>36</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AY5" t="n">
         <v>9.800000000000001</v>
@@ -1480,29 +1480,29 @@
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD5" t="n">
         <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG5" t="n">
         <v>24</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -1533,64 +1533,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="G6" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.96</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.06</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1602,10 +1602,10 @@
         <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1617,13 +1617,13 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU6" t="n">
         <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="AY6" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG6" t="n">
         <v>5.5</v>
       </c>
-      <c r="BG6" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -1730,28 +1730,28 @@
         <v>2.68</v>
       </c>
       <c r="G7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="I7" t="n">
         <v>2.74</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
         <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.22</v>
@@ -1766,13 +1766,13 @@
         <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U7" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
         <v>1.58</v>
@@ -1781,7 +1781,7 @@
         <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Y7" t="n">
         <v>16</v>
@@ -1793,7 +1793,7 @@
         <v>40</v>
       </c>
       <c r="AB7" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
         <v>9.800000000000001</v>
@@ -1832,13 +1832,13 @@
         <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AP7" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
         <v>17</v>
@@ -1871,7 +1871,7 @@
         <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1880,17 +1880,17 @@
         <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>1.59</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I8" t="n">
         <v>6.4</v>
@@ -1936,7 +1936,7 @@
         <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.32</v>
@@ -1951,7 +1951,7 @@
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
         <v>1.62</v>
@@ -1966,34 +1966,34 @@
         <v>1.71</v>
       </c>
       <c r="U8" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
         <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X8" t="n">
         <v>28</v>
       </c>
       <c r="Y8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z8" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC8" t="n">
         <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2002,22 +2002,22 @@
         <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK8" t="n">
         <v>15.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2029,16 +2029,16 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.4</v>
+        <v>19.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT8" t="n">
         <v>10</v>
@@ -2050,22 +2050,22 @@
         <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC8" t="n">
         <v>13</v>
@@ -2074,17 +2074,17 @@
         <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="H9" t="n">
         <v>5.6</v>
       </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J9" t="n">
         <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.31</v>
@@ -2139,25 +2139,25 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O9" t="n">
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T9" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U9" t="n">
         <v>2.34</v>
@@ -2166,28 +2166,28 @@
         <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2202,83 +2202,83 @@
         <v>18</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
         <v>16</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AO9" t="n">
-        <v>630</v>
+        <v>55</v>
       </c>
       <c r="AP9" t="n">
         <v>19.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AR9" t="n">
         <v>27</v>
       </c>
       <c r="AS9" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV9" t="n">
         <v>18.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX9" t="n">
         <v>10.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BB9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC9" t="n">
         <v>14</v>
       </c>
       <c r="BD9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG9" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -2309,67 +2309,67 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.2</v>
       </c>
-      <c r="G10" t="n">
+      <c r="K10" t="n">
         <v>3.4</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P10" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="W10" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="X10" t="n">
         <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2378,22 +2378,22 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2414,19 +2414,19 @@
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="AT10" t="n">
         <v>5.2</v>
@@ -2435,44 +2435,44 @@
         <v>4.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY10" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.16</v>
+        <v>7.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.16</v>
+        <v>4.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="G11" t="n">
         <v>1.44</v>
@@ -2512,7 +2512,7 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
         <v>5.5</v>
@@ -2527,7 +2527,7 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O11" t="n">
         <v>1.18</v>
@@ -2539,16 +2539,16 @@
         <v>1.55</v>
       </c>
       <c r="R11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V11" t="n">
         <v>1.12</v>
@@ -2569,10 +2569,10 @@
         <v>250</v>
       </c>
       <c r="AB11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD11" t="n">
         <v>32</v>
@@ -2581,7 +2581,7 @@
         <v>110</v>
       </c>
       <c r="AF11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
@@ -2590,7 +2590,7 @@
         <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ11" t="n">
         <v>13</v>
@@ -2614,16 +2614,16 @@
         <v>12.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU11" t="n">
         <v>11.5</v>
@@ -2632,7 +2632,7 @@
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AX11" t="n">
         <v>9</v>
@@ -2641,32 +2641,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="BC11" t="n">
         <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF11" t="n">
         <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
         <v>4.7</v>
@@ -2709,10 +2709,10 @@
         <v>5.4</v>
       </c>
       <c r="J12" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="K12" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.82</v>
@@ -2739,16 +2739,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
         <v>1.23</v>
       </c>
       <c r="W12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X12" t="n">
         <v>7</v>
@@ -2811,19 +2811,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT12" t="n">
         <v>4.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AW12" t="n">
         <v>5.8</v>
@@ -2835,16 +2835,16 @@
         <v>12.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>30</v>
+        <v>5.3</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BC12" t="n">
-        <v>36</v>
+        <v>5.3</v>
       </c>
       <c r="BD12" t="n">
         <v>5.8</v>
@@ -2853,14 +2853,14 @@
         <v>6</v>
       </c>
       <c r="BF12" t="n">
-        <v>36</v>
+        <v>5.4</v>
       </c>
       <c r="BG12" t="n">
         <v>5.9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -2891,82 +2891,82 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G13" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H13" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="I13" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P13" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="W13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X13" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AB13" t="n">
         <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
         <v>11</v>
       </c>
       <c r="AE13" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AF13" t="n">
         <v>40</v>
@@ -2975,10 +2975,10 @@
         <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ13" t="n">
         <v>1000</v>
@@ -2996,65 +2996,65 @@
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="AV13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="AY13" t="n">
-        <v>15.5</v>
+        <v>5.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC13" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="n">
         <v>3.6</v>
@@ -3109,146 +3109,146 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P14" t="n">
         <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="n">
         <v>16.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA14" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC14" t="n">
         <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
         <v>21</v>
       </c>
       <c r="AK14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR14" t="n">
         <v>5.2</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AS14" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT14" t="n">
         <v>6.4</v>
       </c>
       <c r="AU14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY14" t="n">
         <v>4</v>
       </c>
-      <c r="AV14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>5.7</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="BG14" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G15" t="n">
         <v>1.51</v>
@@ -3291,13 +3291,13 @@
         <v>7.6</v>
       </c>
       <c r="J15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
@@ -3306,49 +3306,49 @@
         <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="S15" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="T15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U15" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V15" t="n">
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X15" t="n">
         <v>30</v>
       </c>
       <c r="Y15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z15" t="n">
         <v>65</v>
       </c>
       <c r="AA15" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AB15" t="n">
         <v>12</v>
       </c>
       <c r="AC15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD15" t="n">
         <v>32</v>
@@ -3363,86 +3363,86 @@
         <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AK15" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO15" t="n">
         <v>90</v>
       </c>
-      <c r="AN15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>80</v>
-      </c>
       <c r="AP15" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AQ15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS15" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AT15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX15" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AU15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AY15" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BA15" t="n">
-        <v>34</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BC15" t="n">
         <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BG15" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -3473,64 +3473,64 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="G16" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="H16" t="n">
         <v>21</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P16" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="U16" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="V16" t="n">
         <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="X16" t="n">
         <v>70</v>
       </c>
       <c r="Y16" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="Z16" t="n">
         <v>240</v>
@@ -3539,7 +3539,7 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AC16" t="n">
         <v>26</v>
@@ -3548,22 +3548,22 @@
         <v>80</v>
       </c>
       <c r="AE16" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AF16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
         <v>46</v>
       </c>
       <c r="AI16" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AJ16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AK16" t="n">
         <v>13.5</v>
@@ -3572,71 +3572,71 @@
         <v>36</v>
       </c>
       <c r="AM16" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AO16" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AP16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>9.4</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AR16" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AS16" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU16" t="n">
         <v>20</v>
       </c>
       <c r="AV16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC16" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>11</v>
       </c>
       <c r="BD16" t="n">
         <v>15</v>
       </c>
       <c r="BE16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -3670,19 +3670,19 @@
         <v>3.4</v>
       </c>
       <c r="G17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H17" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
         <v>1.34</v>
@@ -3691,7 +3691,7 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
         <v>1.25</v>
@@ -3700,7 +3700,7 @@
         <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R17" t="n">
         <v>1.49</v>
@@ -3709,16 +3709,16 @@
         <v>2.84</v>
       </c>
       <c r="T17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
         <v>1.83</v>
       </c>
       <c r="W17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X17" t="n">
         <v>18.5</v>
@@ -3739,13 +3739,13 @@
         <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AF17" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AG17" t="n">
         <v>15.5</v>
@@ -3772,7 +3772,7 @@
         <v>36</v>
       </c>
       <c r="AO17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP17" t="n">
         <v>15</v>
@@ -3787,7 +3787,7 @@
         <v>22</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="AU17" t="n">
         <v>7.6</v>
@@ -3796,13 +3796,13 @@
         <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="AX17" t="n">
         <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
@@ -3811,26 +3811,26 @@
         <v>23</v>
       </c>
       <c r="BB17" t="n">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC17" t="n">
         <v>18</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -3861,170 +3861,170 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="G18" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="H18" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="I18" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="M18" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N18" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="P18" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S18" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="U18" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="V18" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="X18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y18" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AK18" t="n">
         <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.75</v>
+        <v>7.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AS18" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.05</v>
+        <v>4.9</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BA18" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -4055,82 +4055,82 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="G19" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I19" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U19" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="X19" t="n">
         <v>14.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB19" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC19" t="n">
         <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF19" t="n">
         <v>16</v>
@@ -4142,7 +4142,7 @@
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ19" t="n">
         <v>36</v>
@@ -4160,7 +4160,7 @@
         <v>27</v>
       </c>
       <c r="AO19" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AP19" t="n">
         <v>9.4</v>
@@ -4169,25 +4169,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU19" t="n">
         <v>6.2</v>
       </c>
       <c r="AV19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX19" t="n">
         <v>10</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
         <v>8.6</v>
@@ -4196,29 +4196,29 @@
         <v>15</v>
       </c>
       <c r="BA19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB19" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB19" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BC19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG19" t="n">
         <v>4.9</v>
       </c>
-      <c r="BD19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -4267,34 +4267,34 @@
         <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U20" t="n">
         <v>3.25</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.45</v>
       </c>
       <c r="V20" t="n">
         <v>1.56</v>
@@ -4303,31 +4303,31 @@
         <v>1.64</v>
       </c>
       <c r="X20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>23</v>
       </c>
       <c r="AF20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
@@ -4339,49 +4339,49 @@
         <v>25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK20" t="n">
         <v>20</v>
       </c>
       <c r="AL20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR20" t="n">
         <v>23</v>
       </c>
-      <c r="AM20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>26</v>
-      </c>
       <c r="AS20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT20" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW20" t="n">
         <v>22</v>
       </c>
       <c r="AX20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY20" t="n">
         <v>12</v>
@@ -4399,20 +4399,20 @@
         <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF20" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H21" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.34</v>
@@ -4473,16 +4473,16 @@
         <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
         <v>1.8</v>
@@ -4491,10 +4491,10 @@
         <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W21" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X21" t="n">
         <v>18</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,100 +757,100 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="G2" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="P2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
         <v>65</v>
@@ -859,68 +859,68 @@
         <v>250</v>
       </c>
       <c r="AN2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO2" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AS2" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
         <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC2" t="n">
         <v>23</v>
       </c>
       <c r="BD2" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG2" t="n">
         <v>14.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -951,31 +951,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O3" t="n">
         <v>1.53</v>
@@ -996,79 +996,79 @@
         <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X3" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC3" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC3" t="n">
-        <v>8</v>
-      </c>
       <c r="AD3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="n">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>55</v>
+        <v>17.5</v>
       </c>
       <c r="AH3" t="n">
         <v>42</v>
       </c>
       <c r="AI3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AK3" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AO3" t="n">
         <v>150</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
@@ -1080,41 +1080,41 @@
         <v>16.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AX3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY3" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.6</v>
+        <v>24</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I4" t="n">
         <v>2.56</v>
@@ -1160,46 +1160,46 @@
         <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R4" t="n">
         <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
         <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
         <v>1.64</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
         <v>9.6</v>
@@ -1208,7 +1208,7 @@
         <v>15.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AB4" t="n">
         <v>12</v>
@@ -1229,13 +1229,13 @@
         <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK4" t="n">
         <v>44</v>
@@ -1250,10 +1250,10 @@
         <v>70</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>8.199999999999999</v>
@@ -1262,13 +1262,13 @@
         <v>13.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
@@ -1280,25 +1280,25 @@
         <v>18.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BB4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC4" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="BE4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF4" t="n">
         <v>32</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -1345,13 +1345,13 @@
         <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
         <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
         <v>4.6</v>
@@ -1363,7 +1363,7 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
@@ -1372,7 +1372,7 @@
         <v>2.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R5" t="n">
         <v>1.69</v>
@@ -1381,7 +1381,7 @@
         <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U5" t="n">
         <v>2.6</v>
@@ -1393,19 +1393,19 @@
         <v>2.16</v>
       </c>
       <c r="X5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Y5" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AA5" t="n">
         <v>85</v>
       </c>
       <c r="AB5" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
         <v>11</v>
@@ -1414,25 +1414,25 @@
         <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AJ5" t="n">
         <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL5" t="n">
         <v>44</v>
@@ -1441,31 +1441,31 @@
         <v>60</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AS5" t="n">
         <v>44</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.6</v>
+        <v>15.5</v>
       </c>
       <c r="AW5" t="n">
         <v>36</v>
@@ -1477,22 +1477,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BD5" t="n">
         <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BF5" t="n">
         <v>6.8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>1.83</v>
       </c>
       <c r="G6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
         <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
         <v>4.3</v>
@@ -1563,25 +1563,25 @@
         <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
         <v>1.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
         <v>2.08</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H7" t="n">
         <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J7" t="n">
         <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.33</v>
@@ -1760,13 +1760,13 @@
         <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R7" t="n">
         <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T7" t="n">
         <v>1.58</v>
@@ -1778,25 +1778,25 @@
         <v>1.58</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X7" t="n">
         <v>21</v>
       </c>
       <c r="Y7" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
         <v>40</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
         <v>13</v>
@@ -1823,7 +1823,7 @@
         <v>28</v>
       </c>
       <c r="AL7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
         <v>65</v>
@@ -1832,7 +1832,7 @@
         <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AP7" t="n">
         <v>17.5</v>
@@ -1871,26 +1871,26 @@
         <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
         <v>15.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
         <v>1.62</v>
       </c>
       <c r="H8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I8" t="n">
         <v>6.4</v>
@@ -1951,7 +1951,7 @@
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q8" t="n">
         <v>1.62</v>
@@ -1960,13 +1960,13 @@
         <v>1.59</v>
       </c>
       <c r="S8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
         <v>1.71</v>
       </c>
       <c r="U8" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="V8" t="n">
         <v>1.19</v>
@@ -1975,7 +1975,7 @@
         <v>2.6</v>
       </c>
       <c r="X8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
         <v>26</v>
@@ -1987,19 +1987,19 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
         <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG8" t="n">
         <v>10.5</v>
@@ -2008,10 +2008,10 @@
         <v>18.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK8" t="n">
         <v>15.5</v>
@@ -2023,7 +2023,7 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2035,10 +2035,10 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
         <v>10</v>
@@ -2047,7 +2047,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW8" t="n">
         <v>25</v>
@@ -2056,13 +2056,13 @@
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
         <v>14</v>
@@ -2074,17 +2074,17 @@
         <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG8" t="n">
         <v>21</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I9" t="n">
         <v>5.6</v>
       </c>
-      <c r="I9" t="n">
-        <v>5.8</v>
-      </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
         <v>4.5</v>
@@ -2148,31 +2148,31 @@
         <v>2.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
         <v>1.58</v>
       </c>
       <c r="S9" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U9" t="n">
         <v>2.34</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W9" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="n">
         <v>46</v>
@@ -2181,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
         <v>9.800000000000001</v>
@@ -2190,25 +2190,25 @@
         <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
         <v>10</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
         <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL9" t="n">
         <v>27</v>
@@ -2217,34 +2217,34 @@
         <v>80</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO9" t="n">
         <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS9" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AT9" t="n">
         <v>10.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV9" t="n">
         <v>18.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AX9" t="n">
         <v>10.5</v>
@@ -2256,29 +2256,29 @@
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB9" t="n">
         <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BE9" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BF9" t="n">
         <v>7</v>
       </c>
       <c r="BG9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="G10" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="H10" t="n">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="I10" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="J10" t="n">
         <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L10" t="n">
         <v>1.5</v>
@@ -2333,146 +2333,146 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.43</v>
       </c>
       <c r="P10" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U10" t="n">
         <v>1.98</v>
       </c>
       <c r="V10" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="W10" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="X10" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH10" t="n">
         <v>19</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>24</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.7</v>
+        <v>15</v>
       </c>
       <c r="BG10" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -2509,19 +2509,19 @@
         <v>1.44</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
@@ -2536,10 +2536,10 @@
         <v>2.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S11" t="n">
         <v>2.38</v>
@@ -2548,7 +2548,7 @@
         <v>1.82</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
         <v>1.12</v>
@@ -2557,10 +2557,10 @@
         <v>3.25</v>
       </c>
       <c r="X11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y11" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="Z11" t="n">
         <v>75</v>
@@ -2569,13 +2569,13 @@
         <v>250</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AE11" t="n">
         <v>110</v>
@@ -2590,19 +2590,19 @@
         <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AM11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="n">
         <v>5.3</v>
@@ -2614,13 +2614,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR11" t="n">
         <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT11" t="n">
         <v>9.800000000000001</v>
@@ -2632,7 +2632,7 @@
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX11" t="n">
         <v>9</v>
@@ -2647,26 +2647,26 @@
         <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BC11" t="n">
         <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF11" t="n">
         <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -2697,67 +2697,67 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="M12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="N12" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="O12" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="P12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
         <v>1.11</v>
       </c>
       <c r="S12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
         <v>1.23</v>
       </c>
       <c r="W12" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X12" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="Y12" t="n">
         <v>10.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AA12" t="n">
         <v>190</v>
@@ -2766,28 +2766,28 @@
         <v>6.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE12" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
         <v>16.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="n">
         <v>230</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AK12" t="n">
         <v>55</v>
@@ -2805,28 +2805,28 @@
         <v>320</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT12" t="n">
         <v>4.8</v>
       </c>
       <c r="AU12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV12" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV12" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AW12" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12" t="n">
         <v>9.6</v>
@@ -2835,32 +2835,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.3</v>
+        <v>38</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>4.7</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I13" t="n">
         <v>2.04</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
         <v>3.45</v>
@@ -2915,19 +2915,19 @@
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
         <v>1.38</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
         <v>2.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
         <v>4.1</v>
@@ -2945,19 +2945,19 @@
         <v>1.24</v>
       </c>
       <c r="X13" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB13" t="n">
         <v>25</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>970</v>
       </c>
       <c r="AC13" t="n">
         <v>7.8</v>
@@ -2966,10 +2966,10 @@
         <v>11</v>
       </c>
       <c r="AE13" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AF13" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
@@ -2996,65 +2996,65 @@
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>6.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.7</v>
+        <v>13.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC13" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.5</v>
+        <v>15</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -3085,79 +3085,79 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="H14" t="n">
         <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N14" t="n">
         <v>4</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.55</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="U14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
         <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="Z14" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
         <v>150</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
         <v>75</v>
@@ -3172,7 +3172,7 @@
         <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="n">
         <v>21</v>
@@ -3181,52 +3181,52 @@
         <v>24</v>
       </c>
       <c r="AL14" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AM14" t="n">
         <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO14" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AQ14" t="n">
         <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
         <v>14</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AX14" t="n">
         <v>9.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
         <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BB14" t="n">
         <v>14.5</v>
@@ -3235,20 +3235,20 @@
         <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G15" t="n">
         <v>1.51</v>
@@ -3288,10 +3288,10 @@
         <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K15" t="n">
         <v>5.4</v>
@@ -3321,22 +3321,22 @@
         <v>2.38</v>
       </c>
       <c r="T15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
         <v>2.96</v>
       </c>
       <c r="X15" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Y15" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Z15" t="n">
         <v>65</v>
@@ -3351,16 +3351,16 @@
         <v>12.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AE15" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="AF15" t="n">
         <v>11.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AH15" t="n">
         <v>21</v>
@@ -3369,10 +3369,10 @@
         <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL15" t="n">
         <v>29</v>
@@ -3390,25 +3390,25 @@
         <v>18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AS15" t="n">
         <v>7.2</v>
       </c>
       <c r="AT15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU15" t="n">
         <v>10</v>
       </c>
-      <c r="AU15" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AV15" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AX15" t="n">
         <v>9.800000000000001</v>
@@ -3417,10 +3417,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>8.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BB15" t="n">
         <v>12</v>
@@ -3429,20 +3429,20 @@
         <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -3482,43 +3482,43 @@
         <v>21</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
         <v>1.1</v>
       </c>
       <c r="P16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
         <v>1.04</v>
@@ -3527,13 +3527,13 @@
         <v>6.6</v>
       </c>
       <c r="X16" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="Y16" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="Z16" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
@@ -3542,16 +3542,16 @@
         <v>16.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD16" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AE16" t="n">
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="AF16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
         <v>13.5</v>
@@ -3560,61 +3560,61 @@
         <v>46</v>
       </c>
       <c r="AI16" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AJ16" t="n">
         <v>10.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
         <v>180</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="AO16" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AP16" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AT16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU16" t="n">
         <v>20</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AW16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX16" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AY16" t="n">
         <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BB16" t="n">
         <v>8.4</v>
@@ -3626,17 +3626,17 @@
         <v>15</v>
       </c>
       <c r="BE16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G17" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="H17" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="I17" t="n">
         <v>2.22</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
         <v>3.95</v>
@@ -3691,22 +3691,22 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
         <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
         <v>1.74</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T17" t="n">
         <v>1.64</v>
@@ -3718,10 +3718,10 @@
         <v>1.83</v>
       </c>
       <c r="W17" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="n">
         <v>13.5</v>
@@ -3733,7 +3733,7 @@
         <v>32</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AC17" t="n">
         <v>9</v>
@@ -3745,13 +3745,13 @@
         <v>22</v>
       </c>
       <c r="AF17" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AG17" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI17" t="n">
         <v>36</v>
@@ -3769,10 +3769,10 @@
         <v>70</v>
       </c>
       <c r="AN17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO17" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP17" t="n">
         <v>15</v>
@@ -3787,50 +3787,50 @@
         <v>22</v>
       </c>
       <c r="AT17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU17" t="n">
         <v>7.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>9.6</v>
+        <v>18.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY17" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
         <v>23</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="BG17" t="n">
         <v>11.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -3861,100 +3861,100 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="H18" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="I18" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="P18" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="R18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="U18" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="V18" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="X18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y18" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AG18" t="n">
         <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3963,68 +3963,68 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AY18" t="n">
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BB18" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BF18" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G19" t="n">
         <v>2.42</v>
@@ -4070,7 +4070,7 @@
         <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.46</v>
@@ -4085,13 +4085,13 @@
         <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
         <v>2.12</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
         <v>3.9</v>
@@ -4115,7 +4115,7 @@
         <v>12.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA19" t="n">
         <v>70</v>
@@ -4169,7 +4169,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS19" t="n">
         <v>5</v>
@@ -4193,16 +4193,16 @@
         <v>8.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="BA19" t="n">
         <v>5</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>19.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD19" t="n">
         <v>5</v>
@@ -4211,14 +4211,14 @@
         <v>5.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG19" t="n">
         <v>4.9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="G20" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="H20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I20" t="n">
         <v>2.74</v>
       </c>
-      <c r="I20" t="n">
-        <v>2.76</v>
-      </c>
       <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
         <v>4.1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.24</v>
@@ -4285,31 +4285,31 @@
         <v>1.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S20" t="n">
         <v>2.14</v>
       </c>
       <c r="T20" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="U20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="V20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W20" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y20" t="n">
         <v>21</v>
       </c>
       <c r="Z20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA20" t="n">
         <v>42</v>
@@ -4318,10 +4318,10 @@
         <v>21</v>
       </c>
       <c r="AC20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE20" t="n">
         <v>23</v>
@@ -4342,7 +4342,7 @@
         <v>38</v>
       </c>
       <c r="AK20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="n">
         <v>24</v>
@@ -4351,10 +4351,10 @@
         <v>38</v>
       </c>
       <c r="AN20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP20" t="n">
         <v>30</v>
@@ -4369,19 +4369,19 @@
         <v>40</v>
       </c>
       <c r="AT20" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW20" t="n">
         <v>22</v>
       </c>
       <c r="AX20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY20" t="n">
         <v>12</v>
@@ -4396,7 +4396,7 @@
         <v>36</v>
       </c>
       <c r="BC20" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
         <v>23</v>
@@ -4408,11 +4408,11 @@
         <v>10.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -4455,13 +4455,13 @@
         <v>4.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
@@ -4479,7 +4479,7 @@
         <v>1.87</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
         <v>3.05</v>
@@ -4491,7 +4491,7 @@
         <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
         <v>1.79</v>
@@ -4500,113 +4500,113 @@
         <v>18</v>
       </c>
       <c r="Y21" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z21" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA21" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG21" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="AH21" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AI21" t="n">
         <v>55</v>
       </c>
-      <c r="AF21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>60</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP21" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="AV21" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AW21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY21" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AZ21" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="G2" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="I2" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="O2" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="P2" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="R2" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="T2" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W2" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="X2" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
         <v>13.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH2" t="n">
         <v>25</v>
       </c>
-      <c r="AE2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>29</v>
-      </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
         <v>26</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO2" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ2" t="n">
         <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>15.5</v>
+        <v>48</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY2" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>14.5</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF2" t="n">
         <v>19.5</v>
       </c>
-      <c r="BC2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>20</v>
-      </c>
       <c r="BG2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
         <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="X3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AK3" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
         <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
         <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX3" t="n">
         <v>9.6</v>
       </c>
-      <c r="AX3" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BC3" t="n">
         <v>24</v>
       </c>
       <c r="BD3" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BE3" t="n">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="G4" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.48</v>
+        <v>1.93</v>
       </c>
       <c r="I4" t="n">
-        <v>2.56</v>
+        <v>1.96</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="U4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V4" t="n">
         <v>2</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.64</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="X4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Y4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AA4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>12</v>
-      </c>
       <c r="AC4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="n">
         <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AO4" t="n">
-        <v>44</v>
+        <v>16.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AX4" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
         <v>21</v>
       </c>
       <c r="BB4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD4" t="n">
         <v>12</v>
       </c>
-      <c r="BC4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>44</v>
-      </c>
       <c r="BE4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF4" t="n">
         <v>32</v>
       </c>
       <c r="BG4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -1339,37 +1339,37 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K5" t="n">
         <v>4.5</v>
       </c>
-      <c r="J5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" t="n">
         <v>1.55</v>
@@ -1378,88 +1378,88 @@
         <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U5" t="n">
         <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="X5" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE5" t="n">
         <v>40</v>
       </c>
-      <c r="Y5" t="n">
-        <v>42</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>70</v>
-      </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>15.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ5" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AL5" t="n">
         <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS5" t="n">
         <v>13</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>44</v>
-      </c>
       <c r="AT5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU5" t="n">
         <v>9.4</v>
@@ -1468,10 +1468,10 @@
         <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY5" t="n">
         <v>9.800000000000001</v>
@@ -1480,29 +1480,29 @@
         <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BE5" t="n">
         <v>11.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -1533,64 +1533,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
         <v>4.4</v>
       </c>
-      <c r="I6" t="n">
-        <v>4.7</v>
-      </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1599,25 +1599,25 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1626,7 +1626,7 @@
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1644,59 +1644,59 @@
         <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
         <v>7.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.7</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.4</v>
+        <v>42</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE6" t="n">
         <v>7.8</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF6" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -1727,79 +1727,79 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="G7" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="I7" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="R7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T7" t="n">
         <v>1.53</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.58</v>
-      </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB7" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE7" t="n">
         <v>26</v>
@@ -1808,89 +1808,89 @@
         <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN7" t="n">
         <v>16</v>
       </c>
-      <c r="AI7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>20</v>
-      </c>
       <c r="AO7" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AP7" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT7" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU7" t="n">
         <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX7" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BC7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.8</v>
+        <v>27</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BF7" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG7" t="n">
         <v>14</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -1924,58 +1924,58 @@
         <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H8" t="n">
         <v>5.8</v>
       </c>
       <c r="I8" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K8" t="n">
         <v>4.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.2</v>
       </c>
       <c r="P8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S8" t="n">
         <v>2.52</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U8" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
         <v>26</v>
@@ -1984,19 +1984,19 @@
         <v>55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF8" t="n">
         <v>11.5</v>
@@ -2008,83 +2008,83 @@
         <v>18.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
         <v>16</v>
       </c>
       <c r="AK8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT8" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>10</v>
       </c>
-      <c r="AU8" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AV8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW8" t="n">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="BB8" t="n">
         <v>14</v>
       </c>
       <c r="BC8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -2118,52 +2118,52 @@
         <v>1.69</v>
       </c>
       <c r="G9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I9" t="n">
         <v>5.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U9" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
         <v>2.38</v>
@@ -2172,7 +2172,7 @@
         <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z9" t="n">
         <v>46</v>
@@ -2181,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
         <v>9.800000000000001</v>
@@ -2199,25 +2199,25 @@
         <v>10</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI9" t="n">
         <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK9" t="n">
         <v>16.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM9" t="n">
         <v>80</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO9" t="n">
         <v>55</v>
@@ -2226,25 +2226,25 @@
         <v>19</v>
       </c>
       <c r="AQ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR9" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AS9" t="n">
         <v>40</v>
       </c>
       <c r="AT9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AX9" t="n">
         <v>10.5</v>
@@ -2259,7 +2259,7 @@
         <v>29</v>
       </c>
       <c r="BB9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC9" t="n">
         <v>14.5</v>
@@ -2268,17 +2268,17 @@
         <v>24</v>
       </c>
       <c r="BE9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -2315,13 +2315,13 @@
         <v>3.35</v>
       </c>
       <c r="H10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I10" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
         <v>3.35</v>
@@ -2333,40 +2333,40 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.43</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.42</v>
-      </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z10" t="n">
         <v>15</v>
@@ -2378,7 +2378,7 @@
         <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AD10" t="n">
         <v>12</v>
@@ -2390,31 +2390,31 @@
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
         <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
         <v>60</v>
       </c>
       <c r="AK10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM10" t="n">
         <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>130</v>
       </c>
       <c r="AN10" t="n">
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP10" t="n">
         <v>9.800000000000001</v>
@@ -2441,38 +2441,38 @@
         <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY10" t="n">
         <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC10" t="n">
         <v>14.5</v>
       </c>
-      <c r="BB10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>14</v>
-      </c>
       <c r="BD10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BE10" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="BG10" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -2509,10 +2509,10 @@
         <v>1.44</v>
       </c>
       <c r="H11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
         <v>5.4</v>
@@ -2527,7 +2527,7 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
         <v>1.18</v>
@@ -2536,16 +2536,16 @@
         <v>2.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
         <v>2.1</v>
@@ -2557,10 +2557,10 @@
         <v>3.25</v>
       </c>
       <c r="X11" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="Y11" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="Z11" t="n">
         <v>75</v>
@@ -2569,7 +2569,7 @@
         <v>250</v>
       </c>
       <c r="AB11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC11" t="n">
         <v>14</v>
@@ -2590,7 +2590,7 @@
         <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="n">
         <v>12.5</v>
@@ -2608,31 +2608,31 @@
         <v>5.3</v>
       </c>
       <c r="AO11" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AP11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR11" t="n">
         <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU11" t="n">
         <v>11.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX11" t="n">
         <v>9</v>
@@ -2644,10 +2644,10 @@
         <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC11" t="n">
         <v>12</v>
@@ -2656,17 +2656,17 @@
         <v>11</v>
       </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BF11" t="n">
         <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
         <v>4.9</v>
       </c>
       <c r="I12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K12" t="n">
         <v>2.72</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.83</v>
@@ -2724,13 +2724,13 @@
         <v>2.04</v>
       </c>
       <c r="O12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="P12" t="n">
         <v>1.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
         <v>1.11</v>
@@ -2739,128 +2739,128 @@
         <v>9.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.84</v>
+        <v>2.24</v>
       </c>
       <c r="U12" t="n">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
         <v>1.23</v>
       </c>
       <c r="W12" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.4</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE12" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK12" t="n">
         <v>48</v>
       </c>
-      <c r="AK12" t="n">
-        <v>55</v>
-      </c>
       <c r="AL12" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>1.26</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="AR12" t="n">
-        <v>11</v>
+        <v>1.61</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.61</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.8</v>
+        <v>1.61</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.6</v>
+        <v>1.52</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.61</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.6</v>
+        <v>1.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>12.5</v>
+        <v>1.46</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.4</v>
+        <v>1.61</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.4</v>
+        <v>1.61</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.5</v>
+        <v>1.53</v>
       </c>
       <c r="BC12" t="n">
-        <v>38</v>
+        <v>1.55</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.61</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.6</v>
+        <v>1.61</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.4</v>
+        <v>1.61</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.4</v>
+        <v>1.61</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="G13" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="I13" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.47</v>
@@ -2915,61 +2915,61 @@
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
         <v>1.38</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
         <v>2.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
         <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U13" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="W13" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AB13" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE13" t="n">
         <v>34</v>
       </c>
       <c r="AF13" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
@@ -2978,7 +2978,7 @@
         <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="n">
         <v>1000</v>
@@ -2996,65 +2996,65 @@
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
         <v>6.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AT13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV13" t="n">
         <v>9</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BE13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BF13" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BG13" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G14" t="n">
         <v>1.8</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.82</v>
-      </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="n">
         <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.41</v>
@@ -3109,7 +3109,7 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
         <v>1.31</v>
@@ -3121,25 +3121,25 @@
         <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
         <v>22</v>
@@ -3163,22 +3163,22 @@
         <v>75</v>
       </c>
       <c r="AF14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
         <v>75</v>
       </c>
       <c r="AJ14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK14" t="n">
         <v>21</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>24</v>
       </c>
       <c r="AL14" t="n">
         <v>38</v>
@@ -3187,7 +3187,7 @@
         <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO14" t="n">
         <v>110</v>
@@ -3196,16 +3196,16 @@
         <v>15</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU14" t="n">
         <v>6.8</v>
@@ -3214,10 +3214,10 @@
         <v>14</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY14" t="n">
         <v>8.6</v>
@@ -3226,29 +3226,29 @@
         <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BB14" t="n">
         <v>14.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H15" t="n">
         <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.29</v>
@@ -3303,67 +3303,67 @@
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S15" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U15" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X15" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Y15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z15" t="n">
         <v>65</v>
       </c>
       <c r="AA15" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC15" t="n">
         <v>12</v>
       </c>
-      <c r="AC15" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AD15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE15" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AF15" t="n">
         <v>11.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI15" t="n">
         <v>80</v>
@@ -3372,31 +3372,31 @@
         <v>14.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AM15" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ15" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AT15" t="n">
         <v>10.5</v>
@@ -3405,44 +3405,44 @@
         <v>10</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AX15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>17</v>
-      </c>
       <c r="BA15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC15" t="n">
         <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BE15" t="n">
         <v>11.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG15" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G16" t="n">
         <v>1.18</v>
       </c>
       <c r="H16" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="K16" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
@@ -3500,40 +3500,40 @@
         <v>10</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="U16" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="X16" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="Y16" t="n">
         <v>120</v>
       </c>
       <c r="Z16" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
@@ -3542,25 +3542,25 @@
         <v>16.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AD16" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AE16" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AF16" t="n">
         <v>11</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
         <v>46</v>
       </c>
       <c r="AI16" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AJ16" t="n">
         <v>10.5</v>
@@ -3569,74 +3569,74 @@
         <v>13</v>
       </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM16" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="AO16" t="n">
         <v>360</v>
       </c>
       <c r="AP16" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU16" t="n">
         <v>20</v>
       </c>
       <c r="AV16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY16" t="n">
         <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC16" t="n">
         <v>10.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="BG16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -3673,13 +3673,13 @@
         <v>3.75</v>
       </c>
       <c r="H17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K17" t="n">
         <v>3.95</v>
@@ -3691,7 +3691,7 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
         <v>1.25</v>
@@ -3700,137 +3700,137 @@
         <v>2.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R17" t="n">
         <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T17" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AA17" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AB17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE17" t="n">
         <v>22</v>
       </c>
       <c r="AF17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK17" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP17" t="n">
         <v>15.5</v>
       </c>
-      <c r="AP17" t="n">
-        <v>15</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT17" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW17" t="n">
         <v>18.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE17" t="n">
         <v>14</v>
       </c>
-      <c r="BA17" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG17" t="n">
         <v>11.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G18" t="n">
         <v>1.7</v>
       </c>
       <c r="H18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J18" t="n">
         <v>3.5</v>
@@ -3879,34 +3879,34 @@
         <v>3.75</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="M18" t="n">
         <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P18" t="n">
         <v>1.51</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S18" t="n">
         <v>5.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="U18" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
@@ -3915,19 +3915,19 @@
         <v>2.42</v>
       </c>
       <c r="X18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AC18" t="n">
         <v>9</v>
@@ -3942,55 +3942,55 @@
         <v>8</v>
       </c>
       <c r="AG18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AN18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR18" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AS18" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
@@ -3999,32 +3999,32 @@
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA18" t="n">
         <v>13</v>
       </c>
-      <c r="BA18" t="n">
-        <v>11</v>
-      </c>
       <c r="BB18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD18" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BE18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BF18" t="n">
         <v>15.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42</v>
+        <v>2.78</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="I19" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L19" t="n">
         <v>1.46</v>
@@ -4079,34 +4079,34 @@
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
         <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="X19" t="n">
         <v>14.5</v>
@@ -4115,110 +4115,110 @@
         <v>12.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC19" t="n">
         <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AG19" t="n">
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AK19" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AL19" t="n">
         <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN19" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AO19" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC19" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>18</v>
+        <v>4.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -4255,10 +4255,10 @@
         <v>2.6</v>
       </c>
       <c r="H20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I20" t="n">
         <v>2.72</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.74</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
@@ -4267,7 +4267,7 @@
         <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M20" t="n">
         <v>1.03</v>
@@ -4282,13 +4282,13 @@
         <v>3.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R20" t="n">
         <v>1.87</v>
       </c>
       <c r="S20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T20" t="n">
         <v>1.45</v>
@@ -4297,19 +4297,19 @@
         <v>3.15</v>
       </c>
       <c r="V20" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W20" t="n">
         <v>1.62</v>
       </c>
       <c r="X20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y20" t="n">
         <v>21</v>
       </c>
       <c r="Z20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA20" t="n">
         <v>42</v>
@@ -4318,10 +4318,10 @@
         <v>21</v>
       </c>
       <c r="AC20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>23</v>
@@ -4330,7 +4330,7 @@
         <v>22</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>12.5</v>
@@ -4339,7 +4339,7 @@
         <v>25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK20" t="n">
         <v>21</v>
@@ -4351,13 +4351,13 @@
         <v>38</v>
       </c>
       <c r="AN20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO20" t="n">
         <v>12.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ20" t="n">
         <v>20</v>
@@ -4372,19 +4372,19 @@
         <v>20</v>
       </c>
       <c r="AU20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW20" t="n">
         <v>22</v>
       </c>
       <c r="AX20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
         <v>12</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
@@ -4446,19 +4446,19 @@
         <v>2.06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H21" t="n">
         <v>3.55</v>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.35</v>
@@ -4467,13 +4467,13 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
         <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q21" t="n">
         <v>1.87</v>
@@ -4482,19 +4482,19 @@
         <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T21" t="n">
         <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V21" t="n">
         <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X21" t="n">
         <v>18</v>
@@ -4509,7 +4509,7 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC21" t="n">
         <v>8.800000000000001</v>
@@ -4542,71 +4542,71 @@
         <v>38</v>
       </c>
       <c r="AM21" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO21" t="n">
         <v>46</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="AS21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU21" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AV21" t="n">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA21" t="n">
         <v>7.4</v>
       </c>
-      <c r="AX21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BB21" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>2.54</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.54</v>
+        <v>5.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="N2" t="n">
-        <v>2.94</v>
+        <v>1.69</v>
       </c>
       <c r="O2" t="n">
-        <v>1.48</v>
+        <v>2.38</v>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>1.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.46</v>
+        <v>5.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="S2" t="n">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>3.55</v>
       </c>
       <c r="U2" t="n">
-        <v>1.82</v>
+        <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="X2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y2" t="n">
         <v>10</v>
       </c>
-      <c r="Y2" t="n">
-        <v>13.5</v>
-      </c>
       <c r="Z2" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>350</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>990</v>
       </c>
       <c r="AE2" t="n">
-        <v>85</v>
+        <v>310</v>
       </c>
       <c r="AF2" t="n">
         <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>300</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
         <v>100</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>23</v>
-      </c>
       <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>210</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW2" t="n">
         <v>140</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>48</v>
       </c>
       <c r="AX2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="BA2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="BD2" t="n">
-        <v>46</v>
+        <v>220</v>
       </c>
       <c r="BE2" t="n">
-        <v>150</v>
+        <v>13.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>19.5</v>
+        <v>80</v>
       </c>
       <c r="BG2" t="n">
-        <v>14</v>
+        <v>250</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.97</v>
+        <v>2.54</v>
       </c>
       <c r="G3" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>2.54</v>
       </c>
       <c r="L3" t="n">
-        <v>1.57</v>
+        <v>5.8</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="N3" t="n">
-        <v>2.84</v>
+        <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>2.28</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.21</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.58</v>
+        <v>5.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="S3" t="n">
-        <v>5.3</v>
+        <v>15.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>3.35</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="X3" t="n">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AF3" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AI3" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="AJ3" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="AM3" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="AO3" t="n">
-        <v>140</v>
+        <v>470</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AS3" t="n">
-        <v>16.5</v>
+        <v>100</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="n">
         <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>200</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>170</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>170</v>
+      </c>
+      <c r="BF3" t="n">
         <v>70</v>
       </c>
-      <c r="AX3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>140</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>20</v>
-      </c>
       <c r="BG3" t="n">
-        <v>16.5</v>
+        <v>190</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="I4" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="J4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N4" t="n">
         <v>3.55</v>
       </c>
-      <c r="K4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="W4" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1000</v>
       </c>
-      <c r="AF4" t="n">
-        <v>34</v>
-      </c>
       <c r="AG4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AL4" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AM4" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AY4" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BB4" t="n">
         <v>12.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="BD4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BE4" t="n">
         <v>12.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="BG4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G5" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -1351,73 +1351,73 @@
         <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
@@ -1426,83 +1426,83 @@
         <v>15.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ5" t="n">
         <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="AM5" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AN5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR5" t="n">
         <v>20</v>
       </c>
-      <c r="AR5" t="n">
-        <v>30</v>
-      </c>
       <c r="AS5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AV5" t="n">
         <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AX5" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
         <v>17</v>
       </c>
       <c r="BB5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="G6" t="n">
         <v>2.06</v>
@@ -1542,13 +1542,13 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.47</v>
@@ -1557,16 +1557,16 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
         <v>1.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
         <v>1.3</v>
@@ -1575,10 +1575,10 @@
         <v>3.85</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V6" t="n">
         <v>1.3</v>
@@ -1587,10 +1587,10 @@
         <v>1.94</v>
       </c>
       <c r="X6" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1602,7 +1602,7 @@
         <v>8.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>18</v>
@@ -1611,7 +1611,7 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
@@ -1623,10 +1623,10 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1644,25 +1644,25 @@
         <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.6</v>
+        <v>26</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT6" t="n">
         <v>7.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
         <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX6" t="n">
         <v>9.800000000000001</v>
@@ -1671,32 +1671,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -1727,64 +1727,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G7" t="n">
         <v>2.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I7" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="T7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U7" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V7" t="n">
         <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X7" t="n">
         <v>22</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
@@ -1793,13 +1793,13 @@
         <v>42</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC7" t="n">
         <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE7" t="n">
         <v>26</v>
@@ -1808,7 +1808,7 @@
         <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
         <v>14</v>
@@ -1823,74 +1823,74 @@
         <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM7" t="n">
         <v>55</v>
       </c>
       <c r="AN7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>16</v>
       </c>
-      <c r="AO7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AR7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
         <v>36</v>
       </c>
       <c r="AT7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
         <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW7" t="n">
         <v>22</v>
       </c>
       <c r="AX7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC7" t="n">
         <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE7" t="n">
         <v>20</v>
       </c>
       <c r="BF7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG7" t="n">
         <v>13.5</v>
       </c>
-      <c r="BG7" t="n">
-        <v>14</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -1921,46 +1921,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
         <v>1.69</v>
@@ -1969,16 +1969,16 @@
         <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
         <v>55</v>
@@ -1993,22 +1993,22 @@
         <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
         <v>11.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
         <v>18.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ8" t="n">
         <v>16</v>
@@ -2017,28 +2017,28 @@
         <v>15</v>
       </c>
       <c r="AL8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AO8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR8" t="n">
-        <v>17.5</v>
+        <v>44</v>
       </c>
       <c r="AS8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AT8" t="n">
         <v>10.5</v>
@@ -2050,10 +2050,10 @@
         <v>20</v>
       </c>
       <c r="AW8" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AX8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY8" t="n">
         <v>9.199999999999999</v>
@@ -2074,17 +2074,17 @@
         <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -2118,91 +2118,91 @@
         <v>1.69</v>
       </c>
       <c r="G9" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W9" t="n">
         <v>2.42</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.38</v>
-      </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z9" t="n">
         <v>46</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
         <v>21</v>
       </c>
       <c r="AE9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI9" t="n">
         <v>65</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>60</v>
       </c>
       <c r="AJ9" t="n">
         <v>17.5</v>
@@ -2211,74 +2211,74 @@
         <v>16.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AM9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AO9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP9" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>21</v>
       </c>
       <c r="AR9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AS9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX9" t="n">
         <v>10</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10.5</v>
       </c>
       <c r="AY9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BB9" t="n">
         <v>15.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>3.35</v>
       </c>
       <c r="H10" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="I10" t="n">
         <v>2.58</v>
@@ -2333,16 +2333,16 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R10" t="n">
         <v>1.26</v>
@@ -2351,28 +2351,28 @@
         <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U10" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="V10" t="n">
         <v>1.63</v>
       </c>
       <c r="W10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X10" t="n">
         <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
         <v>15</v>
       </c>
       <c r="AA10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB10" t="n">
         <v>11</v>
@@ -2390,13 +2390,13 @@
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ10" t="n">
         <v>60</v>
@@ -2405,7 +2405,7 @@
         <v>44</v>
       </c>
       <c r="AL10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2414,19 +2414,19 @@
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR10" t="n">
         <v>13.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -2435,7 +2435,7 @@
         <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
         <v>15</v>
@@ -2447,32 +2447,32 @@
         <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BC10" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BE10" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BG10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="G11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.28</v>
@@ -2527,7 +2527,7 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O11" t="n">
         <v>1.18</v>
@@ -2545,28 +2545,28 @@
         <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="X11" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Y11" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="Z11" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AA11" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="AB11" t="n">
         <v>11.5</v>
@@ -2578,22 +2578,22 @@
         <v>50</v>
       </c>
       <c r="AE11" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
       </c>
       <c r="AH11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>24</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>12.5</v>
       </c>
       <c r="AK11" t="n">
         <v>16</v>
@@ -2608,19 +2608,19 @@
         <v>5.3</v>
       </c>
       <c r="AO11" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AP11" t="n">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="AR11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
         <v>10</v>
@@ -2629,44 +2629,44 @@
         <v>11.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="BA11" t="n">
-        <v>28</v>
+        <v>7.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BC11" t="n">
         <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -2700,91 +2700,91 @@
         <v>2.28</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="K12" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="L12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="M12" t="n">
         <v>1.23</v>
       </c>
       <c r="N12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O12" t="n">
         <v>1.9</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="S12" t="n">
         <v>9.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.24</v>
+        <v>2.78</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>5.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
         <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ12" t="n">
         <v>34</v>
@@ -2793,74 +2793,74 @@
         <v>48</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.26</v>
+        <v>4.9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.48</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.61</v>
+        <v>6.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.61</v>
+        <v>5.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.61</v>
+        <v>5.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.6</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.52</v>
+        <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.61</v>
+        <v>6.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.6</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.46</v>
+        <v>13</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.61</v>
+        <v>6.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.61</v>
+        <v>5.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.53</v>
+        <v>12.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.55</v>
+        <v>14</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.61</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.61</v>
+        <v>110</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.61</v>
+        <v>5.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -2891,94 +2891,94 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="I13" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V13" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
       </c>
       <c r="Y13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC13" t="n">
         <v>7.8</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8</v>
       </c>
       <c r="AD13" t="n">
         <v>10.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AF13" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AI13" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AJ13" t="n">
         <v>1000</v>
@@ -2996,65 +2996,65 @@
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
         <v>6.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV13" t="n">
         <v>9</v>
       </c>
       <c r="AW13" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AX13" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="AY13" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AZ13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF13" t="n">
         <v>12</v>
       </c>
-      <c r="BA13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>13</v>
-      </c>
       <c r="BG13" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -3091,13 +3091,13 @@
         <v>1.8</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
         <v>5.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
         <v>4.3</v>
@@ -3109,10 +3109,10 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
         <v>2.02</v>
@@ -3121,16 +3121,16 @@
         <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
         <v>3.35</v>
       </c>
       <c r="T14" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="U14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
         <v>1.21</v>
@@ -3139,10 +3139,10 @@
         <v>2.24</v>
       </c>
       <c r="X14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="n">
         <v>55</v>
@@ -3151,13 +3151,13 @@
         <v>150</v>
       </c>
       <c r="AB14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
         <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
         <v>75</v>
@@ -3169,7 +3169,7 @@
         <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
         <v>75</v>
@@ -3181,13 +3181,13 @@
         <v>21</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM14" t="n">
         <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO14" t="n">
         <v>110</v>
@@ -3199,19 +3199,19 @@
         <v>15.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU14" t="n">
         <v>7.8</v>
       </c>
-      <c r="AU14" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
         <v>5.5</v>
@@ -3223,32 +3223,32 @@
         <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
         <v>5.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC14" t="n">
         <v>16</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE14" t="n">
         <v>5.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J15" t="n">
         <v>5.1</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.29</v>
@@ -3309,37 +3309,37 @@
         <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q15" t="n">
         <v>1.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
         <v>3</v>
       </c>
       <c r="X15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z15" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AA15" t="n">
         <v>210</v>
@@ -3348,67 +3348,67 @@
         <v>12.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AE15" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AF15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
         <v>80</v>
       </c>
       <c r="AJ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK15" t="n">
         <v>14.5</v>
       </c>
-      <c r="AK15" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AL15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM15" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AN15" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AO15" t="n">
         <v>85</v>
       </c>
       <c r="AP15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="AR15" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU15" t="n">
         <v>10.5</v>
       </c>
-      <c r="AU15" t="n">
-        <v>10</v>
-      </c>
       <c r="AV15" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
         <v>12</v>
@@ -3429,20 +3429,20 @@
         <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="BE15" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -3473,67 +3473,67 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="G16" t="n">
         <v>1.18</v>
       </c>
       <c r="H16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="L16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.09</v>
       </c>
       <c r="P16" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="T16" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="U16" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
         <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="X16" t="n">
         <v>85</v>
       </c>
       <c r="Y16" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="Z16" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
@@ -3542,101 +3542,101 @@
         <v>16.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AD16" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AE16" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
         <v>46</v>
       </c>
       <c r="AI16" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="AJ16" t="n">
         <v>10.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
         <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="AO16" t="n">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="AP16" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AS16" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU16" t="n">
         <v>20</v>
       </c>
       <c r="AV16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY16" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BA16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC16" t="n">
         <v>11.5</v>
       </c>
-      <c r="BB16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BD16" t="n">
-        <v>9.6</v>
+        <v>27</v>
       </c>
       <c r="BE16" t="n">
-        <v>11.5</v>
+        <v>90</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G17" t="n">
         <v>3.5</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J17" t="n">
         <v>3.75</v>
       </c>
-      <c r="H17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.85</v>
-      </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -3694,143 +3694,143 @@
         <v>4.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P17" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
         <v>1.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
         <v>2.88</v>
       </c>
       <c r="T17" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="U17" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="V17" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="W17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X17" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z17" t="n">
         <v>15</v>
       </c>
       <c r="AA17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>28</v>
+        <v>540</v>
       </c>
       <c r="AG17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI17" t="n">
         <v>32</v>
       </c>
       <c r="AJ17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL17" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM17" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AN17" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AO17" t="n">
         <v>13</v>
       </c>
       <c r="AP17" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
         <v>14</v>
       </c>
       <c r="AS17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA17" t="n">
         <v>27</v>
       </c>
       <c r="BB17" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="BC17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD17" t="n">
         <v>34</v>
       </c>
       <c r="BE17" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="BF17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BG17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H18" t="n">
         <v>7.6</v>
@@ -3873,52 +3873,52 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M18" t="n">
         <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O18" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="P18" t="n">
         <v>1.51</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y18" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z18" t="n">
         <v>65</v>
@@ -3930,19 +3930,19 @@
         <v>5.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
         <v>38</v>
@@ -3951,49 +3951,49 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM18" t="n">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
         <v>18.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ18" t="n">
         <v>15</v>
       </c>
       <c r="AR18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AS18" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AU18" t="n">
         <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AW18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX18" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY18" t="n">
         <v>10</v>
@@ -4002,19 +4002,19 @@
         <v>30</v>
       </c>
       <c r="BA18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BB18" t="n">
         <v>14</v>
       </c>
       <c r="BC18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF18" t="n">
         <v>15.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="G19" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="I19" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="L19" t="n">
         <v>1.46</v>
@@ -4085,13 +4085,13 @@
         <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
         <v>3.9</v>
@@ -4100,13 +4100,13 @@
         <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="X19" t="n">
         <v>14.5</v>
@@ -4127,16 +4127,16 @@
         <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE19" t="n">
         <v>42</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
         <v>22</v>
@@ -4160,7 +4160,7 @@
         <v>36</v>
       </c>
       <c r="AO19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP19" t="n">
         <v>10</v>
@@ -4169,25 +4169,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU19" t="n">
         <v>6.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AX19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
@@ -4196,29 +4196,29 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -4261,10 +4261,10 @@
         <v>2.72</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.25</v>
@@ -4279,22 +4279,22 @@
         <v>1.14</v>
       </c>
       <c r="P20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U20" t="n">
         <v>3.1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.15</v>
       </c>
       <c r="V20" t="n">
         <v>1.58</v>
@@ -4303,13 +4303,13 @@
         <v>1.62</v>
       </c>
       <c r="X20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA20" t="n">
         <v>42</v>
@@ -4333,7 +4333,7 @@
         <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AI20" t="n">
         <v>25</v>
@@ -4342,7 +4342,7 @@
         <v>40</v>
       </c>
       <c r="AK20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
         <v>24</v>
@@ -4351,22 +4351,22 @@
         <v>38</v>
       </c>
       <c r="AN20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO20" t="n">
         <v>12.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ20" t="n">
         <v>20</v>
       </c>
       <c r="AR20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT20" t="n">
         <v>20</v>
@@ -4387,13 +4387,13 @@
         <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA20" t="n">
         <v>24</v>
       </c>
       <c r="BB20" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC20" t="n">
         <v>20</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G21" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H21" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
         <v>1.35</v>
@@ -4473,7 +4473,7 @@
         <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q21" t="n">
         <v>1.87</v>
@@ -4491,22 +4491,22 @@
         <v>2.14</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W21" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X21" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y21" t="n">
         <v>16</v>
       </c>
       <c r="Z21" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB21" t="n">
         <v>10.5</v>
@@ -4515,13 +4515,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AF21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG21" t="n">
         <v>11.5</v>
@@ -4533,22 +4533,22 @@
         <v>55</v>
       </c>
       <c r="AJ21" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM21" t="n">
         <v>100</v>
       </c>
       <c r="AN21" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP21" t="n">
         <v>13</v>
@@ -4557,10 +4557,10 @@
         <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
         <v>8.4</v>
@@ -4569,10 +4569,10 @@
         <v>7.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -4584,19 +4584,19 @@
         <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
         <v>12</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,588 +727,6 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>English National League</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>15:45:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Scunthorpe</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Southend</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>2026-04-28 18:13:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Paris St-G</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>2026-04-28 18:13:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Brazilian Campeonato Women</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>EC Bahia (W)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Gremio FBPA (W)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
